--- a/data/ippu_distributions.xlsx
+++ b/data/ippu_distributions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D33E2AA-93A9-4101-9189-96289A8CFCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9D33E2AA-93A9-4101-9189-96289A8CFCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4A3E2C0-7C71-4725-8212-E03A464DB5C1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{FB5909C3-F38C-4901-A615-5D51A8770A5A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB5909C3-F38C-4901-A615-5D51A8770A5A}"/>
   </bookViews>
   <sheets>
     <sheet name="ammonia" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="64">
-  <si>
-    <t>Total U.S. Emissions from Ammonia Production: 1990-2021 (kilotons CO2 Eq.)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="63">
   <si>
     <t>Source</t>
   </si>
@@ -583,508 +580,613 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84074A0-088C-4684-B63F-D6368A9563AD}">
-  <dimension ref="A1:AJ54"/>
+  <dimension ref="A1:AJ53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>1990</v>
+      </c>
+      <c r="E1">
+        <v>1991</v>
+      </c>
+      <c r="F1">
+        <v>1992</v>
+      </c>
+      <c r="G1">
+        <v>1993</v>
+      </c>
+      <c r="H1">
+        <v>1994</v>
+      </c>
+      <c r="I1">
+        <v>1995</v>
+      </c>
+      <c r="J1">
+        <v>1996</v>
+      </c>
+      <c r="K1">
+        <v>1997</v>
+      </c>
+      <c r="L1">
+        <v>1998</v>
+      </c>
+      <c r="M1">
+        <v>1999</v>
+      </c>
+      <c r="N1">
+        <v>2000</v>
+      </c>
+      <c r="O1">
+        <v>2001</v>
+      </c>
+      <c r="P1">
+        <v>2002</v>
+      </c>
+      <c r="Q1">
+        <v>2003</v>
+      </c>
+      <c r="R1">
+        <v>2004</v>
+      </c>
+      <c r="S1">
+        <v>2005</v>
+      </c>
+      <c r="T1">
+        <v>2006</v>
+      </c>
+      <c r="U1">
+        <v>2007</v>
+      </c>
+      <c r="V1">
+        <v>2008</v>
+      </c>
+      <c r="W1">
+        <v>2009</v>
+      </c>
+      <c r="X1">
+        <v>2010</v>
+      </c>
+      <c r="Y1">
+        <v>2011</v>
+      </c>
+      <c r="Z1">
+        <v>2012</v>
+      </c>
+      <c r="AA1">
+        <v>2013</v>
+      </c>
+      <c r="AB1">
+        <v>2014</v>
+      </c>
+      <c r="AC1">
+        <v>2015</v>
+      </c>
+      <c r="AD1">
+        <v>2016</v>
+      </c>
+      <c r="AE1">
+        <v>2017</v>
+      </c>
+      <c r="AF1">
+        <v>2018</v>
+      </c>
+      <c r="AG1">
+        <v>2019</v>
+      </c>
+      <c r="AH1">
+        <v>2020</v>
+      </c>
+      <c r="AI1">
+        <v>2021</v>
+      </c>
+      <c r="AJ1">
+        <v>2022</v>
+      </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>1990</v>
+        <v>14403.815604354599</v>
       </c>
       <c r="E2">
-        <v>1991</v>
+        <v>14663.974693530996</v>
       </c>
       <c r="F2">
-        <v>1992</v>
+        <v>15128.808576792448</v>
       </c>
       <c r="G2">
-        <v>1993</v>
+        <v>14547.052345486658</v>
       </c>
       <c r="H2">
-        <v>1994</v>
+        <v>15561.554712779844</v>
       </c>
       <c r="I2">
-        <v>1995</v>
+        <v>14884.66274922726</v>
       </c>
       <c r="J2">
-        <v>1996</v>
+        <v>15219.573166126538</v>
       </c>
       <c r="K2">
-        <v>1997</v>
+        <v>15409.598234317356</v>
       </c>
       <c r="L2">
-        <v>1998</v>
+        <v>15649.762055654426</v>
       </c>
       <c r="M2">
-        <v>1999</v>
+        <v>14302.061319273165</v>
       </c>
       <c r="N2">
-        <v>2000</v>
+        <v>13384.149823445825</v>
       </c>
       <c r="O2">
-        <v>2001</v>
+        <v>10285.999596291473</v>
       </c>
       <c r="P2">
-        <v>2002</v>
+        <v>11652.888280816562</v>
       </c>
       <c r="Q2">
-        <v>2003</v>
+        <v>9846.627438392994</v>
       </c>
       <c r="R2">
-        <v>2004</v>
+        <v>10615.317059150926</v>
       </c>
       <c r="S2">
-        <v>2005</v>
+        <v>10233.689044379847</v>
       </c>
       <c r="T2">
-        <v>2006</v>
+        <v>9764.6818749631093</v>
       </c>
       <c r="U2">
-        <v>2007</v>
+        <v>10262.403978684382</v>
       </c>
       <c r="V2">
-        <v>2008</v>
+        <v>9428.7976023598803</v>
       </c>
       <c r="W2">
-        <v>2009</v>
+        <v>9285.2282858599174</v>
       </c>
       <c r="X2">
-        <v>2010</v>
+        <v>9817.8117409999995</v>
       </c>
       <c r="Y2">
-        <v>2011</v>
+        <v>8967.8274846990007</v>
       </c>
       <c r="Z2">
-        <v>2012</v>
+        <v>9970.631116397999</v>
       </c>
       <c r="AA2">
-        <v>2013</v>
+        <v>9944.1345182270034</v>
       </c>
       <c r="AB2">
-        <v>2014</v>
+        <v>10557.573779920102</v>
       </c>
       <c r="AC2">
-        <v>2015</v>
+        <v>10108.836600000001</v>
       </c>
       <c r="AD2">
-        <v>2016</v>
+        <v>10194.648299999999</v>
       </c>
       <c r="AE2">
-        <v>2017</v>
+        <v>12481.3431</v>
       </c>
       <c r="AF2">
-        <v>2018</v>
+        <v>12669.261999999999</v>
       </c>
       <c r="AG2">
-        <v>2019</v>
+        <v>12400.736000000003</v>
       </c>
       <c r="AH2">
-        <v>2020</v>
+        <v>13005.737000000001</v>
       </c>
       <c r="AI2">
-        <v>2021</v>
-      </c>
-      <c r="AJ2">
-        <v>2022</v>
+        <v>12207.441000000003</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>12609.8</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
       <c r="D3">
-        <v>14403.815604354599</v>
+        <v>993.02417127573926</v>
       </c>
       <c r="E3">
-        <v>14663.974693530996</v>
+        <v>993.49422042892922</v>
       </c>
       <c r="F3">
-        <v>15128.808576792448</v>
+        <v>1062.9534650608819</v>
       </c>
       <c r="G3">
-        <v>14547.052345486658</v>
+        <v>1039.4025177860167</v>
       </c>
       <c r="H3">
-        <v>15561.554712779844</v>
+        <v>1094.111300736761</v>
       </c>
       <c r="I3">
-        <v>14884.66274922726</v>
+        <v>1021.3998395304327</v>
       </c>
       <c r="J3">
-        <v>15219.573166126538</v>
+        <v>1075.0731120041494</v>
       </c>
       <c r="K3">
-        <v>15409.598234317356</v>
+        <v>1041.308321870031</v>
       </c>
       <c r="L3">
-        <v>15649.762055654426</v>
+        <v>1043.3174703769616</v>
       </c>
       <c r="M3">
-        <v>14302.061319273165</v>
+        <v>1002.4610844515792</v>
       </c>
       <c r="N3">
-        <v>13384.149823445825</v>
+        <v>913.10449291663542</v>
       </c>
       <c r="O3">
-        <v>10285.999596291473</v>
+        <v>743.89605967162356</v>
       </c>
       <c r="P3">
-        <v>11652.888280816562</v>
+        <v>881.24571063105464</v>
       </c>
       <c r="Q3">
-        <v>9846.627438392994</v>
+        <v>800.8513434830661</v>
       </c>
       <c r="R3">
-        <v>10615.317059150926</v>
+        <v>889.71076330552876</v>
       </c>
       <c r="S3">
-        <v>10233.689044379847</v>
+        <v>1000.7910581657651</v>
       </c>
       <c r="T3">
-        <v>9764.6818749631093</v>
+        <v>231.46892355144519</v>
       </c>
       <c r="U3">
-        <v>10262.403978684382</v>
+        <v>272.96220328979075</v>
       </c>
       <c r="V3">
-        <v>9428.7976023598803</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>9285.2282858599174</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>9817.8117409999995</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>8967.8274846990007</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>9970.631116397999</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>9944.1345182270034</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>10557.573779920102</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>10108.836600000001</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>10194.648299999999</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>12481.3431</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>12669.261999999999</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>12400.736000000003</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>13005.737000000001</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>12207.441000000003</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>12609.8</v>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>993.02417127573926</v>
+        <v>144.81602497771198</v>
       </c>
       <c r="E4">
-        <v>993.49422042892922</v>
+        <v>144.88457381255219</v>
       </c>
       <c r="F4">
-        <v>1062.9534650608819</v>
+        <v>149.03844880483265</v>
       </c>
       <c r="G4">
-        <v>1039.4025177860167</v>
+        <v>145.73633185888596</v>
       </c>
       <c r="H4">
-        <v>1094.111300736761</v>
+        <v>153.95017417446456</v>
       </c>
       <c r="I4">
-        <v>1021.3998395304327</v>
+        <v>142.45839867134978</v>
       </c>
       <c r="J4">
-        <v>1075.0731120041494</v>
+        <v>144.86154644801672</v>
       </c>
       <c r="K4">
-        <v>1041.308321870031</v>
+        <v>140.31188404858892</v>
       </c>
       <c r="L4">
-        <v>1043.3174703769616</v>
+        <v>140.58260829655671</v>
       </c>
       <c r="M4">
-        <v>1002.4610844515792</v>
+        <v>135.07738341339072</v>
       </c>
       <c r="N4">
-        <v>913.10449291663542</v>
+        <v>119.98645816011987</v>
       </c>
       <c r="O4">
-        <v>743.89605967162356</v>
+        <v>104.14544835402729</v>
       </c>
       <c r="P4">
-        <v>881.24571063105464</v>
+        <v>123.37439948834763</v>
       </c>
       <c r="Q4">
-        <v>800.8513434830661</v>
+        <v>112.11918808762925</v>
       </c>
       <c r="R4">
-        <v>889.71076330552876</v>
+        <v>124.55950686277403</v>
       </c>
       <c r="S4">
-        <v>1000.7910581657651</v>
+        <v>140.1107481432071</v>
       </c>
       <c r="T4">
-        <v>231.46892355144519</v>
+        <v>144.66807721965324</v>
       </c>
       <c r="U4">
-        <v>272.96220328979075</v>
+        <v>155.00353686813116</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>146.30416890555489</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>137.96386295222194</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>141.40215102154423</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>124.87174963612229</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>118.15393109974652</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>92.116355655855187</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>110.98441408354374</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>139.53657626864674</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>125.93820421606446</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>131.57079338374004</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>100.47378533846448</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>115.04701039189085</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>124.90337438499435</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>109.91201076235185</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>144.81602497771198</v>
+        <v>496.51208563786963</v>
       </c>
       <c r="E5">
-        <v>144.88457381255219</v>
+        <v>505.02622871803902</v>
       </c>
       <c r="F5">
-        <v>149.03844880483265</v>
+        <v>519.29119898036038</v>
       </c>
       <c r="G5">
-        <v>145.73633185888596</v>
+        <v>332.71879537594714</v>
       </c>
       <c r="H5">
-        <v>153.95017417446456</v>
+        <v>351.47115236057016</v>
       </c>
       <c r="I5">
-        <v>142.45839867134978</v>
+        <v>326.13117683252409</v>
       </c>
       <c r="J5">
-        <v>144.86154644801672</v>
+        <v>331.63272268602572</v>
       </c>
       <c r="K5">
-        <v>140.31188404858892</v>
+        <v>344.16122502484069</v>
       </c>
       <c r="L5">
-        <v>140.58260829655671</v>
+        <v>344.82526563306357</v>
       </c>
       <c r="M5">
-        <v>135.07738341339072</v>
+        <v>331.32188384416594</v>
       </c>
       <c r="N5">
-        <v>119.98645816011987</v>
+        <v>287.51472049689102</v>
       </c>
       <c r="O5">
-        <v>104.14544835402729</v>
+        <v>226.73951898791086</v>
       </c>
       <c r="P5">
-        <v>123.37439948834763</v>
+        <v>268.60369260034543</v>
       </c>
       <c r="Q5">
-        <v>112.11918808762925</v>
+        <v>244.09948949363854</v>
       </c>
       <c r="R5">
-        <v>124.55950686277403</v>
+        <v>276.1662209300361</v>
       </c>
       <c r="S5">
-        <v>140.1107481432071</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>144.66807721965324</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>155.00353686813116</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>146.30416890555489</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>137.96386295222194</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>141.40215102154423</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>124.87174963612229</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>118.15393109974652</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>92.116355655855187</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>110.98441408354374</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>139.53657626864674</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>125.93820421606446</v>
+        <v>154.30629156038219</v>
       </c>
       <c r="AE5">
-        <v>131.57079338374004</v>
+        <v>299.77222390057557</v>
       </c>
       <c r="AF5">
-        <v>100.47378533846448</v>
+        <v>309.56230799199955</v>
       </c>
       <c r="AG5">
-        <v>115.04701039189085</v>
+        <v>278.5832720204827</v>
       </c>
       <c r="AH5">
-        <v>124.90337438499435</v>
+        <v>301.73068271763754</v>
       </c>
       <c r="AI5">
-        <v>109.91201076235185</v>
+        <v>298.76764760349261</v>
       </c>
       <c r="AJ5">
-        <v>110.1</v>
+        <v>291.8</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>496.51208563786963</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>505.02622871803902</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>519.29119898036038</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>332.71879537594714</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>351.47115236057016</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>326.13117683252409</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>331.63272268602572</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>344.16122502484069</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>344.82526563306357</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>331.32188384416594</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>287.51472049689102</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>226.73951898791086</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>268.60369260034543</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>244.09948949363854</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>276.1662209300361</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1120,54 +1222,54 @@
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>154.30629156038219</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>299.77222390057557</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>309.56230799199955</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>278.5832720204827</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>301.73068271763754</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>298.76764760349261</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>291.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>16.550402854595657</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>16.558237007148819</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>16.872277223188604</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>16.498452663270104</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>17.428321604656372</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>17.023330658840543</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1253,31 +1355,31 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>16.550402854595657</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>16.558237007148819</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>16.872277223188604</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>16.498452663270104</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>17.428321604656372</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>17.023330658840543</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1363,13 +1465,13 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1473,13 +1575,13 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1583,13 +1685,13 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1693,58 +1795,58 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>82.752014272978258</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>82.791185035744107</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>85.2987348505646</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>83.408844019865541</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>43.570804011640931</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>41.214379489824474</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>41.909629789992273</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>40.593375259340185</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>62.77588169217313</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>60.317573725476365</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>53.578858675273658</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>42.25329618934822</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>50.054756363843907</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>49.97312383334333</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>55.517951630264996</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1803,1113 +1905,1113 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>82.752014272978258</v>
+        <v>450.99847778773159</v>
       </c>
       <c r="E13">
-        <v>82.791185035744107</v>
+        <v>451.2119584448053</v>
       </c>
       <c r="F13">
-        <v>85.2987348505646</v>
+        <v>463.05027490306497</v>
       </c>
       <c r="G13">
-        <v>83.408844019865541</v>
+        <v>457.37377105398798</v>
       </c>
       <c r="H13">
-        <v>43.570804011640931</v>
+        <v>505.42132653503467</v>
       </c>
       <c r="I13">
-        <v>41.214379489824474</v>
+        <v>501.74027205003711</v>
       </c>
       <c r="J13">
-        <v>41.909629789992273</v>
+        <v>553.02489744620232</v>
       </c>
       <c r="K13">
-        <v>40.593375259340185</v>
+        <v>576.24943574672045</v>
       </c>
       <c r="L13">
-        <v>62.77588169217313</v>
+        <v>577.36127809843731</v>
       </c>
       <c r="M13">
-        <v>60.317573725476365</v>
+        <v>554.75176961600107</v>
       </c>
       <c r="N13">
-        <v>53.578858675273658</v>
+        <v>516.1681596322137</v>
       </c>
       <c r="O13">
-        <v>42.25329618934822</v>
+        <v>405.86969015683781</v>
       </c>
       <c r="P13">
-        <v>50.054756363843907</v>
+        <v>550.60232000228291</v>
       </c>
       <c r="Q13">
-        <v>49.97312383334333</v>
+        <v>455.52424417316803</v>
       </c>
       <c r="R13">
-        <v>55.517951630264996</v>
+        <v>511.76163105334018</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>575.65501665694808</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>594.37912869103252</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>670.70712808348571</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>633.06457991837578</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>596.9757088750232</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>739.51969860309771</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>692.98458989186634</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>661.07984382280495</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>740.17246441800512</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>855.73292186946912</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>808.3839206362403</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>671.02438095971195</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>570.63175818008835</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>643.87402394334242</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>606.74655748484906</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>588.79206197706435</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>633.85051236074457</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>545.4</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>450.99847778773159</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>451.2119584448053</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>463.05027490306497</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>457.37377105398798</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>505.42132653503467</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>501.74027205003711</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>553.02489744620232</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>576.24943574672045</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>577.36127809843731</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>554.75176961600107</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>516.1681596322137</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>405.86969015683781</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>550.60232000228291</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>455.52424417316803</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>511.76163105334018</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>575.65501665694808</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>594.37912869103252</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>670.70712808348571</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>633.06457991837578</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>596.9757088750232</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>739.51969860309771</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>692.98458989186634</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>661.07984382280495</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>740.17246441800512</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>855.73292186946912</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>808.3839206362403</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>671.02438095971195</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>570.63175818008835</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>643.87402394334242</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>606.74655748484906</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>588.79206197706435</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>633.85051236074457</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>545.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>604.91722433547113</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>608.51521001271908</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>663.64290411208503</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>711.26662592764455</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>770.71911096147062</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>742.75479558835843</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>755.28441512833876</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>823.33954602096514</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>819.62313138935895</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>586.18487141660137</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>533.52469131575322</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>420.74761135027035</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>498.43257393292458</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>452.96151987402214</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>537.38530103653943</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>574.85438381041547</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>593.55245396406303</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>699.95307843596333</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>660.66914008923527</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>623.00662641317831</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>587.70241895598508</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>481.53957283672503</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>593.78605814140712</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>603.64748194020751</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>622.34137894725995</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>570.56187345576745</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>603.64157947142564</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1697.9038281485696</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2010.2617659190294</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1875.4412835309156</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>2042.60288328252</v>
       </c>
       <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
+        <v>1767.5044590241707</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>1959.1</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>604.91722433547113</v>
+        <v>89.372175414816525</v>
       </c>
       <c r="E16">
-        <v>608.51521001271908</v>
+        <v>89.41447983860364</v>
       </c>
       <c r="F16">
-        <v>663.64290411208503</v>
+        <v>91.860175992915728</v>
       </c>
       <c r="G16">
-        <v>711.26662592764455</v>
+        <v>85.24200542689556</v>
       </c>
       <c r="H16">
-        <v>770.71911096147062</v>
+        <v>90.046328290724574</v>
       </c>
       <c r="I16">
-        <v>742.75479558835843</v>
+        <v>83.324723751166871</v>
       </c>
       <c r="J16">
-        <v>755.28441512833876</v>
+        <v>84.730338488462621</v>
       </c>
       <c r="K16">
-        <v>823.33954602096514</v>
+        <v>82.069215198231248</v>
       </c>
       <c r="L16">
-        <v>819.62313138935895</v>
+        <v>82.227563343269026</v>
       </c>
       <c r="M16">
-        <v>586.18487141660137</v>
+        <v>79.007526147454954</v>
       </c>
       <c r="N16">
-        <v>533.52469131575322</v>
+        <v>70.180758546485208</v>
       </c>
       <c r="O16">
-        <v>420.74761135027035</v>
+        <v>55.345866839568799</v>
       </c>
       <c r="P16">
-        <v>498.43257393292458</v>
+        <v>65.564680870950468</v>
       </c>
       <c r="Q16">
-        <v>452.96151987402214</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>537.38530103653943</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>574.85438381041547</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>593.55245396406303</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>699.95307843596333</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>660.66914008923527</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>623.00662641317831</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>587.70241895598508</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>481.53957283672503</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>593.78605814140712</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>603.64748194020751</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>622.34137894725995</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>570.56187345576745</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>603.64157947142564</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1697.9038281485696</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>2010.2617659190294</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1875.4412835309156</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>2042.60288328252</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1767.5044590241707</v>
-      </c>
-      <c r="AJ16" s="1">
-        <v>1959.1</v>
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>89.372175414816525</v>
+        <v>196.94979396968827</v>
       </c>
       <c r="E17">
-        <v>89.41447983860364</v>
+        <v>197.04302038507097</v>
       </c>
       <c r="F17">
-        <v>91.860175992915728</v>
+        <v>202.46732667826325</v>
       </c>
       <c r="G17">
-        <v>85.24200542689556</v>
+        <v>224.56227236117647</v>
       </c>
       <c r="H17">
-        <v>90.046328290724574</v>
+        <v>251.74242317836976</v>
       </c>
       <c r="I17">
-        <v>83.324723751166871</v>
+        <v>241.01452353832136</v>
       </c>
       <c r="J17">
-        <v>84.730338488462621</v>
+        <v>245.08022638060692</v>
       </c>
       <c r="K17">
-        <v>82.069215198231248</v>
+        <v>237.382998799185</v>
       </c>
       <c r="L17">
-        <v>82.227563343269026</v>
+        <v>258.17686555090921</v>
       </c>
       <c r="M17">
-        <v>79.007526147454954</v>
+        <v>248.06664123717039</v>
       </c>
       <c r="N17">
-        <v>70.180758546485208</v>
+        <v>220.35248919971701</v>
       </c>
       <c r="O17">
-        <v>55.345866839568799</v>
+        <v>165.44248367096907</v>
       </c>
       <c r="P17">
-        <v>65.564680870950468</v>
+        <v>195.98904604434657</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>178.1093387906339</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>197.87167375914964</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>222.57593133606616</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>229.81557409750627</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>271.01247326629226</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>255.80225758329723</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>241.21983585357043</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>244.05749210109946</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>192.85236514413205</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>230.34822770179571</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>191.60717463258558</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>266.63013806738763</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>276.69056069748353</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>253.14202650307394</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>261.29434159907913</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>255.72321543883047</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>213.31117990145736</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>276.33522494863053</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>267.49308664032679</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>222.3</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>196.94979396968827</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>197.04302038507097</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>202.46732667826325</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>224.56227236117647</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>251.74242317836976</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>241.01452353832136</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>245.08022638060692</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>237.382998799185</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>258.17686555090921</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>248.06664123717039</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>220.35248919971701</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>165.44248367096907</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>195.98904604434657</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>178.1093387906339</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>197.87167375914964</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>222.57593133606616</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>229.81557409750627</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>271.01247326629226</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>255.80225758329723</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>241.21983585357043</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>244.05749210109946</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>192.85236514413205</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>230.34822770179571</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>191.60717463258558</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>266.63013806738763</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>276.69056069748353</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>253.14202650307394</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>261.29434159907913</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>255.72321543883047</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>213.31117990145736</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>276.33522494863053</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>267.49308664032679</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>222.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>504.7872870651675</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>546.42182123591112</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>561.47189203833182</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>565.53029406875862</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>622.57837732189148</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>594.92060828790102</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>604.95639522945351</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>585.95654722178017</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>594.1604577062019</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>570.89309216225524</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>784.062453008582</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>625.46780697190104</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>740.95139349859085</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>404.26975819025182</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>448.4142247059865</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>524.41451447886084</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>541.47194616498791</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>638.53658269576056</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>602.69956373043055</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>568.34169958305256</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>981.61914652259031</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1051.0209428613834</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1105.600158459355</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1092.6292256644326</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1177.6454184366848</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1054.5754271333778</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1054.995496865517</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1038.9109891423518</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>937.99995566523432</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1016.2344353609355</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1045.9509465873257</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1036.3663571682398</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>879.3</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>504.7872870651675</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>546.42182123591112</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>561.47189203833182</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>565.53029406875862</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>622.57837732189148</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>594.92060828790102</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>604.95639522945351</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>585.95654722178017</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>594.1604577062019</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>570.89309216225524</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>784.062453008582</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>625.46780697190104</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>740.95139349859085</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>404.26975819025182</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>448.4142247059865</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>524.41451447886084</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>541.47194616498791</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>638.53658269576056</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>602.69956373043055</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>568.34169958305256</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>981.61914652259031</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1051.0209428613834</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>1105.600158459355</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1092.6292256644326</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>1177.6454184366848</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1054.5754271333778</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1054.995496865517</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1038.9109891423518</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>937.99995566523432</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>1016.2344353609355</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>1045.9509465873257</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>1036.3663571682398</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>879.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>5790.1584386802897</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>5923.7092893074914</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>6102.1402623865451</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>5746.9610110390868</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>6230.6249736646523</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>5783.4526001481945</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>5840.015803344575</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>5680.4251422689731</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>5674.5860380333388</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>5073.4725392752798</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4511.9436059079035</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3479.0530918722493</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3818.9664115907385</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3209.1715036053429</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3588.0255662585369</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2928.7149526162948</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3023.9761512542377</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2483.9560499370955</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>2344.5473105116594</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>2604.827148318052</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2712.7097917045735</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>2163.2775130870727</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2822.1270525892869</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2977.260680579589</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3200.18600852076</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3199.6722311763642</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>3442.6456885429766</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>4257.6419705667131</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>3888.8188859375905</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>3965.961330076751</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>3957.8227580046532</v>
       </c>
       <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
+        <v>3747.6246436252559</v>
+      </c>
+      <c r="AJ21" s="1">
+        <v>3986.8</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>5790.1584386802897</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>5923.7092893074914</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>6102.1402623865451</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>5746.9610110390868</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>6230.6249736646523</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>5783.4526001481945</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>5840.015803344575</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>5680.4251422689731</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>5674.5860380333388</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>5073.4725392752798</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>4511.9436059079035</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3479.0530918722493</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3818.9664115907385</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3209.1715036053429</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>3588.0255662585369</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2928.7149526162948</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3023.9761512542377</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2483.9560499370955</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>2344.5473105116594</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>2604.827148318052</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>2712.7097917045735</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>2163.2775130870727</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2822.1270525892869</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2977.260680579589</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>3200.18600852076</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>3199.6722311763642</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>3442.6456885429766</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>4257.6419705667131</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>3888.8188859375905</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>3965.961330076751</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>3957.8227580046532</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>3747.6246436252559</v>
-      </c>
-      <c r="AJ22" s="1">
-        <v>3986.8</v>
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3013,13 +3115,13 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3123,13 +3225,13 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3233,13 +3335,13 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3343,13 +3445,13 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3453,233 +3555,233 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>413.76007136489142</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>413.95592517872046</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>425.55632551820145</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>416.12763939581265</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>439.58100047299951</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>407.6639710406551</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>414.54090335753216</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>424.46551086397022</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>569.40377196844349</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>547.10587998882795</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>468.62635545556259</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>369.56756244486263</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>437.80286904150802</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>397.86294744238728</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>329.54886672836784</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>363.48731232580587</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>375.310326044129</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>442.58871533416072</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>417.74901058567247</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>393.93455207741351</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>463.35981465942928</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>388.99793103876914</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>374.88884844621231</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>411.34225221087553</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>462.40440016292899</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>465.60522951116513</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>382.94942835039097</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>417.37182505744926</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>393.7898210945429</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>372.67762504019561</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>409.26503108276916</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>331.90017674124016</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>396.4</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>413.76007136489142</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>413.95592517872046</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>425.55632551820145</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>416.12763939581265</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>439.58100047299951</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>407.6639710406551</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>414.54090335753216</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>424.46551086397022</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>569.40377196844349</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>547.10587998882795</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>468.62635545556259</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>369.56756244486263</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>437.80286904150802</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>397.86294744238728</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>329.54886672836784</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>363.48731232580587</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>375.310326044129</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>442.58871533416072</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>417.74901058567247</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>393.93455207741351</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>463.35981465942928</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>388.99793103876914</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>374.88884844621231</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>411.34225221087553</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>462.40440016292899</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>465.60522951116513</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>382.94942835039097</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>417.37182505744926</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>393.7898210945429</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>372.67762504019561</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>409.26503108276916</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>331.90017674124016</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>396.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3783,343 +3885,343 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>19.869884408578585</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>20.621672161674958</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>20.164775477330128</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>21.301281961246673</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>19.711224973394312</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>82.908180671506429</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>283.27116213583042</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>295.31189415754676</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>283.74745949731135</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>273.93134787499065</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>216.02741572863951</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>255.91375436725826</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>232.56723014748241</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>258.37200566392556</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>290.62972329133817</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>300.08292588990929</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>353.8759992649787</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>334.01517806739889</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>314.97410221167644</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>114.6134276146324</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>197.46776122880144</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>184.32772713873669</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>210.68803569424392</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>179.79994761457144</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>255.01759011120762</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>171.94907537292517</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>200.54243154724057</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>239.21733186930061</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>213.92044415386763</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>247.67071454491787</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>247.60628421034866</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>254.1</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>469.20392092778684</v>
       </c>
       <c r="E32">
-        <v>19.869884408578585</v>
+        <v>364.28121415727412</v>
       </c>
       <c r="F32">
-        <v>20.621672161674958</v>
+        <v>374.00214511401401</v>
       </c>
       <c r="G32">
-        <v>20.164775477330128</v>
+        <v>373.96492703412235</v>
       </c>
       <c r="H32">
-        <v>21.301281961246673</v>
+        <v>399.88315681794893</v>
       </c>
       <c r="I32">
-        <v>19.711224973394312</v>
+        <v>391.53660515333252</v>
       </c>
       <c r="J32">
-        <v>82.908180671506429</v>
+        <v>398.1414830049265</v>
       </c>
       <c r="K32">
-        <v>283.27116213583042</v>
+        <v>385.6370649637318</v>
       </c>
       <c r="L32">
-        <v>295.31189415754676</v>
+        <v>386.38113097858667</v>
       </c>
       <c r="M32">
-        <v>283.74745949731135</v>
+        <v>216.63353943657003</v>
       </c>
       <c r="N32">
-        <v>273.93134787499065</v>
+        <v>205.25985295316104</v>
       </c>
       <c r="O32">
-        <v>216.02741572863951</v>
+        <v>161.87178258454529</v>
       </c>
       <c r="P32">
-        <v>255.91375436725826</v>
+        <v>191.75906663331747</v>
       </c>
       <c r="Q32">
-        <v>232.56723014748241</v>
+        <v>174.26525234191519</v>
       </c>
       <c r="R32">
-        <v>258.37200566392556</v>
+        <v>188.61868182077211</v>
       </c>
       <c r="S32">
-        <v>290.62972329133817</v>
+        <v>212.1677043311422</v>
       </c>
       <c r="T32">
-        <v>300.08292588990929</v>
+        <v>219.06880264690352</v>
       </c>
       <c r="U32">
-        <v>353.8759992649787</v>
+        <v>258.33922811355194</v>
       </c>
       <c r="V32">
-        <v>334.01517806739889</v>
+        <v>243.84028150925815</v>
       </c>
       <c r="W32">
-        <v>314.97410221167644</v>
+        <v>229.93977158703655</v>
       </c>
       <c r="X32">
-        <v>114.6134276146324</v>
+        <v>235.23356368221505</v>
       </c>
       <c r="Y32">
-        <v>197.46776122880144</v>
+        <v>233.01004855449821</v>
       </c>
       <c r="Z32">
-        <v>184.32772713873669</v>
+        <v>228.2377691215593</v>
       </c>
       <c r="AA32">
-        <v>210.68803569424392</v>
+        <v>253.27283868205376</v>
       </c>
       <c r="AB32">
-        <v>179.79994761457144</v>
+        <v>258.57589277464837</v>
       </c>
       <c r="AC32">
-        <v>255.01759011120762</v>
+        <v>210.17013029413181</v>
       </c>
       <c r="AD32">
-        <v>171.94907537292517</v>
+        <v>242.74076664061923</v>
       </c>
       <c r="AE32">
-        <v>200.54243154724057</v>
+        <v>241.23455141663254</v>
       </c>
       <c r="AF32">
-        <v>239.21733186930061</v>
+        <v>233.78593424206525</v>
       </c>
       <c r="AG32">
-        <v>213.92044415386763</v>
+        <v>255.59758346251698</v>
       </c>
       <c r="AH32">
-        <v>247.67071454491787</v>
+        <v>258.91724321550686</v>
       </c>
       <c r="AI32">
-        <v>247.60628421034866</v>
+        <v>228.40407060181775</v>
       </c>
       <c r="AJ32">
-        <v>254.1</v>
+        <v>259.3</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
         <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>469.20392092778684</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>364.28121415727412</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>374.00214511401401</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>373.96492703412235</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>399.88315681794893</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>391.53660515333252</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>398.1414830049265</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>385.6370649637318</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>386.38113097858667</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>216.63353943657003</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>205.25985295316104</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>161.87178258454529</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>191.75906663331747</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>174.26525234191519</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>188.61868182077211</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>212.1677043311422</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>219.06880264690352</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>258.33922811355194</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>243.84028150925815</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>229.93977158703655</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>235.23356368221505</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>233.01004855449821</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>228.2377691215593</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>253.27283868205376</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>258.57589277464837</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>210.17013029413181</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>242.74076664061923</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>241.23455141663254</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>233.78593424206525</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>255.59758346251698</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>258.91724321550686</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>228.40407060181775</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>259.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -4223,13 +4325,13 @@
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
         <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4333,13 +4435,13 @@
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
         <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4443,13 +4545,13 @@
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4553,465 +4655,465 @@
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>438.58567564678486</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>438.7932806894438</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>450.86474135298437</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>440.87531839071784</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>478.31060403890257</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>468.58957550387385</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>476.4942691340425</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>486.23803843253143</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>487.17620862517447</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>468.09835384137301</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>409.01044228166643</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>322.55333147361597</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>408.19301316430449</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>336.35756426288776</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>385.77858696927723</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>433.94300282067576</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>448.05770201744036</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>528.37683636809493</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>498.72238708686012</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>470.29191018933511</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>448.59108994109113</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>473.7178210677879</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>479.1853958082927</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>497.42380452442416</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>462.46225459078704</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>415.21603029345908</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>514.33336826730363</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>500.78507475996872</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>496.15412531195625</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>488.00955606777245</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>449.99618451589993</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>571.10283269490685</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>542</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
         <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>438.58567564678486</v>
+        <v>1931.4320131313129</v>
       </c>
       <c r="E39">
-        <v>438.7932806894438</v>
+        <v>2023.4165622735861</v>
       </c>
       <c r="F39">
-        <v>450.86474135298437</v>
+        <v>2077.1647959214415</v>
       </c>
       <c r="G39">
-        <v>440.87531839071784</v>
+        <v>2089.8040040142132</v>
       </c>
       <c r="H39">
-        <v>478.31060403890257</v>
+        <v>2249.2217270898195</v>
       </c>
       <c r="I39">
-        <v>468.58957550387385</v>
+        <v>2155.6912402721237</v>
       </c>
       <c r="J39">
-        <v>476.4942691340425</v>
+        <v>2192.0558537982911</v>
       </c>
       <c r="K39">
-        <v>486.23803843253143</v>
+        <v>2341.178794848468</v>
       </c>
       <c r="L39">
-        <v>487.17620862517447</v>
+        <v>2365.1476553037055</v>
       </c>
       <c r="M39">
-        <v>468.09835384137301</v>
+        <v>2272.5283058542154</v>
       </c>
       <c r="N39">
-        <v>409.01044228166643</v>
+        <v>1956.0056575536521</v>
       </c>
       <c r="O39">
-        <v>322.55333147361597</v>
+        <v>1344.3689590385579</v>
       </c>
       <c r="P39">
-        <v>408.19301316430449</v>
+        <v>1592.5872482524421</v>
       </c>
       <c r="Q39">
-        <v>336.35756426288776</v>
+        <v>1447.298547942597</v>
       </c>
       <c r="R39">
-        <v>385.77858696927723</v>
+        <v>1732.4447983085256</v>
       </c>
       <c r="S39">
-        <v>433.94300282067576</v>
+        <v>1827.0441557874206</v>
       </c>
       <c r="T39">
-        <v>448.05770201744036</v>
+        <v>1886.4717269442783</v>
       </c>
       <c r="U39">
-        <v>528.37683636809493</v>
+        <v>2224.6419568117944</v>
       </c>
       <c r="V39">
-        <v>498.72238708686012</v>
+        <v>2099.7868769967063</v>
       </c>
       <c r="W39">
-        <v>470.29191018933511</v>
+        <v>1980.0851274023298</v>
       </c>
       <c r="X39">
-        <v>448.59108994109113</v>
+        <v>2113.7089110264637</v>
       </c>
       <c r="Y39">
-        <v>473.7178210677879</v>
+        <v>1982.2714677556467</v>
       </c>
       <c r="Z39">
-        <v>479.1853958082927</v>
+        <v>2087.2841162044342</v>
       </c>
       <c r="AA39">
-        <v>497.42380452442416</v>
+        <v>1869.2599237078261</v>
       </c>
       <c r="AB39">
-        <v>462.46225459078704</v>
+        <v>1855.6346775620232</v>
       </c>
       <c r="AC39">
-        <v>415.21603029345908</v>
+        <v>1724.5210111183267</v>
       </c>
       <c r="AD39">
-        <v>514.33336826730363</v>
+        <v>1769.8054053630217</v>
       </c>
       <c r="AE39">
-        <v>500.78507475996872</v>
+        <v>1910.9818236524093</v>
       </c>
       <c r="AF39">
-        <v>496.15412531195625</v>
+        <v>1885.1793703949197</v>
       </c>
       <c r="AG39">
-        <v>488.00955606777245</v>
+        <v>1872.2206051754538</v>
       </c>
       <c r="AH39">
-        <v>449.99618451589993</v>
+        <v>2126.4588030089276</v>
       </c>
       <c r="AI39">
-        <v>571.10283269490685</v>
-      </c>
-      <c r="AJ39">
-        <v>542</v>
+        <v>1888.0931487807004</v>
+      </c>
+      <c r="AJ39" s="1">
+        <v>2004.7</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40">
-        <v>1931.4320131313129</v>
+        <v>72.821772560220879</v>
       </c>
       <c r="E40">
-        <v>2023.4165622735861</v>
+        <v>72.856242831454807</v>
       </c>
       <c r="F40">
-        <v>2077.1647959214415</v>
+        <v>74.987898769727124</v>
       </c>
       <c r="G40">
-        <v>2089.8040040142132</v>
+        <v>70.576714170655464</v>
       </c>
       <c r="H40">
-        <v>2249.2217270898195</v>
+        <v>74.554486864363355</v>
       </c>
       <c r="I40">
-        <v>2155.6912402721237</v>
+        <v>76.157005579023476</v>
       </c>
       <c r="J40">
-        <v>2192.0558537982911</v>
+        <v>77.44170722063788</v>
       </c>
       <c r="K40">
-        <v>2341.178794848468</v>
+        <v>77.65689180047687</v>
       </c>
       <c r="L40">
-        <v>2365.1476553037055</v>
+        <v>77.806726604383584</v>
       </c>
       <c r="M40">
-        <v>2272.5283058542154</v>
+        <v>74.75980968791437</v>
       </c>
       <c r="N40">
-        <v>1956.0056575536521</v>
+        <v>70.180758546485208</v>
       </c>
       <c r="O40">
-        <v>1344.3689590385579</v>
+        <v>54.155633144094196</v>
       </c>
       <c r="P40">
-        <v>1592.5872482524421</v>
+        <v>71.20465341898921</v>
       </c>
       <c r="Q40">
-        <v>1447.298547942597</v>
+        <v>64.708788553431731</v>
       </c>
       <c r="R40">
-        <v>1732.4447983085256</v>
+        <v>71.888629675086719</v>
       </c>
       <c r="S40">
-        <v>1827.0441557874206</v>
+        <v>80.863917499793828</v>
       </c>
       <c r="T40">
-        <v>1886.4717269442783</v>
+        <v>83.494147423914157</v>
       </c>
       <c r="U40">
-        <v>2224.6419568117944</v>
+        <v>98.461366186674525</v>
       </c>
       <c r="V40">
-        <v>2099.7868769967063</v>
+        <v>92.935352575226688</v>
       </c>
       <c r="W40">
-        <v>1980.0851274023298</v>
+        <v>87.63742237845544</v>
       </c>
       <c r="X40">
-        <v>2113.7089110264637</v>
+        <v>81.473790219151752</v>
       </c>
       <c r="Y40">
-        <v>1982.2714677556467</v>
+        <v>83.145991197793975</v>
       </c>
       <c r="Z40">
-        <v>2087.2841162044342</v>
+        <v>80.316433709359615</v>
       </c>
       <c r="AA40">
-        <v>1869.2599237078261</v>
+        <v>89.0509024602908</v>
       </c>
       <c r="AB40">
-        <v>1855.6346775620232</v>
+        <v>93.516128030329668</v>
       </c>
       <c r="AC40">
-        <v>1724.5210111183267</v>
+        <v>78.664575806399753</v>
       </c>
       <c r="AD40">
-        <v>1769.8054053630217</v>
+        <v>69.729457446181272</v>
       </c>
       <c r="AE40">
-        <v>1910.9818236524093</v>
+        <v>73.361565050101262</v>
       </c>
       <c r="AF40">
-        <v>1885.1793703949197</v>
+        <v>58.648262826112614</v>
       </c>
       <c r="AG40">
-        <v>1872.2206051754538</v>
+        <v>63.364497691086704</v>
       </c>
       <c r="AH40">
-        <v>2126.4588030089276</v>
+        <v>57.520657855989526</v>
       </c>
       <c r="AI40">
-        <v>1888.0931487807004</v>
-      </c>
-      <c r="AJ40" s="1">
-        <v>2004.7</v>
+        <v>67.972973704996107</v>
+      </c>
+      <c r="AJ40">
+        <v>64.599999999999994</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" t="s">
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>72.821772560220879</v>
+        <v>28.963204995542394</v>
       </c>
       <c r="E41">
-        <v>72.856242831454807</v>
+        <v>28.97691476251044</v>
       </c>
       <c r="F41">
-        <v>74.987898769727124</v>
+        <v>29.99515950789085</v>
       </c>
       <c r="G41">
-        <v>70.576714170655464</v>
+        <v>29.330582512480188</v>
       </c>
       <c r="H41">
-        <v>74.554486864363355</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>76.157005579023476</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>77.44170722063788</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>77.65689180047687</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>77.806726604383584</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>74.75980968791437</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>70.180758546485208</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>54.155633144094196</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>71.20465341898921</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>64.708788553431731</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>71.888629675086719</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>80.863917499793828</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>83.494147423914157</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>98.461366186674525</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>92.935352575226688</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>87.63742237845544</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>81.473790219151752</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>83.145991197793975</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>80.316433709359615</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>89.0509024602908</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>93.516128030329668</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>78.664575806399753</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>69.729457446181272</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>73.361565050101262</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>58.648262826112614</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>63.364497691086704</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>57.520657855989526</v>
+        <v>0</v>
       </c>
       <c r="AI41">
-        <v>67.972973704996107</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
-        <v>64.599999999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>28.963204995542394</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>28.97691476251044</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>29.99515950789085</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>29.330582512480188</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -5103,13 +5205,13 @@
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -5213,13 +5315,13 @@
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5323,55 +5425,55 @@
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
         <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>281.35684852812608</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>281.49002912152991</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>288.70341026344943</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>282.30685668262186</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>298.21794745745342</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>318.96345866038075</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>324.344091418201</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>314.15742592011105</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>314.76357580864266</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>302.43741191928996</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>279.96840237361306</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>243.40279072455522</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>288.34359651848109</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>238.3333598205605</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -5410,485 +5512,485 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>8.1119301873853598</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>37.573631845914484</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>38.711853851102831</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>37.38188606094652</v>
       </c>
       <c r="AH45">
-        <v>0</v>
+        <v>39.166754506768868</v>
       </c>
       <c r="AI45">
-        <v>0</v>
+        <v>43.127317439119011</v>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>281.35684852812608</v>
+        <v>736.49292702950663</v>
       </c>
       <c r="E46">
-        <v>281.49002912152991</v>
+        <v>800.59075929564551</v>
       </c>
       <c r="F46">
-        <v>288.70341026344943</v>
+        <v>893.29334409437433</v>
       </c>
       <c r="G46">
-        <v>282.30685668262186</v>
+        <v>873.50141044980057</v>
       </c>
       <c r="H46">
-        <v>298.21794745745342</v>
+        <v>927.5740054033779</v>
       </c>
       <c r="I46">
-        <v>318.96345866038075</v>
+        <v>895.96477151792328</v>
       </c>
       <c r="J46">
-        <v>324.344091418201</v>
+        <v>911.07890847809267</v>
       </c>
       <c r="K46">
-        <v>314.15742592011105</v>
+        <v>898.34904378278929</v>
       </c>
       <c r="L46">
-        <v>314.76357580864266</v>
+        <v>908.03986616706743</v>
       </c>
       <c r="M46">
-        <v>302.43741191928996</v>
+        <v>872.48096078963704</v>
       </c>
       <c r="N46">
-        <v>279.96840237361306</v>
+        <v>1134.9662457410082</v>
       </c>
       <c r="O46">
-        <v>243.40279072455522</v>
+        <v>921.83599714507591</v>
       </c>
       <c r="P46">
-        <v>288.34359651848109</v>
+        <v>742.36138663560041</v>
       </c>
       <c r="Q46">
-        <v>238.3333598205605</v>
+        <v>674.63717175013494</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>604.29155043711512</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>494.79109915715424</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>510.88498126711835</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>477.68385575713381</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>450.87448279070372</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>425.17165312319963</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>354.5758213292662</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>350.2787270343087</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>398.23972135991329</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>336.20440016110268</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>375.99253617787923</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>324.52248159255259</v>
       </c>
       <c r="AD46">
-        <v>8.1119301873853598</v>
+        <v>190.23903243759392</v>
       </c>
       <c r="AE46">
-        <v>37.573631845914484</v>
+        <v>262.9905952354822</v>
       </c>
       <c r="AF46">
-        <v>38.711853851102831</v>
+        <v>478.97358574345481</v>
       </c>
       <c r="AG46">
-        <v>37.38188606094652</v>
+        <v>294.8530765632039</v>
       </c>
       <c r="AH46">
-        <v>39.166754506768868</v>
+        <v>317.50746511177431</v>
       </c>
       <c r="AI46">
-        <v>43.127317439119011</v>
+        <v>224.05842782060103</v>
       </c>
       <c r="AJ46">
-        <v>37.9</v>
+        <v>318.2</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>736.49292702950663</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>800.59075929564551</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>893.29334409437433</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>873.50141044980057</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>927.5740054033779</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>895.96477151792328</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>911.07890847809267</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>898.34904378278929</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>908.03986616706743</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>872.48096078963704</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>1134.9662457410082</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>921.83599714507591</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>742.36138663560041</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>674.63717175013494</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>604.29155043711512</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>494.79109915715424</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>510.88498126711835</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>477.68385575713381</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>450.87448279070372</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>425.17165312319963</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>354.5758213292662</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>350.2787270343087</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>398.23972135991329</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>336.20440016110268</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>375.99253617787923</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>324.52248159255259</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>190.23903243759392</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>262.9905952354822</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>478.97358574345481</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>294.8530765632039</v>
+        <v>0</v>
       </c>
       <c r="AH47">
-        <v>317.50746511177431</v>
+        <v>0</v>
       </c>
       <c r="AI47">
-        <v>224.05842782060103</v>
+        <v>0</v>
       </c>
       <c r="AJ47">
-        <v>318.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>339.2832585192109</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>339.44385864655078</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>365.56600650241978</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>359.29963577788232</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>379.55011494584983</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>366.44959155083069</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>372.63127356753989</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>360.92805393630732</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>361.62444524082827</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>347.46320639042023</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>308.64441124206934</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>243.40279072455522</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>288.34359651848109</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>262.03855958765922</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>291.113361753569</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>424.33540866228441</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>438.13760529380704</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>516.67845622710388</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>487.6805630185163</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>459.87954317407309</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>468.13761026184466</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>421.87630835553097</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>454.99684353251064</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>443.89419980523007</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>482.30754968683146</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>431.275059602174</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>389.51119839330801</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>407.98813582828762</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>376.82980295142619</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>418.24294545143243</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>384.45971108154754</v>
       </c>
       <c r="AI48">
-        <v>0</v>
+        <v>400.44871034216101</v>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>376.7</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49">
-        <v>339.2832585192109</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>339.44385864655078</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>365.56600650241978</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>359.29963577788232</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>379.55011494584983</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>366.44959155083069</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>372.63127356753989</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>360.92805393630732</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>361.62444524082827</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>347.46320639042023</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>308.64441124206934</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>243.40279072455522</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>288.34359651848109</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>262.03855958765922</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>291.113361753569</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>424.33540866228441</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>438.13760529380704</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>516.67845622710388</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>487.6805630185163</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>459.87954317407309</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>468.13761026184466</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>421.87630835553097</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>454.99684353251064</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>443.89419980523007</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>482.30754968683146</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>431.275059602174</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>389.51119839330801</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>407.98813582828762</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>376.82980295142619</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>418.24294545143243</v>
+        <v>0</v>
       </c>
       <c r="AH49">
-        <v>384.45971108154754</v>
+        <v>0</v>
       </c>
       <c r="AI49">
-        <v>400.44871034216101</v>
+        <v>0</v>
       </c>
       <c r="AJ49">
-        <v>376.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>139.0233839786035</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>139.08919086005008</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>23.433718365539729</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5897,22 +5999,22 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>134.39471572768849</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>136.66183627171392</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>132.36970193263105</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>132.62510216656293</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>127.43149378621769</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>135.83372621900364</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -5983,22 +6085,22 @@
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>139.0233839786035</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>139.08919086005008</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>23.433718365539729</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -6007,22 +6109,22 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>134.39471572768849</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>136.66183627171392</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>132.36970193263105</v>
+        <v>0</v>
       </c>
       <c r="L51">
-        <v>132.62510216656293</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>127.43149378621769</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>135.83372621900364</v>
+        <v>0</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -6093,25 +6195,25 @@
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>41.376007136489129</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>41.395592517872053</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>42.18069305797151</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>41.246131658175265</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -6203,221 +6305,111 @@
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53">
-        <v>41.376007136489129</v>
+        <v>140.67842426406304</v>
       </c>
       <c r="E53">
-        <v>41.395592517872053</v>
+        <v>140.74501456076496</v>
       </c>
       <c r="F53">
-        <v>42.18069305797151</v>
+        <v>144.35170513172471</v>
       </c>
       <c r="G53">
-        <v>41.246131658175265</v>
+        <v>141.15342834131093</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>161.69609488764519</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>154.1059407010828</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>156.70557225823194</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>153.54885424185201</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>153.84511851321301</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>147.8205327920125</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>131.30593534503686</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>139.85245921826521</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>182.59411124275451</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>111.4785070128428</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>123.8477382521296</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>139.3101152966745</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>143.84140249268378</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>169.62651204436995</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>160.10644899098457</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>150.9793217212995</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>131.10701335701614</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>130.51469500856248</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>152.05898926258612</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>135.56477809028084</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>153.36011339499873</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>154.42390230270144</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>149.58496942211849</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>170.78756068539377</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>321.25797148062389</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>313.14271156624403</v>
       </c>
       <c r="AH53">
-        <v>0</v>
+        <v>376.63650317307759</v>
       </c>
       <c r="AI53">
-        <v>0</v>
+        <v>343.20834047953008</v>
       </c>
       <c r="AJ53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54">
-        <v>140.67842426406304</v>
-      </c>
-      <c r="E54">
-        <v>140.74501456076496</v>
-      </c>
-      <c r="F54">
-        <v>144.35170513172471</v>
-      </c>
-      <c r="G54">
-        <v>141.15342834131093</v>
-      </c>
-      <c r="H54">
-        <v>161.69609488764519</v>
-      </c>
-      <c r="I54">
-        <v>154.1059407010828</v>
-      </c>
-      <c r="J54">
-        <v>156.70557225823194</v>
-      </c>
-      <c r="K54">
-        <v>153.54885424185201</v>
-      </c>
-      <c r="L54">
-        <v>153.84511851321301</v>
-      </c>
-      <c r="M54">
-        <v>147.8205327920125</v>
-      </c>
-      <c r="N54">
-        <v>131.30593534503686</v>
-      </c>
-      <c r="O54">
-        <v>139.85245921826521</v>
-      </c>
-      <c r="P54">
-        <v>182.59411124275451</v>
-      </c>
-      <c r="Q54">
-        <v>111.4785070128428</v>
-      </c>
-      <c r="R54">
-        <v>123.8477382521296</v>
-      </c>
-      <c r="S54">
-        <v>139.3101152966745</v>
-      </c>
-      <c r="T54">
-        <v>143.84140249268378</v>
-      </c>
-      <c r="U54">
-        <v>169.62651204436995</v>
-      </c>
-      <c r="V54">
-        <v>160.10644899098457</v>
-      </c>
-      <c r="W54">
-        <v>150.9793217212995</v>
-      </c>
-      <c r="X54">
-        <v>131.10701335701614</v>
-      </c>
-      <c r="Y54">
-        <v>130.51469500856248</v>
-      </c>
-      <c r="Z54">
-        <v>152.05898926258612</v>
-      </c>
-      <c r="AA54">
-        <v>135.56477809028084</v>
-      </c>
-      <c r="AB54">
-        <v>153.36011339499873</v>
-      </c>
-      <c r="AC54">
-        <v>154.42390230270144</v>
-      </c>
-      <c r="AD54">
-        <v>149.58496942211849</v>
-      </c>
-      <c r="AE54">
-        <v>170.78756068539377</v>
-      </c>
-      <c r="AF54">
-        <v>321.25797148062389</v>
-      </c>
-      <c r="AG54">
-        <v>313.14271156624403</v>
-      </c>
-      <c r="AH54">
-        <v>376.63650317307759</v>
-      </c>
-      <c r="AI54">
-        <v>343.20834047953008</v>
-      </c>
-      <c r="AJ54">
         <v>360.9</v>
       </c>
     </row>
@@ -6433,16 +6425,16 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1">
         <v>1990</v>
@@ -6546,16 +6538,16 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
       <c r="E2">
         <v>20081.5</v>
@@ -6659,16 +6651,16 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6772,16 +6764,16 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>57.5</v>
@@ -6885,16 +6877,16 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>115</v>
@@ -6998,16 +6990,16 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7111,16 +7103,16 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7224,16 +7216,16 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -7337,16 +7329,16 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7450,16 +7442,16 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7563,16 +7555,16 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>98.4</v>
@@ -7676,16 +7668,16 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7789,16 +7781,16 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7902,16 +7894,16 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -8015,16 +8007,16 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>306.5</v>
@@ -8128,16 +8120,16 @@
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -8241,16 +8233,16 @@
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>482.4</v>
@@ -8354,16 +8346,16 @@
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -8467,16 +8459,16 @@
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>83.6</v>
@@ -8580,16 +8572,16 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>180.2</v>
@@ -8693,16 +8685,16 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>5647.1</v>
@@ -8806,16 +8798,16 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -8919,16 +8911,16 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -9032,16 +9024,16 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -9145,16 +9137,16 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -9258,16 +9250,16 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -9371,16 +9363,16 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -9484,16 +9476,16 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -9597,16 +9589,16 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -9710,16 +9702,16 @@
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -9823,16 +9815,16 @@
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -9936,16 +9928,16 @@
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -10049,16 +10041,16 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -10162,16 +10154,16 @@
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -10275,16 +10267,16 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -10388,16 +10380,16 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -10501,16 +10493,16 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -10614,16 +10606,16 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>278.7</v>
@@ -10727,16 +10719,16 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>151.6</v>
@@ -10840,16 +10832,16 @@
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -10953,16 +10945,16 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -11066,16 +11058,16 @@
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -11179,16 +11171,16 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -11292,16 +11284,16 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -11405,16 +11397,16 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>42.1</v>
@@ -11518,16 +11510,16 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>12272.4</v>
@@ -11631,16 +11623,16 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -11744,16 +11736,16 @@
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -11857,16 +11849,16 @@
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -11970,16 +11962,16 @@
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -12083,16 +12075,16 @@
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -12196,16 +12188,16 @@
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52">
         <v>365.9</v>
@@ -12309,16 +12301,16 @@
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -12432,16 +12424,16 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1">
         <v>1990</v>
@@ -12545,16 +12537,16 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="E2">
         <v>3381.3308358775671</v>
@@ -12658,16 +12650,16 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -12771,16 +12763,16 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>63</v>
       </c>
       <c r="E4">
         <v>57.505626460502846</v>
@@ -12884,16 +12876,16 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>63</v>
       </c>
       <c r="E5">
         <v>115.01125292100569</v>
@@ -12997,16 +12989,16 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>63</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -13110,16 +13102,16 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -13223,16 +13215,16 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
         <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -13336,16 +13328,16 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
         <v>61</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
         <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>63</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -13449,16 +13441,16 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
         <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>63</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -13562,16 +13554,16 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
         <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -13675,16 +13667,16 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
         <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -13788,16 +13780,16 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
         <v>61</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
         <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -13901,16 +13893,16 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
         <v>61</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
         <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -14014,16 +14006,16 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
         <v>61</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
         <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -14127,16 +14119,16 @@
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
         <v>61</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
         <v>62</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -14240,16 +14232,16 @@
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
         <v>62</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -14353,16 +14345,16 @@
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
         <v>61</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -14466,16 +14458,16 @@
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
         <v>61</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
         <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>63</v>
       </c>
       <c r="E19">
         <v>83.644547578913219</v>
@@ -14579,16 +14571,16 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" t="s">
-        <v>63</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -14692,16 +14684,16 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
         <v>61</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
         <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" t="s">
-        <v>63</v>
       </c>
       <c r="E21">
         <v>1211.8003830495056</v>
@@ -14805,16 +14797,16 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
         <v>61</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>63</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -14918,16 +14910,16 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s">
-        <v>63</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -15031,16 +15023,16 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
         <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>63</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -15144,16 +15136,16 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" t="s">
         <v>61</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
         <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" t="s">
-        <v>63</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -15257,16 +15249,16 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
         <v>62</v>
-      </c>
-      <c r="C26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" t="s">
-        <v>63</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -15370,16 +15362,16 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
         <v>61</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
         <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -15483,16 +15475,16 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
         <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>63</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -15596,16 +15588,16 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
         <v>61</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
         <v>62</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>63</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -15709,16 +15701,16 @@
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
         <v>61</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" t="s">
         <v>62</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" t="s">
-        <v>63</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -15822,16 +15814,16 @@
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
         <v>61</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
         <v>62</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s">
-        <v>63</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -15935,16 +15927,16 @@
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
         <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" t="s">
-        <v>63</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -16048,16 +16040,16 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
         <v>61</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
         <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" t="s">
-        <v>63</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -16161,16 +16153,16 @@
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
         <v>61</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" t="s">
         <v>62</v>
-      </c>
-      <c r="C34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" t="s">
-        <v>63</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -16274,16 +16266,16 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
         <v>61</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
         <v>62</v>
-      </c>
-      <c r="C35" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" t="s">
-        <v>63</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -16387,16 +16379,16 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
         <v>61</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
         <v>62</v>
-      </c>
-      <c r="C36" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" t="s">
-        <v>63</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -16500,16 +16492,16 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
         <v>61</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
         <v>62</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" t="s">
-        <v>63</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -16613,16 +16605,16 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" t="s">
         <v>61</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
         <v>62</v>
-      </c>
-      <c r="C38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" t="s">
-        <v>63</v>
       </c>
       <c r="E38">
         <v>125.46682136836985</v>
@@ -16726,16 +16718,16 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
         <v>61</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" t="s">
         <v>62</v>
-      </c>
-      <c r="C39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" t="s">
-        <v>63</v>
       </c>
       <c r="E39">
         <v>151.60574248678026</v>
@@ -16839,16 +16831,16 @@
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
         <v>61</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
         <v>62</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
-        <v>63</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -16952,16 +16944,16 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" t="s">
         <v>61</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" t="s">
         <v>62</v>
-      </c>
-      <c r="C41" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" t="s">
-        <v>63</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -17065,16 +17057,16 @@
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" t="s">
         <v>61</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" t="s">
         <v>62</v>
-      </c>
-      <c r="C42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" t="s">
-        <v>63</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -17178,16 +17170,16 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
         <v>61</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" t="s">
         <v>62</v>
-      </c>
-      <c r="C43" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" t="s">
-        <v>63</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -17291,16 +17283,16 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" t="s">
         <v>61</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" t="s">
         <v>62</v>
-      </c>
-      <c r="C44" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" t="s">
-        <v>63</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -17404,16 +17396,16 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" t="s">
         <v>61</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" t="s">
         <v>62</v>
-      </c>
-      <c r="C45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" t="s">
-        <v>63</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -17517,16 +17509,16 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
         <v>61</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" t="s">
         <v>62</v>
-      </c>
-      <c r="C46" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" t="s">
-        <v>63</v>
       </c>
       <c r="E46">
         <v>1270.3515663547448</v>
@@ -17630,16 +17622,16 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" t="s">
         <v>62</v>
-      </c>
-      <c r="C47" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" t="s">
-        <v>63</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -17743,16 +17735,16 @@
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
         <v>61</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" t="s">
         <v>62</v>
-      </c>
-      <c r="C48" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" t="s">
-        <v>63</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -17856,16 +17848,16 @@
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s">
         <v>61</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" t="s">
         <v>62</v>
-      </c>
-      <c r="C49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" t="s">
-        <v>63</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -17969,16 +17961,16 @@
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" t="s">
         <v>61</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" t="s">
         <v>62</v>
-      </c>
-      <c r="C50" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" t="s">
-        <v>63</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -18082,16 +18074,16 @@
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" t="s">
         <v>61</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" t="s">
         <v>62</v>
-      </c>
-      <c r="C51" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" t="s">
-        <v>63</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -18195,16 +18187,16 @@
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
         <v>61</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" t="s">
         <v>62</v>
-      </c>
-      <c r="C52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" t="s">
-        <v>63</v>
       </c>
       <c r="E52">
         <v>365.94489565774535</v>
@@ -18308,16 +18300,16 @@
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" t="s">
         <v>61</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" t="s">
         <v>62</v>
-      </c>
-      <c r="C53" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" t="s">
-        <v>63</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -18431,16 +18423,16 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1">
         <v>1990</v>
@@ -18544,16 +18536,16 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
       <c r="E2">
         <v>104763.9</v>
@@ -18657,16 +18649,16 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -18770,16 +18762,16 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>5835.2</v>
@@ -18883,16 +18875,16 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
         <v>59</v>
       </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>1047.0999999999999</v>
@@ -18996,16 +18988,16 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>266.8</v>
@@ -19109,16 +19101,16 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
         <v>59</v>
       </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>3464.4</v>
@@ -19222,16 +19214,16 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
         <v>59</v>
       </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>118.3</v>
@@ -19335,16 +19327,16 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" t="s">
-        <v>60</v>
-      </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>1297.8</v>
@@ -19448,16 +19440,16 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -19561,16 +19553,16 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
         <v>59</v>
       </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -19674,16 +19666,16 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
         <v>59</v>
       </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>950.1</v>
@@ -19787,16 +19779,16 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>869.8</v>
@@ -19900,16 +19892,16 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -20013,16 +20005,16 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>389</v>
@@ -20126,16 +20118,16 @@
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
         <v>59</v>
       </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -20239,16 +20231,16 @@
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>7558.2</v>
@@ -20352,16 +20344,16 @@
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
         <v>59</v>
       </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>24295.9</v>
@@ -20465,16 +20457,16 @@
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
         <v>59</v>
       </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -20578,16 +20570,16 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
         <v>59</v>
       </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>3122.5</v>
@@ -20691,16 +20683,16 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
         <v>59</v>
       </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>253.1</v>
@@ -20804,16 +20796,16 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
         <v>59</v>
       </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -20917,16 +20909,16 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>1919.6</v>
@@ -21030,16 +21022,16 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
         <v>59</v>
       </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -21143,16 +21135,16 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
         <v>59</v>
       </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>6812.7</v>
@@ -21256,16 +21248,16 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
         <v>59</v>
       </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>209.6</v>
@@ -21369,16 +21361,16 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
         <v>59</v>
       </c>
-      <c r="B27" t="s">
-        <v>60</v>
-      </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>319</v>
@@ -21482,16 +21474,16 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
         <v>59</v>
       </c>
-      <c r="B28" t="s">
-        <v>60</v>
-      </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>356.4</v>
@@ -21595,16 +21587,16 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" t="s">
         <v>59</v>
       </c>
-      <c r="B29" t="s">
-        <v>60</v>
-      </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -21708,16 +21700,16 @@
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="B30" t="s">
-        <v>60</v>
-      </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>1020.3</v>
@@ -21821,16 +21813,16 @@
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
         <v>59</v>
       </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -21934,16 +21926,16 @@
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
         <v>59</v>
       </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -22047,16 +22039,16 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" t="s">
         <v>59</v>
       </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -22160,16 +22152,16 @@
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
         <v>59</v>
       </c>
-      <c r="B34" t="s">
-        <v>60</v>
-      </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>1001.4</v>
@@ -22273,16 +22265,16 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" t="s">
         <v>59</v>
       </c>
-      <c r="B35" t="s">
-        <v>60</v>
-      </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -22386,16 +22378,16 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" t="s">
         <v>59</v>
       </c>
-      <c r="B36" t="s">
-        <v>60</v>
-      </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -22499,16 +22491,16 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s">
         <v>59</v>
       </c>
-      <c r="B37" t="s">
-        <v>60</v>
-      </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>1521.9</v>
@@ -22612,16 +22604,16 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
         <v>59</v>
       </c>
-      <c r="B38" t="s">
-        <v>60</v>
-      </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>15169.8</v>
@@ -22725,16 +22717,16 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
         <v>59</v>
       </c>
-      <c r="B39" t="s">
-        <v>60</v>
-      </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>226.7</v>
@@ -22838,16 +22830,16 @@
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
         <v>59</v>
       </c>
-      <c r="B40" t="s">
-        <v>60</v>
-      </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>1436.1</v>
@@ -22951,16 +22943,16 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
         <v>59</v>
       </c>
-      <c r="B41" t="s">
-        <v>60</v>
-      </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41">
         <v>8956.7999999999993</v>
@@ -23064,16 +23056,16 @@
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
         <v>59</v>
       </c>
-      <c r="B42" t="s">
-        <v>60</v>
-      </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -23177,16 +23169,16 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" t="s">
         <v>59</v>
       </c>
-      <c r="B43" t="s">
-        <v>60</v>
-      </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>1641.3</v>
@@ -23290,16 +23282,16 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
         <v>59</v>
       </c>
-      <c r="B44" t="s">
-        <v>60</v>
-      </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -23403,16 +23395,16 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" t="s">
         <v>59</v>
       </c>
-      <c r="B45" t="s">
-        <v>60</v>
-      </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>3452.3</v>
@@ -23516,16 +23508,16 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
         <v>59</v>
       </c>
-      <c r="B46" t="s">
-        <v>60</v>
-      </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>4539.3999999999996</v>
@@ -23629,16 +23621,16 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
         <v>59</v>
       </c>
-      <c r="B47" t="s">
-        <v>60</v>
-      </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47">
         <v>546.1</v>
@@ -23742,16 +23734,16 @@
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
         <v>59</v>
       </c>
-      <c r="B48" t="s">
-        <v>60</v>
-      </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48">
         <v>1629</v>
@@ -23855,16 +23847,16 @@
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
         <v>59</v>
       </c>
-      <c r="B49" t="s">
-        <v>60</v>
-      </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -23968,16 +23960,16 @@
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
         <v>59</v>
       </c>
-      <c r="B50" t="s">
-        <v>60</v>
-      </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50">
         <v>497.3</v>
@@ -24081,16 +24073,16 @@
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
         <v>59</v>
       </c>
-      <c r="B51" t="s">
-        <v>60</v>
-      </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E51">
         <v>1738.4</v>
@@ -24194,16 +24186,16 @@
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
         <v>59</v>
       </c>
-      <c r="B52" t="s">
-        <v>60</v>
-      </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52">
         <v>2301.6</v>
@@ -24307,16 +24299,16 @@
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
         <v>59</v>
       </c>
-      <c r="B53" t="s">
-        <v>60</v>
-      </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53">
         <v>0</v>

--- a/data/ippu_distributions.xlsx
+++ b/data/ippu_distributions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/camobreco_vincent_epa_gov/Documents/GHG Inventory/State Level Data/FFC CO2 Inv State Breakout/2023 Calculations/IPPU Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{9D33E2AA-93A9-4101-9189-96289A8CFCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4A3E2C0-7C71-4725-8212-E03A464DB5C1}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{9D33E2AA-93A9-4101-9189-96289A8CFCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46DB89C9-D887-4D25-8249-36672B369FE1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB5909C3-F38C-4901-A615-5D51A8770A5A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="3" xr2:uid="{FB5909C3-F38C-4901-A615-5D51A8770A5A}"/>
   </bookViews>
   <sheets>
     <sheet name="ammonia" sheetId="1" r:id="rId1"/>
@@ -284,9 +284,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -324,7 +324,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -430,7 +430,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -572,7 +572,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -580,10 +580,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84074A0-088C-4684-B63F-D6368A9563AD}">
-  <dimension ref="A1:AJ53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AK53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -692,8 +692,11 @@
       <c r="AJ1">
         <v>2022</v>
       </c>
+      <c r="AK1">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -791,19 +794,22 @@
         <v>12669.261999999999</v>
       </c>
       <c r="AG2">
-        <v>12400.736000000003</v>
+        <v>12387.934000000001</v>
       </c>
       <c r="AH2">
-        <v>13005.737000000001</v>
+        <v>12334.688</v>
       </c>
       <c r="AI2">
-        <v>12207.441000000003</v>
+        <v>11458.29880368</v>
       </c>
       <c r="AJ2" s="1">
-        <v>12609.8</v>
+        <v>11944.866439439997</v>
+      </c>
+      <c r="AK2">
+        <v>12210.56328547</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -912,8 +918,11 @@
       <c r="AJ3">
         <v>0</v>
       </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1011,19 +1020,22 @@
         <v>100.47378533846448</v>
       </c>
       <c r="AG4">
-        <v>115.04701039189085</v>
+        <v>114.99915333600946</v>
       </c>
       <c r="AH4">
-        <v>124.90337438499435</v>
+        <v>124.86278847654003</v>
       </c>
       <c r="AI4">
-        <v>109.91201076235185</v>
+        <v>109.70440247842215</v>
       </c>
       <c r="AJ4">
-        <v>110.1</v>
+        <v>110.10075907992965</v>
+      </c>
+      <c r="AK4">
+        <v>117.92595962610604</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1121,19 +1133,22 @@
         <v>309.56230799199955</v>
       </c>
       <c r="AG5">
-        <v>278.5832720204827</v>
+        <v>278.46738743407502</v>
       </c>
       <c r="AH5">
-        <v>301.73068271763754</v>
+        <v>301.63263881828783</v>
       </c>
       <c r="AI5">
-        <v>298.76764760349261</v>
+        <v>298.2033176619106</v>
       </c>
       <c r="AJ5">
-        <v>291.8</v>
+        <v>291.7083581710159</v>
+      </c>
+      <c r="AK5">
+        <v>317.18525397226534</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1242,8 +1257,11 @@
       <c r="AJ6">
         <v>0</v>
       </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1370,11 @@
       <c r="AJ7">
         <v>0</v>
       </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1462,8 +1483,11 @@
       <c r="AJ8">
         <v>0</v>
       </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1572,8 +1596,11 @@
       <c r="AJ9">
         <v>0</v>
       </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1682,8 +1709,11 @@
       <c r="AJ10">
         <v>0</v>
       </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1792,8 +1822,11 @@
       <c r="AJ11">
         <v>0</v>
       </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1902,8 +1935,11 @@
       <c r="AJ12">
         <v>0</v>
       </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2001,19 +2037,22 @@
         <v>643.87402394334242</v>
       </c>
       <c r="AG13">
-        <v>606.74655748484906</v>
+        <v>606.49416410401739</v>
       </c>
       <c r="AH13">
-        <v>588.79206197706435</v>
+        <v>588.60074079904427</v>
       </c>
       <c r="AI13">
-        <v>633.85051236074457</v>
+        <v>632.65325815507185</v>
       </c>
       <c r="AJ13">
-        <v>545.4</v>
+        <v>545.14764310658302</v>
+      </c>
+      <c r="AK13">
+        <v>685.23351990460685</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2122,8 +2161,11 @@
       <c r="AJ14">
         <v>0</v>
       </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2221,19 +2263,22 @@
         <v>2010.2617659190294</v>
       </c>
       <c r="AG15">
-        <v>1875.4412835309156</v>
+        <v>1867.0175773753058</v>
       </c>
       <c r="AH15">
-        <v>2042.60288328252</v>
+        <v>2035.426227052847</v>
       </c>
       <c r="AI15">
-        <v>1767.5044590241707</v>
+        <v>1749.9909947375822</v>
       </c>
       <c r="AJ15" s="1">
-        <v>1959.1</v>
+        <v>1950.7748252054048</v>
+      </c>
+      <c r="AK15">
+        <v>1948.8607452207436</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2342,8 +2387,11 @@
       <c r="AJ16">
         <v>0</v>
       </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2441,19 +2489,22 @@
         <v>255.72321543883047</v>
       </c>
       <c r="AG17">
-        <v>213.31117990145736</v>
+        <v>213.22244708674197</v>
       </c>
       <c r="AH17">
-        <v>276.33522494863053</v>
+        <v>276.24543300988029</v>
       </c>
       <c r="AI17">
-        <v>267.49308664032679</v>
+        <v>266.98782993275432</v>
       </c>
       <c r="AJ17">
-        <v>222.3</v>
+        <v>222.22836294294976</v>
+      </c>
+      <c r="AK17">
+        <v>278.27528493332221</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2562,8 +2613,11 @@
       <c r="AJ18">
         <v>0</v>
       </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2661,19 +2715,22 @@
         <v>937.99995566523432</v>
       </c>
       <c r="AG19">
-        <v>1016.2344353609355</v>
+        <v>1015.8117039227524</v>
       </c>
       <c r="AH19">
-        <v>1045.9509465873257</v>
+        <v>385.30107691146708</v>
       </c>
       <c r="AI19">
-        <v>1036.3663571682398</v>
+        <v>320.28480731138751</v>
       </c>
       <c r="AJ19">
-        <v>879.3</v>
+        <v>226.52789306467491</v>
+      </c>
+      <c r="AK19">
+        <v>337.21972659991872</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2782,8 +2839,11 @@
       <c r="AJ20">
         <v>0</v>
       </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -2881,19 +2941,22 @@
         <v>3888.8188859375905</v>
       </c>
       <c r="AG21">
-        <v>3965.961330076751</v>
+        <v>3964.311576359984</v>
       </c>
       <c r="AH21">
-        <v>3957.8227580046532</v>
+        <v>3956.536709225541</v>
       </c>
       <c r="AI21">
-        <v>3747.6246436252559</v>
+        <v>3740.5459093206132</v>
       </c>
       <c r="AJ21" s="1">
-        <v>3986.8</v>
+        <v>3985.2407451428135</v>
+      </c>
+      <c r="AK21">
+        <v>3991.9076144291653</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -3002,8 +3065,11 @@
       <c r="AJ22">
         <v>0</v>
       </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3178,11 @@
       <c r="AJ23">
         <v>0</v>
       </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3291,11 @@
       <c r="AJ24">
         <v>0</v>
       </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3332,8 +3404,11 @@
       <c r="AJ25">
         <v>0</v>
       </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -3442,8 +3517,11 @@
       <c r="AJ26">
         <v>0</v>
       </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -3552,8 +3630,11 @@
       <c r="AJ27">
         <v>0</v>
       </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -3651,19 +3732,22 @@
         <v>393.7898210945429</v>
       </c>
       <c r="AG28">
-        <v>372.67762504019561</v>
+        <v>372.52259924798653</v>
       </c>
       <c r="AH28">
-        <v>409.26503108276916</v>
+        <v>409.13204513929998</v>
       </c>
       <c r="AI28">
-        <v>331.90017674124016</v>
+        <v>331.27326412585552</v>
       </c>
       <c r="AJ28">
-        <v>396.4</v>
+        <v>396.25352893790466</v>
+      </c>
+      <c r="AK28">
+        <v>431.06524449568587</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3856,11 @@
       <c r="AJ29">
         <v>0</v>
       </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -3882,8 +3969,11 @@
       <c r="AJ30">
         <v>0</v>
       </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -3981,19 +4071,22 @@
         <v>239.21733186930061</v>
       </c>
       <c r="AG31">
-        <v>213.92044415386763</v>
+        <v>213.831457898465</v>
       </c>
       <c r="AH31">
-        <v>247.67071454491787</v>
+        <v>247.59023680765236</v>
       </c>
       <c r="AI31">
-        <v>247.60628421034866</v>
+        <v>247.13859086729565</v>
       </c>
       <c r="AJ31">
-        <v>254.1</v>
+        <v>254.04006858641765</v>
+      </c>
+      <c r="AK31">
+        <v>236.52586217512305</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -4091,19 +4184,22 @@
         <v>233.78593424206525</v>
       </c>
       <c r="AG32">
-        <v>255.59758346251698</v>
+        <v>255.4912604229765</v>
       </c>
       <c r="AH32">
-        <v>258.91724321550686</v>
+        <v>258.83311104868488</v>
       </c>
       <c r="AI32">
-        <v>228.40407060181775</v>
+        <v>227.97264753156992</v>
       </c>
       <c r="AJ32">
-        <v>259.3</v>
+        <v>259.1910487341973</v>
+      </c>
+      <c r="AK32">
+        <v>254.41701199270861</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -4212,8 +4308,11 @@
       <c r="AJ33">
         <v>0</v>
       </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -4322,8 +4421,11 @@
       <c r="AJ34">
         <v>0</v>
       </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -4432,8 +4534,11 @@
       <c r="AJ35">
         <v>0</v>
       </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -4542,8 +4647,11 @@
       <c r="AJ36">
         <v>0</v>
       </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -4652,8 +4760,11 @@
       <c r="AJ37">
         <v>0</v>
       </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -4751,19 +4862,22 @@
         <v>496.15412531195625</v>
       </c>
       <c r="AG38">
-        <v>488.00955606777245</v>
+        <v>487.80655469889001</v>
       </c>
       <c r="AH38">
-        <v>449.99618451589993</v>
+        <v>449.84996345470381</v>
       </c>
       <c r="AI38">
-        <v>571.10283269490685</v>
+        <v>570.02410000481393</v>
       </c>
       <c r="AJ38">
-        <v>542</v>
+        <v>541.83071355122388</v>
+      </c>
+      <c r="AK38">
+        <v>530.77576603612806</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -4861,19 +4975,22 @@
         <v>1885.1793703949197</v>
       </c>
       <c r="AG39">
-        <v>1872.2206051754538</v>
+        <v>1871.4418020947048</v>
       </c>
       <c r="AH39">
-        <v>2126.4588030089276</v>
+        <v>2125.7678347886076</v>
       </c>
       <c r="AI39">
-        <v>1888.0931487807004</v>
+        <v>1884.5268071607175</v>
       </c>
       <c r="AJ39" s="1">
-        <v>2004.7</v>
+        <v>2003.9147731159312</v>
+      </c>
+      <c r="AK39">
+        <v>1992.2473644612269</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -4971,19 +5088,22 @@
         <v>58.648262826112614</v>
       </c>
       <c r="AG40">
-        <v>63.364497691086704</v>
+        <v>63.338139437216668</v>
       </c>
       <c r="AH40">
-        <v>57.520657855989526</v>
+        <v>57.501967182775374</v>
       </c>
       <c r="AI40">
-        <v>67.972973704996107</v>
+        <v>70.059417760957587</v>
       </c>
       <c r="AJ40">
-        <v>64.599999999999994</v>
+        <v>64.548195447380692</v>
+      </c>
+      <c r="AK40">
+        <v>63.182194645899244</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -5092,8 +5212,11 @@
       <c r="AJ41">
         <v>0</v>
       </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -5202,8 +5325,11 @@
       <c r="AJ42">
         <v>0</v>
       </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -5312,8 +5438,11 @@
       <c r="AJ43">
         <v>0</v>
       </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -5422,8 +5551,11 @@
       <c r="AJ44">
         <v>0</v>
       </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -5521,19 +5653,22 @@
         <v>38.711853851102831</v>
       </c>
       <c r="AG45">
-        <v>37.38188606094652</v>
+        <v>37.3663360088063</v>
       </c>
       <c r="AH45">
-        <v>39.166754506768868</v>
+        <v>39.154027722399022</v>
       </c>
       <c r="AI45">
-        <v>43.127317439119011</v>
+        <v>43.045856020099151</v>
       </c>
       <c r="AJ45">
-        <v>37.9</v>
+        <v>37.924301914206914</v>
+      </c>
+      <c r="AK45">
+        <v>32.276810979282665</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -5631,19 +5766,22 @@
         <v>478.97358574345481</v>
       </c>
       <c r="AG46">
-        <v>294.8530765632039</v>
+        <v>294.73042409171586</v>
       </c>
       <c r="AH46">
-        <v>317.50746511177431</v>
+        <v>317.40429472926024</v>
       </c>
       <c r="AI46">
-        <v>224.05842782060103</v>
+        <v>223.63521305656224</v>
       </c>
       <c r="AJ46">
-        <v>318.2</v>
+        <v>318.08680592120402</v>
+      </c>
+      <c r="AK46">
+        <v>228.7525549861079</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -5752,8 +5890,11 @@
       <c r="AJ47">
         <v>0</v>
       </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -5851,19 +5992,22 @@
         <v>376.82980295142619</v>
       </c>
       <c r="AG48">
-        <v>418.24294545143243</v>
+        <v>418.06896547625286</v>
       </c>
       <c r="AH48">
-        <v>384.45971108154754</v>
+        <v>384.33478534022822</v>
       </c>
       <c r="AI48">
-        <v>400.44871034216101</v>
+        <v>399.69231921639272</v>
       </c>
       <c r="AJ48">
-        <v>376.7</v>
+        <v>376.60053716258943</v>
+      </c>
+      <c r="AK48">
+        <v>406.5281013484032</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -5972,8 +6116,11 @@
       <c r="AJ49">
         <v>0</v>
       </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -6082,8 +6229,11 @@
       <c r="AJ50">
         <v>0</v>
       </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -6192,8 +6342,11 @@
       <c r="AJ51">
         <v>0</v>
       </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6455,11 @@
       <c r="AJ52">
         <v>0</v>
       </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -6401,16 +6557,19 @@
         <v>321.25797148062389</v>
       </c>
       <c r="AG53">
-        <v>313.14271156624403</v>
+        <v>313.01245100410313</v>
       </c>
       <c r="AH53">
-        <v>376.63650317307759</v>
+        <v>376.51411949278383</v>
       </c>
       <c r="AI53">
-        <v>343.20834047953008</v>
+        <v>342.56006833799518</v>
       </c>
       <c r="AJ53">
-        <v>360.9</v>
+        <v>360.74787935556895</v>
+      </c>
+      <c r="AK53">
+        <v>358.18426966330782</v>
       </c>
     </row>
   </sheetData>
@@ -6420,10 +6579,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF8D813B-F6D2-4258-9AD6-288120984E5F}">
-  <dimension ref="A1:AK53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AL53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6535,8 +6694,11 @@
       <c r="AK1">
         <v>2022</v>
       </c>
+      <c r="AL1">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -6550,106 +6712,109 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>20081.5</v>
+        <v>20081.510967123289</v>
       </c>
       <c r="F2">
-        <v>21441.9</v>
+        <v>21441.924243026908</v>
       </c>
       <c r="G2">
-        <v>22163.4</v>
+        <v>22163.435329959819</v>
       </c>
       <c r="H2">
-        <v>22660.9</v>
+        <v>22660.929770771178</v>
       </c>
       <c r="I2">
-        <v>24571.9</v>
+        <v>24571.870788463188</v>
       </c>
       <c r="J2">
-        <v>25823</v>
+        <v>25823.00412185524</v>
       </c>
       <c r="K2">
-        <v>26806.7</v>
+        <v>26806.734848296048</v>
       </c>
       <c r="L2">
-        <v>28051.5</v>
+        <v>28051.513545313192</v>
       </c>
       <c r="M2">
-        <v>28442</v>
+        <v>28442.013996194473</v>
       </c>
       <c r="N2">
-        <v>29977.8</v>
+        <v>29977.754071135205</v>
       </c>
       <c r="O2">
-        <v>29543.5</v>
+        <v>29543.453389475217</v>
       </c>
       <c r="P2">
-        <v>26257.3</v>
+        <v>26257.266886560712</v>
       </c>
       <c r="Q2">
-        <v>27243.3</v>
+        <v>27243.321647998069</v>
       </c>
       <c r="R2">
-        <v>27062.9</v>
+        <v>27062.912036967511</v>
       </c>
       <c r="S2">
-        <v>29520.2</v>
+        <v>29520.173985123158</v>
       </c>
       <c r="T2">
-        <v>26888.3</v>
+        <v>26888.274996011463</v>
       </c>
       <c r="U2">
-        <v>27329.3</v>
+        <v>27329.255412930583</v>
       </c>
       <c r="V2">
-        <v>27751.8</v>
+        <v>27751.828429421417</v>
       </c>
       <c r="W2">
-        <v>24445</v>
+        <v>24445.037506993343</v>
       </c>
       <c r="X2">
-        <v>23487.599999999999</v>
+        <v>23487.559240366307</v>
       </c>
       <c r="Y2">
-        <v>26969</v>
+        <v>26969.020714679322</v>
       </c>
       <c r="Z2">
-        <v>26056.7</v>
+        <v>26056.67613188428</v>
       </c>
       <c r="AA2">
-        <v>26099.4</v>
+        <v>26099.358996035506</v>
       </c>
       <c r="AB2">
-        <v>25895.200000000001</v>
+        <v>25895.151258395832</v>
       </c>
       <c r="AC2">
-        <v>25639.9</v>
+        <v>25639.898159452008</v>
       </c>
       <c r="AD2">
-        <v>27193.3</v>
+        <v>27193.292000000001</v>
       </c>
       <c r="AE2">
-        <v>26786.799999999999</v>
+        <v>26786.813200000001</v>
       </c>
       <c r="AF2">
-        <v>27337.200000000001</v>
+        <v>27337.241599999998</v>
       </c>
       <c r="AG2">
-        <v>27206.3</v>
+        <v>27206.300000000003</v>
       </c>
       <c r="AH2">
-        <v>28488</v>
+        <v>28487.989599999997</v>
       </c>
       <c r="AI2">
-        <v>27930.3</v>
+        <v>27930.283999999996</v>
       </c>
       <c r="AJ2">
-        <v>30660.3</v>
+        <v>30660.284</v>
       </c>
       <c r="AK2">
-        <v>28792.799999999999</v>
+        <v>28792.787999999997</v>
+      </c>
+      <c r="AL2">
+        <v>30545.392800000001</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -6761,8 +6926,11 @@
       <c r="AK3">
         <v>0</v>
       </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -6776,106 +6944,109 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>57.5</v>
+        <v>57.505626460502846</v>
       </c>
       <c r="F4">
-        <v>64.900000000000006</v>
+        <v>64.899236504681014</v>
       </c>
       <c r="G4">
-        <v>65.599999999999994</v>
+        <v>65.645133775317802</v>
       </c>
       <c r="H4">
-        <v>68.900000000000006</v>
+        <v>68.885393528673063</v>
       </c>
       <c r="I4">
-        <v>72.5</v>
+        <v>72.513240398595229</v>
       </c>
       <c r="J4">
-        <v>83.5</v>
+        <v>83.458910404922932</v>
       </c>
       <c r="K4">
-        <v>93.3</v>
+        <v>93.256999116654768</v>
       </c>
       <c r="L4">
-        <v>97.8</v>
+        <v>97.833056209699649</v>
       </c>
       <c r="M4">
-        <v>113.1</v>
+        <v>113.06463082618635</v>
       </c>
       <c r="N4">
-        <v>214</v>
+        <v>213.95155267603457</v>
       </c>
       <c r="O4">
-        <v>206.4</v>
+        <v>206.40908274525137</v>
       </c>
       <c r="P4">
-        <v>191.5</v>
+        <v>191.49652880510232</v>
       </c>
       <c r="Q4">
-        <v>202.6</v>
+        <v>202.59368146866231</v>
       </c>
       <c r="R4">
-        <v>196.9</v>
+        <v>196.92479088788284</v>
       </c>
       <c r="S4">
-        <v>209.9</v>
+        <v>209.93729528097995</v>
       </c>
       <c r="T4">
-        <v>203.3</v>
+        <v>203.30593948161535</v>
       </c>
       <c r="U4">
-        <v>187.1</v>
+        <v>187.06790510596539</v>
       </c>
       <c r="V4">
-        <v>196.8</v>
+        <v>196.80672028577268</v>
       </c>
       <c r="W4">
-        <v>177.5</v>
+        <v>177.46402063998056</v>
       </c>
       <c r="X4">
-        <v>144.4</v>
+        <v>144.42746848041827</v>
       </c>
       <c r="Y4">
-        <v>179.1</v>
+        <v>179.08713692946057</v>
       </c>
       <c r="Z4">
-        <v>186.6</v>
+        <v>186.61037394451145</v>
       </c>
       <c r="AA4">
-        <v>188.3</v>
+        <v>188.25693606755127</v>
       </c>
       <c r="AB4">
-        <v>175.1</v>
+        <v>175.08443908323281</v>
       </c>
       <c r="AC4">
-        <v>179.5</v>
+        <v>179.47527141133898</v>
       </c>
       <c r="AD4">
-        <v>178.9</v>
+        <v>178.92641737032571</v>
       </c>
       <c r="AE4">
-        <v>173.4</v>
+        <v>173.43787696019299</v>
       </c>
       <c r="AF4">
-        <v>181.7</v>
+        <v>181.67068757539204</v>
       </c>
       <c r="AG4">
-        <v>188.8</v>
+        <v>188.80579010856454</v>
       </c>
       <c r="AH4">
-        <v>181.1</v>
+        <v>181.12183353437879</v>
       </c>
       <c r="AI4">
-        <v>143.30000000000001</v>
+        <v>143.25090470446321</v>
       </c>
       <c r="AJ4">
-        <v>164.7</v>
+        <v>164.65621230398068</v>
       </c>
       <c r="AK4">
-        <v>167.9</v>
+        <v>167.94933655006031</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -6889,40 +7060,40 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>115</v>
+        <v>115.01125292100569</v>
       </c>
       <c r="F5">
-        <v>119</v>
+        <v>118.98193359191518</v>
       </c>
       <c r="G5">
-        <v>120.3</v>
+        <v>120.34941192141601</v>
       </c>
       <c r="H5">
-        <v>126.3</v>
+        <v>126.28988813590064</v>
       </c>
       <c r="I5">
-        <v>145</v>
+        <v>145.02648079719046</v>
       </c>
       <c r="J5">
-        <v>146.1</v>
+        <v>146.05309320861511</v>
       </c>
       <c r="K5">
-        <v>145.69999999999999</v>
+        <v>145.71406111977308</v>
       </c>
       <c r="L5">
-        <v>152.9</v>
+        <v>152.86415032765572</v>
       </c>
       <c r="M5">
-        <v>141.30000000000001</v>
+        <v>141.33078853273292</v>
       </c>
       <c r="N5">
-        <v>139.1</v>
+        <v>139.06850923942244</v>
       </c>
       <c r="O5">
-        <v>134.19999999999999</v>
+        <v>134.16590378441339</v>
       </c>
       <c r="P5">
-        <v>124.5</v>
+        <v>124.4727437233165</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -6987,8 +7158,11 @@
       <c r="AK5">
         <v>0</v>
       </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -7100,8 +7274,11 @@
       <c r="AK6">
         <v>0</v>
       </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -7213,8 +7390,11 @@
       <c r="AK7">
         <v>0</v>
       </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -7237,22 +7417,22 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>19</v>
+        <v>18.980784413031678</v>
       </c>
       <c r="I8">
-        <v>19.5</v>
+        <v>19.538456987601339</v>
       </c>
       <c r="J8">
-        <v>16.399999999999999</v>
+        <v>16.392167617617226</v>
       </c>
       <c r="K8">
-        <v>15.5</v>
+        <v>15.547623219921062</v>
       </c>
       <c r="L8">
-        <v>16.5</v>
+        <v>16.516818318611254</v>
       </c>
       <c r="M8">
-        <v>15.8</v>
+        <v>15.793519143286462</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -7326,8 +7506,11 @@
       <c r="AK8">
         <v>0</v>
       </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -7439,8 +7622,11 @@
       <c r="AK9">
         <v>0</v>
       </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -7552,8 +7738,11 @@
       <c r="AK10">
         <v>0</v>
       </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -7567,64 +7756,64 @@
         <v>5</v>
       </c>
       <c r="E11">
-        <v>98.4</v>
+        <v>98.437182422539877</v>
       </c>
       <c r="F11">
-        <v>99</v>
+        <v>98.991271217420461</v>
       </c>
       <c r="G11">
-        <v>127.1</v>
+        <v>127.0880693299991</v>
       </c>
       <c r="H11">
-        <v>176.9</v>
+        <v>176.93384365554471</v>
       </c>
       <c r="I11">
-        <v>184.7</v>
+        <v>184.65476946913586</v>
       </c>
       <c r="J11">
-        <v>173.2</v>
+        <v>173.19519647087952</v>
       </c>
       <c r="K11">
-        <v>170.4</v>
+        <v>170.41091349287899</v>
       </c>
       <c r="L11">
-        <v>110.2</v>
+        <v>110.1721650166364</v>
       </c>
       <c r="M11">
-        <v>153.5</v>
+        <v>153.54254693163631</v>
       </c>
       <c r="N11">
-        <v>165.9</v>
+        <v>165.90559666177822</v>
       </c>
       <c r="O11">
-        <v>159.19999999999999</v>
+        <v>159.15080292927874</v>
       </c>
       <c r="P11">
-        <v>139.6</v>
+        <v>139.64003266254633</v>
       </c>
       <c r="Q11">
-        <v>143.80000000000001</v>
+        <v>143.84300061933004</v>
       </c>
       <c r="R11">
-        <v>145.19999999999999</v>
+        <v>145.24038657214632</v>
       </c>
       <c r="S11">
-        <v>85</v>
+        <v>84.98892978903605</v>
       </c>
       <c r="T11">
-        <v>114.3</v>
+        <v>114.33425891804771</v>
       </c>
       <c r="U11">
-        <v>96.4</v>
+        <v>96.521026019618333</v>
       </c>
       <c r="V11">
-        <v>157.6</v>
+        <v>157.64318025234624</v>
       </c>
       <c r="W11">
-        <v>140</v>
+        <v>139.96649717111657</v>
       </c>
       <c r="X11">
-        <v>46.6</v>
+        <v>46.566608670126747</v>
       </c>
       <c r="Y11">
         <v>0</v>
@@ -7665,8 +7854,11 @@
       <c r="AK11">
         <v>0</v>
       </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -7778,8 +7970,11 @@
       <c r="AK12">
         <v>0</v>
       </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -7891,8 +8086,11 @@
       <c r="AK13">
         <v>0</v>
       </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -8004,8 +8202,11 @@
       <c r="AK14">
         <v>0</v>
       </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -8019,106 +8220,109 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>306.5</v>
+        <v>306.46270699602383</v>
       </c>
       <c r="F15">
-        <v>345.1</v>
+        <v>345.11939455714787</v>
       </c>
       <c r="G15">
-        <v>334.2</v>
+        <v>334.16803836831969</v>
       </c>
       <c r="H15">
-        <v>291.7</v>
+        <v>291.74288488500565</v>
       </c>
       <c r="I15">
-        <v>299.89999999999998</v>
+        <v>299.89941833729665</v>
       </c>
       <c r="J15">
-        <v>312.7</v>
+        <v>312.70902324482716</v>
       </c>
       <c r="K15">
-        <v>323.5</v>
+        <v>323.52468630953462</v>
       </c>
       <c r="L15">
-        <v>333.1</v>
+        <v>333.05612478951639</v>
       </c>
       <c r="M15">
-        <v>336.1</v>
+        <v>336.08115047092718</v>
       </c>
       <c r="N15">
-        <v>357.8</v>
+        <v>357.80994087077909</v>
       </c>
       <c r="O15">
-        <v>350.7</v>
+        <v>350.73038503839433</v>
       </c>
       <c r="P15">
-        <v>314.39999999999998</v>
+        <v>314.41755142057031</v>
       </c>
       <c r="Q15">
-        <v>310.8</v>
+        <v>310.76662559175185</v>
       </c>
       <c r="R15">
-        <v>306.7</v>
+        <v>306.70527269288829</v>
       </c>
       <c r="S15">
-        <v>353.6</v>
+        <v>353.55394792238997</v>
       </c>
       <c r="T15">
-        <v>326.10000000000002</v>
+        <v>326.14254414390803</v>
       </c>
       <c r="U15">
-        <v>334.7</v>
+        <v>334.98473736220484</v>
       </c>
       <c r="V15">
-        <v>333.5</v>
+        <v>333.50290577829691</v>
       </c>
       <c r="W15">
-        <v>296.10000000000002</v>
+        <v>296.1069006820066</v>
       </c>
       <c r="X15">
-        <v>298.5</v>
+        <v>298.52802325899438</v>
       </c>
       <c r="Y15">
-        <v>346.5</v>
+        <v>346.51988636363637</v>
       </c>
       <c r="Z15">
-        <v>331.5</v>
+        <v>331.45983586172599</v>
       </c>
       <c r="AA15">
-        <v>328.2</v>
+        <v>328.22918888178009</v>
       </c>
       <c r="AB15">
-        <v>330.1</v>
+        <v>330.07361046904441</v>
       </c>
       <c r="AC15">
-        <v>320.2</v>
+        <v>320.16600776372519</v>
       </c>
       <c r="AD15">
-        <v>336.6</v>
+        <v>336.57918806726229</v>
       </c>
       <c r="AE15">
-        <v>328.2</v>
+        <v>328.20657144867374</v>
       </c>
       <c r="AF15">
-        <v>326.10000000000002</v>
+        <v>326.06089666746584</v>
       </c>
       <c r="AG15">
-        <v>299.5</v>
+        <v>299.4972918626147</v>
       </c>
       <c r="AH15">
-        <v>295.60000000000002</v>
+        <v>295.61669316852181</v>
       </c>
       <c r="AI15">
-        <v>264.89999999999998</v>
+        <v>264.2954856361149</v>
       </c>
       <c r="AJ15">
-        <v>291.8</v>
+        <v>291.10807113543086</v>
       </c>
       <c r="AK15">
-        <v>247.9</v>
+        <v>247.37516005121637</v>
+      </c>
+      <c r="AL15">
+        <v>258.71431663500158</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -8230,8 +8434,11 @@
       <c r="AK16">
         <v>0</v>
       </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -8245,106 +8452,109 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>482.4</v>
+        <v>482.37702971986857</v>
       </c>
       <c r="F17">
-        <v>496.9</v>
+        <v>496.85734575897715</v>
       </c>
       <c r="G17">
-        <v>399.1</v>
+        <v>399.12062742557288</v>
       </c>
       <c r="H17">
-        <v>364.4</v>
+        <v>364.41887662960994</v>
       </c>
       <c r="I17">
-        <v>332.5</v>
+        <v>332.45821973048925</v>
       </c>
       <c r="J17">
-        <v>345.9</v>
+        <v>345.88444024918999</v>
       </c>
       <c r="K17">
-        <v>357.1</v>
+        <v>357.06842801023254</v>
       </c>
       <c r="L17">
-        <v>366.8</v>
+        <v>366.80751028443871</v>
       </c>
       <c r="M17">
-        <v>369.4</v>
+        <v>369.37220782889642</v>
       </c>
       <c r="N17">
-        <v>392.5</v>
+        <v>392.45820330146904</v>
       </c>
       <c r="O17">
-        <v>383.9</v>
+        <v>383.93372112199233</v>
       </c>
       <c r="P17">
-        <v>343.5</v>
+        <v>343.51972042683002</v>
       </c>
       <c r="Q17">
-        <v>338.9</v>
+        <v>338.89156213724186</v>
       </c>
       <c r="R17">
-        <v>333.8</v>
+        <v>333.84733222323251</v>
       </c>
       <c r="S17">
-        <v>384.1</v>
+        <v>384.14996264644293</v>
       </c>
       <c r="T17">
-        <v>354.4</v>
+        <v>354.36641815636165</v>
       </c>
       <c r="U17">
-        <v>363.8</v>
+        <v>364.08298785341327</v>
       </c>
       <c r="V17">
-        <v>385.3</v>
+        <v>385.34999617240186</v>
       </c>
       <c r="W17">
-        <v>342.1</v>
+        <v>342.14032641828504</v>
       </c>
       <c r="X17">
-        <v>344.9</v>
+        <v>344.93784200093893</v>
       </c>
       <c r="Y17">
-        <v>400.4</v>
+        <v>400.390625</v>
       </c>
       <c r="Z17">
-        <v>383</v>
+        <v>382.98930614275054</v>
       </c>
       <c r="AA17">
-        <v>379.3</v>
+        <v>379.25641572474581</v>
       </c>
       <c r="AB17">
-        <v>381.4</v>
+        <v>381.38757512179518</v>
       </c>
       <c r="AC17">
-        <v>369.9</v>
+        <v>369.93971485304377</v>
       </c>
       <c r="AD17">
-        <v>388.9</v>
+        <v>388.90452402729898</v>
       </c>
       <c r="AE17">
-        <v>379.2</v>
+        <v>379.23028213607262</v>
       </c>
       <c r="AF17">
-        <v>376.8</v>
+        <v>376.75103606534918</v>
       </c>
       <c r="AG17">
-        <v>346.1</v>
+        <v>346.05779521940775</v>
       </c>
       <c r="AH17">
-        <v>341.6</v>
+        <v>341.57391017371214</v>
       </c>
       <c r="AI17">
-        <v>306.10000000000002</v>
+        <v>305.38343928542685</v>
       </c>
       <c r="AJ17">
-        <v>337.2</v>
+        <v>336.36436790858613</v>
       </c>
       <c r="AK17">
-        <v>286.5</v>
+        <v>285.83264291632145</v>
+      </c>
+      <c r="AL17">
+        <v>298.93460955724976</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -8456,8 +8666,11 @@
       <c r="AK18">
         <v>0</v>
       </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -8471,106 +8684,109 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>83.6</v>
+        <v>83.644547578913219</v>
       </c>
       <c r="F19">
-        <v>86.5</v>
+        <v>86.53231533957468</v>
       </c>
       <c r="G19">
-        <v>87.5</v>
+        <v>87.526845033757098</v>
       </c>
       <c r="H19">
-        <v>91.8</v>
+        <v>91.84719137156408</v>
       </c>
       <c r="I19">
-        <v>102.7</v>
+        <v>102.72709056467656</v>
       </c>
       <c r="J19">
-        <v>98.4</v>
+        <v>98.362287262944889</v>
       </c>
       <c r="K19">
-        <v>93.3</v>
+        <v>93.256999116654768</v>
       </c>
       <c r="L19">
-        <v>97.8</v>
+        <v>97.833056209699649</v>
       </c>
       <c r="M19">
-        <v>130</v>
+        <v>130.0243254501143</v>
       </c>
       <c r="N19">
-        <v>123</v>
+        <v>123.02214278871986</v>
       </c>
       <c r="O19">
-        <v>118.7</v>
+        <v>118.68522257851953</v>
       </c>
       <c r="P19">
-        <v>110.1</v>
+        <v>110.1105040629338</v>
       </c>
       <c r="Q19">
-        <v>116.5</v>
+        <v>116.49136684448084</v>
       </c>
       <c r="R19">
-        <v>113.2</v>
+        <v>113.23175476053262</v>
       </c>
       <c r="S19">
-        <v>120.7</v>
+        <v>120.71394478656346</v>
       </c>
       <c r="T19">
-        <v>116.9</v>
+        <v>116.90091520192881</v>
       </c>
       <c r="U19">
-        <v>106.9</v>
+        <v>106.89594577483739</v>
       </c>
       <c r="V19">
-        <v>112.5</v>
+        <v>112.46098302044153</v>
       </c>
       <c r="W19">
-        <v>101.4</v>
+        <v>101.40801179427459</v>
       </c>
       <c r="X19">
-        <v>82.5</v>
+        <v>82.52998198881042</v>
       </c>
       <c r="Y19">
-        <v>102.3</v>
+        <v>102.33550681683462</v>
       </c>
       <c r="Z19">
-        <v>106.6</v>
+        <v>106.63449939686369</v>
       </c>
       <c r="AA19">
-        <v>107.6</v>
+        <v>107.57539203860073</v>
       </c>
       <c r="AB19">
-        <v>100</v>
+        <v>100.04825090470446</v>
       </c>
       <c r="AC19">
-        <v>102.6</v>
+        <v>102.55729794933654</v>
       </c>
       <c r="AD19">
-        <v>102.2</v>
+        <v>102.24366706875755</v>
       </c>
       <c r="AE19">
-        <v>99.1</v>
+        <v>99.107358262967438</v>
       </c>
       <c r="AF19">
-        <v>103.8</v>
+        <v>103.81182147165259</v>
       </c>
       <c r="AG19">
-        <v>107.9</v>
+        <v>107.88902291917974</v>
       </c>
       <c r="AH19">
-        <v>103.5</v>
+        <v>103.49819059107358</v>
       </c>
       <c r="AI19">
-        <v>81.900000000000006</v>
+        <v>81.857659831121836</v>
       </c>
       <c r="AJ19">
-        <v>94.1</v>
+        <v>94.089264173703256</v>
       </c>
       <c r="AK19">
-        <v>96</v>
+        <v>95.971049457177315</v>
+      </c>
+      <c r="AL19">
+        <v>84.620293554562863</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -8584,106 +8800,109 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>180.2</v>
+        <v>180.23698157614504</v>
       </c>
       <c r="F20">
-        <v>182.8</v>
+        <v>182.84199228273334</v>
       </c>
       <c r="G20">
-        <v>180.6</v>
+        <v>180.56110046245647</v>
       </c>
       <c r="H20">
-        <v>151.19999999999999</v>
+        <v>151.16080473198321</v>
       </c>
       <c r="I20">
-        <v>191.5</v>
+        <v>191.45875617349239</v>
       </c>
       <c r="J20">
-        <v>193.9</v>
+        <v>193.94780484937797</v>
       </c>
       <c r="K20">
-        <v>199.7</v>
+        <v>199.69350113070638</v>
       </c>
       <c r="L20">
-        <v>207.9</v>
+        <v>207.86237752262747</v>
       </c>
       <c r="M20">
-        <v>208.4</v>
+        <v>208.40150915540096</v>
       </c>
       <c r="N20">
-        <v>215.8</v>
+        <v>215.82637185580074</v>
       </c>
       <c r="O20">
-        <v>209.8</v>
+        <v>209.80445992896469</v>
       </c>
       <c r="P20">
-        <v>138.1</v>
+        <v>138.13206095484819</v>
       </c>
       <c r="Q20">
-        <v>136.69999999999999</v>
+        <v>136.69401336655926</v>
       </c>
       <c r="R20">
-        <v>136.69999999999999</v>
+        <v>136.67968726929357</v>
       </c>
       <c r="S20">
-        <v>148.80000000000001</v>
+        <v>148.80611367680095</v>
       </c>
       <c r="T20">
-        <v>160.9</v>
+        <v>160.94544899405651</v>
       </c>
       <c r="U20">
-        <v>161.9</v>
+        <v>163.71810663044948</v>
       </c>
       <c r="V20">
-        <v>153.6</v>
+        <v>156.9901623792436</v>
       </c>
       <c r="W20">
-        <v>138.19999999999999</v>
+        <v>142.99503361198344</v>
       </c>
       <c r="X20">
-        <v>144.4</v>
+        <v>144.41689002976776</v>
       </c>
       <c r="Y20">
-        <v>165.2</v>
+        <v>165.2482965102395</v>
       </c>
       <c r="Z20">
-        <v>162.19999999999999</v>
+        <v>162.19767479177264</v>
       </c>
       <c r="AA20">
-        <v>161.4</v>
+        <v>161.40876621172669</v>
       </c>
       <c r="AB20">
-        <v>164.3</v>
+        <v>164.31090042288329</v>
       </c>
       <c r="AC20">
-        <v>198.3</v>
+        <v>198.30202716665642</v>
       </c>
       <c r="AD20">
-        <v>224.8</v>
+        <v>224.7976256874297</v>
       </c>
       <c r="AE20">
-        <v>222.5</v>
+        <v>222.54540278456605</v>
       </c>
       <c r="AF20">
-        <v>219.3</v>
+        <v>219.27163562737982</v>
       </c>
       <c r="AG20">
-        <v>204.9</v>
+        <v>204.89879774781835</v>
       </c>
       <c r="AH20">
-        <v>206.1</v>
+        <v>206.1393840847947</v>
       </c>
       <c r="AI20">
-        <v>185</v>
+        <v>184.65535972519288</v>
       </c>
       <c r="AJ20">
-        <v>196.4</v>
+        <v>195.99959680365504</v>
       </c>
       <c r="AK20">
-        <v>172.2</v>
+        <v>171.88813148741053</v>
+      </c>
+      <c r="AL20">
+        <v>180.43985748057531</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -8697,106 +8916,109 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>5647.1</v>
+        <v>5647.0777869967123</v>
       </c>
       <c r="F21">
-        <v>5976.8</v>
+        <v>5976.7528793024176</v>
       </c>
       <c r="G21">
-        <v>6271.8</v>
+        <v>6271.7830802260341</v>
       </c>
       <c r="H21">
-        <v>6437.6</v>
+        <v>6437.5934917470104</v>
       </c>
       <c r="I21">
-        <v>6774.8</v>
+        <v>6774.8452064701432</v>
       </c>
       <c r="J21">
-        <v>7188.4</v>
+        <v>7188.4289227419276</v>
       </c>
       <c r="K21">
-        <v>7487.6</v>
+        <v>7487.6248559782234</v>
       </c>
       <c r="L21">
-        <v>7944.7</v>
+        <v>7944.6953029301349</v>
       </c>
       <c r="M21">
-        <v>8015.7</v>
+        <v>8015.7413808595038</v>
       </c>
       <c r="N21">
-        <v>8224.7000000000007</v>
+        <v>8224.7257095456443</v>
       </c>
       <c r="O21">
-        <v>8022.4</v>
+        <v>8022.3629077021542</v>
       </c>
       <c r="P21">
-        <v>6961.1</v>
+        <v>6961.0788299085898</v>
       </c>
       <c r="Q21">
-        <v>7014.3</v>
+        <v>7014.3149221560534</v>
       </c>
       <c r="R21">
-        <v>7003</v>
+        <v>7002.9901446705753</v>
       </c>
       <c r="S21">
-        <v>7953.1</v>
+        <v>7953.1462590114152</v>
       </c>
       <c r="T21">
-        <v>7376.3</v>
+        <v>7376.2715730740438</v>
       </c>
       <c r="U21">
-        <v>7347.7</v>
+        <v>7383.3925069933011</v>
       </c>
       <c r="V21">
-        <v>7477.7</v>
+        <v>7506.67907905639</v>
       </c>
       <c r="W21">
-        <v>6678.3</v>
+        <v>6700.9410300235195</v>
       </c>
       <c r="X21">
-        <v>6343.5</v>
+        <v>6363.9925383069294</v>
       </c>
       <c r="Y21">
-        <v>7519.9</v>
+        <v>7519.9193014217235</v>
       </c>
       <c r="Z21">
-        <v>7364.5</v>
+        <v>7364.4859707753803</v>
       </c>
       <c r="AA21">
-        <v>7319.7</v>
+        <v>7319.6994928423519</v>
       </c>
       <c r="AB21">
-        <v>7231.5</v>
+        <v>7231.5331742332583</v>
       </c>
       <c r="AC21">
-        <v>7282.8</v>
+        <v>7282.7593801097482</v>
       </c>
       <c r="AD21">
-        <v>7800.4</v>
+        <v>7800.4316666138238</v>
       </c>
       <c r="AE21">
-        <v>7789.8</v>
+        <v>7789.8304878189556</v>
       </c>
       <c r="AF21">
-        <v>7828.2</v>
+        <v>7828.1557340758345</v>
       </c>
       <c r="AG21">
-        <v>7497.1</v>
+        <v>7497.1181245908529</v>
       </c>
       <c r="AH21">
-        <v>8114.8</v>
+        <v>8114.7926928299057</v>
       </c>
       <c r="AI21">
-        <v>8690.7000000000007</v>
+        <v>8676.1869834645186</v>
       </c>
       <c r="AJ21">
-        <v>9657.6</v>
+        <v>9646.2615890403995</v>
       </c>
       <c r="AK21">
-        <v>8801.6</v>
+        <v>8801.6697088959663</v>
+      </c>
+      <c r="AL21">
+        <v>8959.3282780872469</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -8908,8 +9130,11 @@
       <c r="AK22">
         <v>0</v>
       </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -9021,8 +9246,11 @@
       <c r="AK23">
         <v>0</v>
       </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -9134,8 +9362,11 @@
       <c r="AK24">
         <v>0</v>
       </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -9247,8 +9478,11 @@
       <c r="AK25">
         <v>0</v>
       </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -9360,8 +9594,11 @@
       <c r="AK26">
         <v>0</v>
       </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -9473,8 +9710,11 @@
       <c r="AK27">
         <v>0</v>
       </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -9586,8 +9826,11 @@
       <c r="AK28">
         <v>0</v>
       </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -9699,8 +9942,11 @@
       <c r="AK29">
         <v>0</v>
       </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -9812,8 +10058,11 @@
       <c r="AK30">
         <v>0</v>
       </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -9925,8 +10174,11 @@
       <c r="AK31">
         <v>0</v>
       </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -10038,8 +10290,11 @@
       <c r="AK32">
         <v>0</v>
       </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -10151,8 +10406,11 @@
       <c r="AK33">
         <v>0</v>
       </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -10264,8 +10522,11 @@
       <c r="AK34">
         <v>0</v>
       </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -10377,8 +10638,11 @@
       <c r="AK35">
         <v>0</v>
       </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -10490,8 +10754,11 @@
       <c r="AK36">
         <v>0</v>
       </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -10603,8 +10870,11 @@
       <c r="AK37">
         <v>0</v>
       </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -10618,106 +10888,109 @@
         <v>5</v>
       </c>
       <c r="E38">
-        <v>278.7</v>
+        <v>278.73791320308061</v>
       </c>
       <c r="F38">
-        <v>290.8</v>
+        <v>290.75581609292993</v>
       </c>
       <c r="G38">
-        <v>313.60000000000002</v>
+        <v>313.56386149319928</v>
       </c>
       <c r="H38">
-        <v>303</v>
+        <v>302.99755956472166</v>
       </c>
       <c r="I38">
-        <v>331.5</v>
+        <v>331.50537732843475</v>
       </c>
       <c r="J38">
-        <v>330.9</v>
+        <v>330.92791457039959</v>
       </c>
       <c r="K38">
-        <v>323.60000000000002</v>
+        <v>323.63715150517078</v>
       </c>
       <c r="L38">
-        <v>318.39999999999998</v>
+        <v>318.36462008250862</v>
       </c>
       <c r="M38">
-        <v>364.7</v>
+        <v>364.72800341301581</v>
       </c>
       <c r="N38">
-        <v>353.5</v>
+        <v>353.46362260990304</v>
       </c>
       <c r="O38">
-        <v>361.3</v>
+        <v>361.32810217263329</v>
       </c>
       <c r="P38">
-        <v>325.3</v>
+        <v>325.3385430396994</v>
       </c>
       <c r="Q38">
-        <v>330</v>
+        <v>330.0421818645367</v>
       </c>
       <c r="R38">
-        <v>338.1</v>
+        <v>338.1343667137611</v>
       </c>
       <c r="S38">
-        <v>354.8</v>
+        <v>354.80253163064333</v>
       </c>
       <c r="T38">
-        <v>349.8</v>
+        <v>349.83221031679051</v>
       </c>
       <c r="U38">
-        <v>343.5</v>
+        <v>343.53228136197595</v>
       </c>
       <c r="V38">
-        <v>357.3</v>
+        <v>357.30734352236897</v>
       </c>
       <c r="W38">
-        <v>307</v>
+        <v>307.02474874498887</v>
       </c>
       <c r="X38">
-        <v>258.8</v>
+        <v>258.79464250623823</v>
       </c>
       <c r="Y38">
-        <v>324.89999999999998</v>
+        <v>324.90687751525843</v>
       </c>
       <c r="Z38">
-        <v>310.10000000000002</v>
+        <v>310.05345072516621</v>
       </c>
       <c r="AA38">
-        <v>333.1</v>
+        <v>333.12465654893822</v>
       </c>
       <c r="AB38">
-        <v>292.8</v>
+        <v>292.78536377405317</v>
       </c>
       <c r="AC38">
-        <v>299.3</v>
+        <v>299.27879248488301</v>
       </c>
       <c r="AD38">
-        <v>293.3</v>
+        <v>293.28136437526257</v>
       </c>
       <c r="AE38">
-        <v>276.60000000000002</v>
+        <v>276.62334398193286</v>
       </c>
       <c r="AF38">
-        <v>294.60000000000002</v>
+        <v>294.59436051441941</v>
       </c>
       <c r="AG38">
-        <v>326.8</v>
+        <v>326.80431252095559</v>
       </c>
       <c r="AH38">
-        <v>288</v>
+        <v>287.98684422588514</v>
       </c>
       <c r="AI38">
-        <v>241.2</v>
+        <v>241.22988271331684</v>
       </c>
       <c r="AJ38">
-        <v>271</v>
+        <v>270.96201128860059</v>
       </c>
       <c r="AK38">
-        <v>286.8</v>
+        <v>286.63236516437831</v>
+      </c>
+      <c r="AL38">
+        <v>283.95819953333478</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -10731,106 +11004,109 @@
         <v>5</v>
       </c>
       <c r="E39">
-        <v>151.6</v>
+        <v>151.60574248678026</v>
       </c>
       <c r="F39">
-        <v>156.80000000000001</v>
+        <v>156.83982155297912</v>
       </c>
       <c r="G39">
-        <v>273.5</v>
+        <v>273.52139073049085</v>
       </c>
       <c r="H39">
-        <v>292.8</v>
+        <v>292.76292249686048</v>
       </c>
       <c r="I39">
-        <v>308.2</v>
+        <v>308.1812716940297</v>
       </c>
       <c r="J39">
-        <v>336.2</v>
+        <v>336.21770683504411</v>
       </c>
       <c r="K39">
-        <v>333.8</v>
+        <v>333.79000672579258</v>
       </c>
       <c r="L39">
-        <v>350.5</v>
+        <v>350.49890800440807</v>
       </c>
       <c r="M39">
-        <v>341.9</v>
+        <v>341.85059694258013</v>
       </c>
       <c r="N39">
-        <v>336.6</v>
+        <v>336.60765580386914</v>
       </c>
       <c r="O39">
-        <v>324.10000000000002</v>
+        <v>324.1311959050966</v>
       </c>
       <c r="P39">
-        <v>299</v>
+        <v>299.0329363823995</v>
       </c>
       <c r="Q39">
-        <v>316.5</v>
+        <v>316.46558974921732</v>
       </c>
       <c r="R39">
-        <v>308.10000000000002</v>
+        <v>308.09960616562046</v>
       </c>
       <c r="S39">
-        <v>328.4</v>
+        <v>328.44569484519417</v>
       </c>
       <c r="T39">
-        <v>310.2</v>
+        <v>310.20073138874898</v>
       </c>
       <c r="U39">
-        <v>290.3</v>
+        <v>290.25396943615476</v>
       </c>
       <c r="V39">
-        <v>305.89999999999998</v>
+        <v>305.91033293134632</v>
       </c>
       <c r="W39">
-        <v>276.60000000000002</v>
+        <v>276.6396716766817</v>
       </c>
       <c r="X39">
-        <v>230.8</v>
+        <v>230.81715819494835</v>
       </c>
       <c r="Y39">
-        <v>253.9</v>
+        <v>253.87077652637819</v>
       </c>
       <c r="Z39">
-        <v>264.5</v>
+        <v>264.53558504221957</v>
       </c>
       <c r="AA39">
-        <v>266.89999999999998</v>
+        <v>266.86972255729796</v>
       </c>
       <c r="AB39">
-        <v>248.2</v>
+        <v>248.19662243667071</v>
       </c>
       <c r="AC39">
-        <v>254.4</v>
+        <v>254.42098914354645</v>
       </c>
       <c r="AD39">
-        <v>253.6</v>
+        <v>253.64294330518695</v>
       </c>
       <c r="AE39">
-        <v>245.9</v>
+        <v>245.86248492159228</v>
       </c>
       <c r="AF39">
-        <v>257.5</v>
+        <v>257.53317249698432</v>
       </c>
       <c r="AG39">
-        <v>267.60000000000002</v>
+        <v>267.64776839565741</v>
       </c>
       <c r="AH39">
-        <v>256.8</v>
+        <v>256.75512665862487</v>
       </c>
       <c r="AI39">
-        <v>203.1</v>
+        <v>203.06996381182145</v>
       </c>
       <c r="AJ39">
-        <v>233.4</v>
+        <v>233.41375150784077</v>
       </c>
       <c r="AK39">
-        <v>238.1</v>
+        <v>238.08202653799756</v>
+      </c>
+      <c r="AL39">
+        <v>209.92342054881942</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -10942,8 +11218,11 @@
       <c r="AK40">
         <v>0</v>
       </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -11053,10 +11332,13 @@
         <v>0</v>
       </c>
       <c r="AK41">
-        <v>130.19999999999999</v>
+        <v>129.92392859832793</v>
+      </c>
+      <c r="AL41">
+        <v>815.27620788340846</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -11168,8 +11450,11 @@
       <c r="AK42">
         <v>0</v>
       </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -11281,8 +11566,11 @@
       <c r="AK43">
         <v>0</v>
       </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -11394,8 +11682,11 @@
       <c r="AK44">
         <v>0</v>
       </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>60</v>
       </c>
@@ -11409,106 +11700,109 @@
         <v>5</v>
       </c>
       <c r="E45">
-        <v>42.1</v>
+        <v>42.108743507761503</v>
       </c>
       <c r="F45">
-        <v>44.4</v>
+        <v>44.354543161508786</v>
       </c>
       <c r="G45">
-        <v>36.1</v>
+        <v>36.140550221739559</v>
       </c>
       <c r="H45">
-        <v>41.8</v>
+        <v>41.757725708669696</v>
       </c>
       <c r="I45">
-        <v>43</v>
+        <v>42.984605372722953</v>
       </c>
       <c r="J45">
-        <v>36.1</v>
+        <v>36.062768758757898</v>
       </c>
       <c r="K45">
-        <v>34.200000000000003</v>
+        <v>34.204771083826337</v>
       </c>
       <c r="L45">
-        <v>36.299999999999997</v>
+        <v>36.337000300944752</v>
       </c>
       <c r="M45">
-        <v>34.700000000000003</v>
+        <v>34.745742115230215</v>
       </c>
       <c r="N45">
-        <v>51.8</v>
+        <v>51.77756099907927</v>
       </c>
       <c r="O45">
-        <v>48.9</v>
+        <v>48.884783789906557</v>
       </c>
       <c r="P45">
-        <v>42.4</v>
+        <v>42.411980707385837</v>
       </c>
       <c r="Q45">
-        <v>48.6</v>
+        <v>48.596788898653614</v>
       </c>
       <c r="R45">
-        <v>48.1</v>
+        <v>48.093113513178025</v>
       </c>
       <c r="S45">
-        <v>51.2</v>
+        <v>51.248835872145975</v>
       </c>
       <c r="T45">
-        <v>35.9</v>
+        <v>35.857093348032414</v>
       </c>
       <c r="U45">
-        <v>43.9</v>
+        <v>43.872143461933682</v>
       </c>
       <c r="V45">
-        <v>47.1</v>
+        <v>47.111026536304614</v>
       </c>
       <c r="W45">
-        <v>43.9</v>
+        <v>43.872143461933682</v>
       </c>
       <c r="X45">
-        <v>45.6</v>
+        <v>45.638806957045098</v>
       </c>
       <c r="Y45">
-        <v>52</v>
+        <v>52.019691674368602</v>
       </c>
       <c r="Z45">
-        <v>49.9</v>
+        <v>49.881896126106881</v>
       </c>
       <c r="AA45">
-        <v>36.799999999999997</v>
+        <v>36.761340466777618</v>
       </c>
       <c r="AB45">
-        <v>45.6</v>
+        <v>45.628397463789312</v>
       </c>
       <c r="AC45">
-        <v>51.4</v>
+        <v>51.350854652518436</v>
       </c>
       <c r="AD45">
-        <v>68.8</v>
+        <v>68.81866268818662</v>
       </c>
       <c r="AE45">
-        <v>55.5</v>
+        <v>55.521576622494052</v>
       </c>
       <c r="AF45">
-        <v>48.2</v>
+        <v>48.216106014271141</v>
       </c>
       <c r="AG45">
-        <v>43.4</v>
+        <v>43.392751915144373</v>
       </c>
       <c r="AH45">
-        <v>45.3</v>
+        <v>45.30437044745058</v>
       </c>
       <c r="AI45">
-        <v>45.4</v>
+        <v>45.436276416439775</v>
       </c>
       <c r="AJ45">
-        <v>43.9</v>
+        <v>43.735790355390698</v>
       </c>
       <c r="AK45">
-        <v>45.4</v>
+        <v>44.964969151939769</v>
+      </c>
+      <c r="AL45">
+        <v>47.887692146815851</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -11522,106 +11816,109 @@
         <v>5</v>
       </c>
       <c r="E46">
-        <v>12272.4</v>
+        <v>12272.360557596214</v>
       </c>
       <c r="F46">
-        <v>13200.4</v>
+        <v>13200.418814053985</v>
       </c>
       <c r="G46">
-        <v>13571</v>
+        <v>13571.037273948819</v>
       </c>
       <c r="H46">
-        <v>13862.5</v>
+        <v>13862.506026941004</v>
       </c>
       <c r="I46">
-        <v>15322.8</v>
+        <v>15322.763997547139</v>
       </c>
       <c r="J46">
-        <v>16100.2</v>
+        <v>16100.195400949357</v>
       </c>
       <c r="K46">
-        <v>16752.400000000001</v>
+        <v>16752.378890199481</v>
       </c>
       <c r="L46">
-        <v>17518.400000000001</v>
+        <v>17518.444249229564</v>
       </c>
       <c r="M46">
-        <v>17754.3</v>
+        <v>17754.30704285251</v>
       </c>
       <c r="N46">
-        <v>18934.599999999999</v>
+        <v>18934.607278649088</v>
       </c>
       <c r="O46">
-        <v>18772.3</v>
+        <v>18772.2505426059</v>
       </c>
       <c r="P46">
-        <v>16849.7</v>
+        <v>16849.719722570175</v>
       </c>
       <c r="Q46">
-        <v>17841.099999999999</v>
+        <v>17841.124948340756</v>
       </c>
       <c r="R46">
-        <v>17719.400000000001</v>
+        <v>17719.423520633849</v>
       </c>
       <c r="S46">
-        <v>19089.5</v>
+        <v>19089.512149571477</v>
       </c>
       <c r="T46">
-        <v>17113.2</v>
+        <v>17113.175390076543</v>
       </c>
       <c r="U46">
-        <v>17660.5</v>
+        <v>17622.296771334692</v>
       </c>
       <c r="V46">
-        <v>17919.5</v>
+        <v>17887.124418604155</v>
       </c>
       <c r="W46">
-        <v>15766.5</v>
+        <v>15739.015102128595</v>
       </c>
       <c r="X46">
-        <v>15476</v>
+        <v>15455.489103251002</v>
       </c>
       <c r="Y46">
-        <v>17624.7</v>
+        <v>17624.722615921419</v>
       </c>
       <c r="Z46">
-        <v>16897.8</v>
+        <v>16897.827539077782</v>
       </c>
       <c r="AA46">
-        <v>16978.2</v>
+        <v>16978.177084695741</v>
       </c>
       <c r="AB46">
-        <v>16926.099999999999</v>
+        <v>16926.102924486408</v>
       </c>
       <c r="AC46">
-        <v>16581.599999999999</v>
+        <v>16581.647823917214</v>
       </c>
       <c r="AD46">
-        <v>17545.7</v>
+        <v>17545.665940796469</v>
       </c>
       <c r="AE46">
-        <v>17216.400000000001</v>
+        <v>17216.447815062555</v>
       </c>
       <c r="AF46">
-        <v>17701.2</v>
+        <v>17701.17614949125</v>
       </c>
       <c r="AG46">
-        <v>17924.2</v>
+        <v>17924.188344719805</v>
       </c>
       <c r="AH46">
-        <v>18655.2</v>
+        <v>18655.200554285653</v>
       </c>
       <c r="AI46">
-        <v>17768.599999999999</v>
+        <v>17784.918044411581</v>
       </c>
       <c r="AJ46">
-        <v>19370.2</v>
+        <v>19383.693345482414</v>
       </c>
       <c r="AK46">
-        <v>18320</v>
+        <v>18322.498681189205</v>
+      </c>
+      <c r="AL46">
+        <v>19406.309924572986</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -11733,8 +12030,11 @@
       <c r="AK47">
         <v>0</v>
       </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -11846,8 +12146,11 @@
       <c r="AK48">
         <v>0</v>
       </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -11959,8 +12262,11 @@
       <c r="AK49">
         <v>0</v>
       </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -12072,8 +12378,11 @@
       <c r="AK50">
         <v>0</v>
       </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -12185,8 +12494,11 @@
       <c r="AK51">
         <v>0</v>
       </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -12200,64 +12512,64 @@
         <v>5</v>
       </c>
       <c r="E52">
-        <v>365.9</v>
+        <v>365.94489565774535</v>
       </c>
       <c r="F52">
-        <v>378.6</v>
+        <v>378.57887961063926</v>
       </c>
       <c r="G52">
-        <v>382.9</v>
+        <v>382.92994702268732</v>
       </c>
       <c r="H52">
-        <v>413.3</v>
+        <v>413.31236117203838</v>
       </c>
       <c r="I52">
-        <v>423</v>
+        <v>422.99390232513872</v>
       </c>
       <c r="J52">
-        <v>444.1</v>
+        <v>444.12063036905414</v>
       </c>
       <c r="K52">
-        <v>460.5</v>
+        <v>460.45643313848296</v>
       </c>
       <c r="L52">
-        <v>483.1</v>
+        <v>483.05071503539199</v>
       </c>
       <c r="M52">
-        <v>446.6</v>
+        <v>446.60529176343613</v>
       </c>
       <c r="N52">
-        <v>449.3</v>
+        <v>449.29826061967248</v>
       </c>
       <c r="O52">
-        <v>433.5</v>
+        <v>433.45907376502782</v>
       </c>
       <c r="P52">
-        <v>402.1</v>
+        <v>402.14271049071476</v>
       </c>
       <c r="Q52">
-        <v>425.4</v>
+        <v>425.4467310841909</v>
       </c>
       <c r="R52">
-        <v>413.5</v>
+        <v>413.54206086455395</v>
       </c>
       <c r="S52">
-        <v>440.9</v>
+        <v>440.86832009005786</v>
       </c>
       <c r="T52">
-        <v>426.9</v>
+        <v>426.9424729113922</v>
       </c>
       <c r="U52">
-        <v>392.6</v>
+        <v>392.63703159603722</v>
       </c>
       <c r="V52">
-        <v>304.89999999999998</v>
+        <v>304.94228088235104</v>
       </c>
       <c r="W52">
-        <v>177.5</v>
+        <v>177.46402063998056</v>
       </c>
       <c r="X52">
-        <v>71.400000000000006</v>
+        <v>71.420176721085966</v>
       </c>
       <c r="Y52">
         <v>0</v>
@@ -12298,8 +12610,11 @@
       <c r="AK52">
         <v>0</v>
       </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -12322,34 +12637,34 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>19.7</v>
+        <v>19.740015789552945</v>
       </c>
       <c r="I53">
-        <v>20.3</v>
+        <v>20.319995267105391</v>
       </c>
       <c r="J53">
-        <v>17</v>
+        <v>17.047854322321914</v>
       </c>
       <c r="K53">
-        <v>16.2</v>
+        <v>16.169528148717905</v>
       </c>
       <c r="L53">
-        <v>17.2</v>
+        <v>17.177491051355702</v>
       </c>
       <c r="M53">
-        <v>16.399999999999999</v>
+        <v>16.425259909017925</v>
       </c>
       <c r="N53">
-        <v>19.2</v>
+        <v>19.231665513943728</v>
       </c>
       <c r="O53">
-        <v>18.2</v>
+        <v>18.157205407679577</v>
       </c>
       <c r="P53">
-        <v>15.8</v>
+        <v>15.753021405600451</v>
       </c>
       <c r="Q53">
-        <v>18.100000000000001</v>
+        <v>18.050235876642766</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -12409,6 +12724,9 @@
         <v>0</v>
       </c>
       <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
         <v>0</v>
       </c>
     </row>
@@ -12419,10 +12737,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2228759-CE77-4D2C-B113-C568283D079F}">
-  <dimension ref="A1:AK53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AL53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12534,8 +12852,11 @@
       <c r="AK1">
         <v>2022</v>
       </c>
+      <c r="AL1">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -12647,8 +12968,11 @@
       <c r="AK2">
         <v>3060</v>
       </c>
+      <c r="AL2">
+        <v>2550</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -12760,8 +13084,11 @@
       <c r="AK3">
         <v>0</v>
       </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -12871,10 +13198,13 @@
         <v>164.65621230398068</v>
       </c>
       <c r="AK4">
-        <v>167.9</v>
+        <v>167.94933655006031</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -12986,8 +13316,11 @@
       <c r="AK5">
         <v>0</v>
       </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -13099,8 +13432,11 @@
       <c r="AK6">
         <v>0</v>
       </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -13212,8 +13548,11 @@
       <c r="AK7">
         <v>0</v>
       </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -13325,8 +13664,11 @@
       <c r="AK8">
         <v>0</v>
       </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -13438,8 +13780,11 @@
       <c r="AK9">
         <v>0</v>
       </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -13551,8 +13896,11 @@
       <c r="AK10">
         <v>0</v>
       </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -13664,8 +14012,11 @@
       <c r="AK11">
         <v>0</v>
       </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -13777,8 +14128,11 @@
       <c r="AK12">
         <v>0</v>
       </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -13890,8 +14244,11 @@
       <c r="AK13">
         <v>0</v>
       </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -14003,8 +14360,11 @@
       <c r="AK14">
         <v>0</v>
       </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -14116,8 +14476,11 @@
       <c r="AK15">
         <v>0</v>
       </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -14229,8 +14592,11 @@
       <c r="AK16">
         <v>0</v>
       </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -14342,8 +14708,11 @@
       <c r="AK17">
         <v>0</v>
       </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -14455,8 +14824,11 @@
       <c r="AK18">
         <v>0</v>
       </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -14566,10 +14938,13 @@
         <v>94.089264173703256</v>
       </c>
       <c r="AK19">
-        <v>96</v>
+        <v>95.971049457177315</v>
+      </c>
+      <c r="AL19">
+        <v>84.620293554562863</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -14681,8 +15056,11 @@
       <c r="AK20">
         <v>0</v>
       </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -14792,10 +15170,13 @@
         <v>1329.9155609167672</v>
       </c>
       <c r="AK21">
-        <v>1356.5</v>
+        <v>1356.5138721351025</v>
+      </c>
+      <c r="AL21">
+        <v>1196.0753031269942</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -14907,8 +15288,11 @@
       <c r="AK22">
         <v>0</v>
       </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -15020,8 +15404,11 @@
       <c r="AK23">
         <v>0</v>
       </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -15133,8 +15520,11 @@
       <c r="AK24">
         <v>0</v>
       </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -15246,8 +15636,11 @@
       <c r="AK25">
         <v>0</v>
       </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -15359,8 +15752,11 @@
       <c r="AK26">
         <v>0</v>
       </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -15472,8 +15868,11 @@
       <c r="AK27">
         <v>0</v>
       </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -15585,8 +15984,11 @@
       <c r="AK28">
         <v>0</v>
       </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -15698,8 +16100,11 @@
       <c r="AK29">
         <v>0</v>
       </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -15811,8 +16216,11 @@
       <c r="AK30">
         <v>0</v>
       </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -15924,8 +16332,11 @@
       <c r="AK31">
         <v>0</v>
       </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -16037,8 +16448,11 @@
       <c r="AK32">
         <v>0</v>
       </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -16150,8 +16564,11 @@
       <c r="AK33">
         <v>0</v>
       </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -16263,8 +16680,11 @@
       <c r="AK34">
         <v>0</v>
       </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -16376,8 +16796,11 @@
       <c r="AK35">
         <v>0</v>
       </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -16489,8 +16912,11 @@
       <c r="AK36">
         <v>0</v>
       </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -16602,8 +17028,11 @@
       <c r="AK37">
         <v>0</v>
       </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -16713,10 +17142,13 @@
         <v>151.99034981905911</v>
       </c>
       <c r="AK38">
-        <v>155</v>
+        <v>155.03015681544031</v>
+      </c>
+      <c r="AL38">
+        <v>136.69432035737077</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -16826,10 +17258,13 @@
         <v>233.41375150784077</v>
       </c>
       <c r="AK39">
-        <v>238.1</v>
+        <v>238.08202653799756</v>
+      </c>
+      <c r="AL39">
+        <v>209.92342054881942</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -16941,8 +17376,11 @@
       <c r="AK40">
         <v>0</v>
       </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -17054,8 +17492,11 @@
       <c r="AK41">
         <v>0</v>
       </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -17167,8 +17608,11 @@
       <c r="AK42">
         <v>0</v>
       </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -17280,8 +17724,11 @@
       <c r="AK43">
         <v>0</v>
       </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -17393,8 +17840,11 @@
       <c r="AK44">
         <v>0</v>
       </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>60</v>
       </c>
@@ -17506,8 +17956,11 @@
       <c r="AK45">
         <v>0</v>
       </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -17617,10 +18070,13 @@
         <v>1025.9348612786489</v>
       </c>
       <c r="AK46">
-        <v>1046.5</v>
+        <v>1046.4535585042217</v>
+      </c>
+      <c r="AL46">
+        <v>922.68666241225276</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -17732,8 +18188,11 @@
       <c r="AK47">
         <v>0</v>
       </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -17845,8 +18304,11 @@
       <c r="AK48">
         <v>0</v>
       </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -17958,8 +18420,11 @@
       <c r="AK49">
         <v>0</v>
       </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -18071,8 +18536,11 @@
       <c r="AK50">
         <v>0</v>
       </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -18184,8 +18652,11 @@
       <c r="AK51">
         <v>0</v>
       </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -18297,8 +18768,11 @@
       <c r="AK52">
         <v>0</v>
       </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -18408,6 +18882,9 @@
         <v>0</v>
       </c>
       <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
         <v>0</v>
       </c>
     </row>
@@ -18418,10 +18895,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC59C81A-71AC-4FBD-8F6E-E86A5690562B}">
-  <dimension ref="A1:AK53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AL53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -18533,8 +19010,11 @@
       <c r="AK1">
         <v>2022</v>
       </c>
+      <c r="AL1">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -18548,106 +19028,109 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>104763.9</v>
+        <v>104763.89416779601</v>
       </c>
       <c r="F2">
-        <v>95236.9</v>
+        <v>95236.89697478473</v>
       </c>
       <c r="G2">
-        <v>96017.5</v>
+        <v>96017.527989984839</v>
       </c>
       <c r="H2">
-        <v>91673.5</v>
+        <v>91673.525914709549</v>
       </c>
       <c r="I2">
-        <v>94551.9</v>
+        <v>94551.938131357616</v>
       </c>
       <c r="J2">
-        <v>98423.7</v>
+        <v>98423.712773785708</v>
       </c>
       <c r="K2">
-        <v>96388.4</v>
+        <v>96388.419426855457</v>
       </c>
       <c r="L2">
-        <v>97621.5</v>
+        <v>97621.537284299804</v>
       </c>
       <c r="M2">
-        <v>91160.1</v>
+        <v>91160.081043356055</v>
       </c>
       <c r="N2">
-        <v>89040.6</v>
+        <v>89040.583118713999</v>
       </c>
       <c r="O2">
-        <v>90487.3</v>
+        <v>90487.331671577558</v>
       </c>
       <c r="P2">
-        <v>79806.100000000006</v>
+        <v>79806.072531698403</v>
       </c>
       <c r="Q2">
-        <v>75797.399999999994</v>
+        <v>75797.351029311525</v>
       </c>
       <c r="R2">
-        <v>72678.5</v>
+        <v>72678.516147640868</v>
       </c>
       <c r="S2">
-        <v>72260.899999999994</v>
+        <v>72260.920911556997</v>
       </c>
       <c r="T2">
-        <v>70097.8</v>
+        <v>70097.826254053696</v>
       </c>
       <c r="U2">
-        <v>72787.5</v>
+        <v>72787.540033067038</v>
       </c>
       <c r="V2">
-        <v>74542.600000000006</v>
+        <v>74542.589785359683</v>
       </c>
       <c r="W2">
-        <v>69950.100000000006</v>
+        <v>69950.099368216484</v>
       </c>
       <c r="X2">
-        <v>45077.2</v>
+        <v>45077.217307209103</v>
       </c>
       <c r="Y2">
-        <v>58569.5</v>
+        <v>58569.534082833612</v>
       </c>
       <c r="Z2">
-        <v>62966.7</v>
+        <v>62966.709362383721</v>
       </c>
       <c r="AA2">
-        <v>57269.9</v>
+        <v>57269.940296641049</v>
       </c>
       <c r="AB2">
-        <v>55198.5</v>
+        <v>55198.472887031639</v>
       </c>
       <c r="AC2">
-        <v>58199.7</v>
+        <v>58199.719114585772</v>
       </c>
       <c r="AD2">
-        <v>47955.9</v>
+        <v>47955.866823480239</v>
       </c>
       <c r="AE2">
-        <v>43633.7</v>
+        <v>43633.727565809473</v>
       </c>
       <c r="AF2">
-        <v>40822.5</v>
+        <v>40822.548651671816</v>
       </c>
       <c r="AG2">
-        <v>42872.1</v>
+        <v>42872.116169430403</v>
       </c>
       <c r="AH2">
-        <v>43103.199999999997</v>
+        <v>46843.36932143708</v>
       </c>
       <c r="AI2">
-        <v>37730.9</v>
+        <v>40682.559796101479</v>
       </c>
       <c r="AJ2">
-        <v>41880.699999999997</v>
+        <v>47226.162362407202</v>
       </c>
       <c r="AK2">
-        <v>40679.599999999999</v>
+        <v>45164.283269784901</v>
+      </c>
+      <c r="AL2">
+        <v>46248.117014659168</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -18759,8 +19242,11 @@
       <c r="AK3">
         <v>0</v>
       </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -18774,106 +19260,109 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>5835.2</v>
+        <v>5835.158984024587</v>
       </c>
       <c r="F4">
-        <v>5349.2</v>
+        <v>5349.1790759819105</v>
       </c>
       <c r="G4">
-        <v>5382.7</v>
+        <v>5382.6803882361164</v>
       </c>
       <c r="H4">
-        <v>5099</v>
+        <v>5099.0149310757079</v>
       </c>
       <c r="I4">
-        <v>5362.2</v>
+        <v>5362.163648956539</v>
       </c>
       <c r="J4">
-        <v>5554.3</v>
+        <v>5554.272036897738</v>
       </c>
       <c r="K4">
-        <v>5422</v>
+        <v>5421.9500152613991</v>
       </c>
       <c r="L4">
-        <v>5443.6</v>
+        <v>5443.5756068778828</v>
       </c>
       <c r="M4">
-        <v>5723.1</v>
+        <v>5723.0707037751617</v>
       </c>
       <c r="N4">
-        <v>5799</v>
+        <v>5798.9519256914291</v>
       </c>
       <c r="O4">
-        <v>6250.3</v>
+        <v>6250.3113707937591</v>
       </c>
       <c r="P4">
-        <v>5789.8</v>
+        <v>5789.8133816394238</v>
       </c>
       <c r="Q4">
-        <v>6992.8</v>
+        <v>6992.8338851121698</v>
       </c>
       <c r="R4">
-        <v>6494.2</v>
+        <v>6494.2114194012402</v>
       </c>
       <c r="S4">
-        <v>5750.8</v>
+        <v>5750.7773537280264</v>
       </c>
       <c r="T4">
-        <v>5689.1</v>
+        <v>5689.0972627903684</v>
       </c>
       <c r="U4">
-        <v>5759.6</v>
+        <v>5759.5741750052239</v>
       </c>
       <c r="V4">
-        <v>5560.7</v>
+        <v>5560.7452934098146</v>
       </c>
       <c r="W4">
-        <v>5294.1</v>
+        <v>5294.1166785805826</v>
       </c>
       <c r="X4">
-        <v>3594.6</v>
+        <v>3594.6123570397285</v>
       </c>
       <c r="Y4">
-        <v>1096.5999999999999</v>
+        <v>4339.3522919415072</v>
       </c>
       <c r="Z4">
-        <v>991</v>
+        <v>4618.7967871454257</v>
       </c>
       <c r="AA4">
-        <v>1158.0999999999999</v>
+        <v>5330.7303648477482</v>
       </c>
       <c r="AB4">
-        <v>1132.9000000000001</v>
+        <v>4481.7189645613362</v>
       </c>
       <c r="AC4">
-        <v>1230.3</v>
+        <v>5292.568968296755</v>
       </c>
       <c r="AD4">
-        <v>1032.7</v>
+        <v>2181.2788159974143</v>
       </c>
       <c r="AE4">
-        <v>1181.5999999999999</v>
+        <v>1495.3517181092457</v>
       </c>
       <c r="AF4">
-        <v>919.1</v>
+        <v>1255.1656727653456</v>
       </c>
       <c r="AG4">
-        <v>807.6</v>
+        <v>1179.1577795246649</v>
       </c>
       <c r="AH4">
-        <v>925.3</v>
+        <v>1364.4167761556773</v>
       </c>
       <c r="AI4">
-        <v>838</v>
+        <v>1218.7816232128412</v>
       </c>
       <c r="AJ4">
-        <v>800.3</v>
+        <v>1149.4166251367192</v>
       </c>
       <c r="AK4">
-        <v>758</v>
+        <v>879.5065154115199</v>
+      </c>
+      <c r="AL4">
+        <v>595.44632988723401</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -18887,106 +19376,109 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>1047.0999999999999</v>
+        <v>1047.1372315766589</v>
       </c>
       <c r="F5">
-        <v>952.2</v>
+        <v>952.16465710482134</v>
       </c>
       <c r="G5">
-        <v>971.7</v>
+        <v>971.67888199700781</v>
       </c>
       <c r="H5">
-        <v>936.9</v>
+        <v>936.92817581813881</v>
       </c>
       <c r="I5">
-        <v>943.9</v>
+        <v>943.94613353049692</v>
       </c>
       <c r="J5">
-        <v>984.3</v>
+        <v>984.25529141202924</v>
       </c>
       <c r="K5">
-        <v>971.9</v>
+        <v>971.89798219546412</v>
       </c>
       <c r="L5">
-        <v>991</v>
+        <v>991.0048836375347</v>
       </c>
       <c r="M5">
-        <v>1067.0999999999999</v>
+        <v>1067.1113975212791</v>
       </c>
       <c r="N5">
-        <v>1116.3</v>
+        <v>1116.2877585753276</v>
       </c>
       <c r="O5">
-        <v>1253.5999999999999</v>
+        <v>1253.5611425121176</v>
       </c>
       <c r="P5">
-        <v>1223.4000000000001</v>
+        <v>1223.4124119576466</v>
       </c>
       <c r="Q5">
-        <v>1513.6</v>
+        <v>1513.6043432087588</v>
       </c>
       <c r="R5">
-        <v>1574.8</v>
+        <v>1574.8024994139346</v>
       </c>
       <c r="S5">
-        <v>1558</v>
+        <v>1558.0170356113222</v>
       </c>
       <c r="T5">
-        <v>1706.2</v>
+        <v>1706.2349660463681</v>
       </c>
       <c r="U5">
-        <v>1911.2</v>
+        <v>1911.1645331962638</v>
       </c>
       <c r="V5">
-        <v>2014.3</v>
+        <v>2014.2932634046181</v>
       </c>
       <c r="W5">
-        <v>1908.9</v>
+        <v>1908.9072508741235</v>
       </c>
       <c r="X5">
-        <v>1311.4</v>
+        <v>1311.3574482083752</v>
       </c>
       <c r="Y5">
-        <v>544.4</v>
+        <v>544.37147916112372</v>
       </c>
       <c r="Z5">
-        <v>538.70000000000005</v>
+        <v>538.65202128055137</v>
       </c>
       <c r="AA5">
-        <v>640.79999999999995</v>
+        <v>640.75591132407999</v>
       </c>
       <c r="AB5">
-        <v>52.9</v>
+        <v>52.943266443799395</v>
       </c>
       <c r="AC5">
-        <v>67</v>
+        <v>66.995085936664864</v>
       </c>
       <c r="AD5">
-        <v>51.6</v>
+        <v>51.55385125611442</v>
       </c>
       <c r="AE5">
-        <v>41.2</v>
+        <v>41.178776483659192</v>
       </c>
       <c r="AF5">
-        <v>258.2</v>
+        <v>258.17053971439361</v>
       </c>
       <c r="AG5">
-        <v>244.1</v>
+        <v>244.12614932779334</v>
       </c>
       <c r="AH5">
-        <v>232.8</v>
+        <v>261.73503414302718</v>
       </c>
       <c r="AI5">
-        <v>258.10000000000002</v>
+        <v>284.2840739204741</v>
       </c>
       <c r="AJ5">
-        <v>400.1</v>
+        <v>446.64518319372945</v>
       </c>
       <c r="AK5">
-        <v>499.4</v>
+        <v>459.16174499258358</v>
+      </c>
+      <c r="AL5">
+        <v>342.4666024235778</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -19000,106 +19492,109 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>266.8</v>
+        <v>266.82627613557298</v>
       </c>
       <c r="F6">
-        <v>242.6</v>
+        <v>242.62583934738521</v>
       </c>
       <c r="G6">
-        <v>247.6</v>
+        <v>247.5983566093436</v>
       </c>
       <c r="H6">
-        <v>238.7</v>
+        <v>238.7433553323593</v>
       </c>
       <c r="I6">
-        <v>240.5</v>
+        <v>240.53163624339706</v>
       </c>
       <c r="J6">
-        <v>250.8</v>
+        <v>250.80301440411407</v>
       </c>
       <c r="K6">
-        <v>247.7</v>
+        <v>247.65418662693031</v>
       </c>
       <c r="L6">
-        <v>252.5</v>
+        <v>252.52291176298607</v>
       </c>
       <c r="M6">
-        <v>198.7</v>
+        <v>198.69286034221508</v>
       </c>
       <c r="N6">
-        <v>154.19999999999999</v>
+        <v>154.20251540356543</v>
       </c>
       <c r="O6">
-        <v>158.30000000000001</v>
+        <v>158.34553838448133</v>
       </c>
       <c r="P6">
-        <v>107.1</v>
+        <v>107.12428039375725</v>
       </c>
       <c r="Q6">
-        <v>67.599999999999994</v>
+        <v>67.637009958368338</v>
       </c>
       <c r="R6">
-        <v>72.3</v>
+        <v>72.251643643430526</v>
       </c>
       <c r="S6">
-        <v>78.400000000000006</v>
+        <v>78.393229176325761</v>
       </c>
       <c r="T6">
-        <v>73.5</v>
+        <v>73.503243308462288</v>
       </c>
       <c r="U6">
-        <v>89.8</v>
+        <v>89.756769320533152</v>
       </c>
       <c r="V6">
-        <v>101.9</v>
+        <v>101.94439447092135</v>
       </c>
       <c r="W6">
-        <v>99</v>
+        <v>99.044629985017153</v>
       </c>
       <c r="X6">
-        <v>70.3</v>
+        <v>70.342073492163564</v>
       </c>
       <c r="Y6">
-        <v>31.8</v>
+        <v>31.789520502191941</v>
       </c>
       <c r="Z6">
-        <v>27.1</v>
+        <v>27.113245110949943</v>
       </c>
       <c r="AA6">
-        <v>45</v>
+        <v>44.994346924019709</v>
       </c>
       <c r="AB6">
-        <v>46.5</v>
+        <v>46.497360669296846</v>
       </c>
       <c r="AC6">
-        <v>40.4</v>
+        <v>40.404270385808523</v>
       </c>
       <c r="AD6">
-        <v>34.9</v>
+        <v>34.910322589297003</v>
       </c>
       <c r="AE6">
-        <v>56.4</v>
+        <v>56.433413216496767</v>
       </c>
       <c r="AF6">
-        <v>44.8</v>
+        <v>44.820467448888387</v>
       </c>
       <c r="AG6">
-        <v>34.6</v>
+        <v>34.605744805258531</v>
       </c>
       <c r="AH6">
-        <v>35.299999999999997</v>
+        <v>39.662448106016384</v>
       </c>
       <c r="AI6">
-        <v>25.7</v>
+        <v>28.310680623212551</v>
       </c>
       <c r="AJ6">
-        <v>24.6</v>
+        <v>27.452746858472494</v>
       </c>
       <c r="AK6">
-        <v>20.9</v>
+        <v>19.176072504639073</v>
+      </c>
+      <c r="AL6">
+        <v>15.852173310472688</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -19113,97 +19608,97 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>3464.4</v>
+        <v>3464.3852423969684</v>
       </c>
       <c r="F7">
-        <v>3150.2</v>
+        <v>3150.1746733225805</v>
       </c>
       <c r="G7">
-        <v>3214.7</v>
+        <v>3214.7362137727418</v>
       </c>
       <c r="H7">
-        <v>3099.8</v>
+        <v>3099.7657686213661</v>
       </c>
       <c r="I7">
-        <v>3123</v>
+        <v>3122.9842240418197</v>
       </c>
       <c r="J7">
-        <v>3256.3</v>
+        <v>3256.34444416117</v>
       </c>
       <c r="K7">
-        <v>3215.5</v>
+        <v>3215.4610924908779</v>
       </c>
       <c r="L7">
-        <v>3278.7</v>
+        <v>3278.6750298696265</v>
       </c>
       <c r="M7">
-        <v>3110.7</v>
+        <v>3110.6990650420857</v>
       </c>
       <c r="N7">
-        <v>2923.1</v>
+        <v>2923.1385739005041</v>
       </c>
       <c r="O7">
-        <v>3663.6</v>
+        <v>3663.6426565866968</v>
       </c>
       <c r="P7">
-        <v>3064.1</v>
+        <v>3064.1066175223941</v>
       </c>
       <c r="Q7">
-        <v>2438.6999999999998</v>
+        <v>2438.7387703170989</v>
       </c>
       <c r="R7">
-        <v>2102.6</v>
+        <v>2102.6028097742096</v>
       </c>
       <c r="S7">
-        <v>1903.8</v>
+        <v>1903.8087281830096</v>
       </c>
       <c r="T7">
-        <v>1525.5</v>
+        <v>1525.4504344108329</v>
       </c>
       <c r="U7">
-        <v>1620.3</v>
+        <v>1620.3335787131189</v>
       </c>
       <c r="V7">
-        <v>1623</v>
+        <v>1622.9547599770679</v>
       </c>
       <c r="W7">
-        <v>1576.8</v>
+        <v>1576.7905093614727</v>
       </c>
       <c r="X7">
-        <v>1119.8</v>
+        <v>1119.8458099952436</v>
       </c>
       <c r="Y7">
-        <v>12.8</v>
+        <v>12.768301522141815</v>
       </c>
       <c r="Z7">
-        <v>15.3</v>
+        <v>15.342870230364023</v>
       </c>
       <c r="AA7">
-        <v>15.5</v>
+        <v>15.470870988915227</v>
       </c>
       <c r="AB7">
-        <v>13.1</v>
+        <v>13.066344089857244</v>
       </c>
       <c r="AC7">
-        <v>18.2</v>
+        <v>18.170794779779854</v>
       </c>
       <c r="AD7">
-        <v>16.899999999999999</v>
+        <v>16.917893538591873</v>
       </c>
       <c r="AE7">
-        <v>23.8</v>
+        <v>23.773072501308928</v>
       </c>
       <c r="AF7">
-        <v>18.399999999999999</v>
+        <v>18.350932395412517</v>
       </c>
       <c r="AG7">
-        <v>31</v>
+        <v>30.98469646206598</v>
       </c>
       <c r="AH7">
-        <v>13.7</v>
+        <v>15.372659475143667</v>
       </c>
       <c r="AI7">
-        <v>105.4</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
         <v>0</v>
@@ -19211,8 +19706,11 @@
       <c r="AK7">
         <v>0</v>
       </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -19226,106 +19724,109 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>118.3</v>
+        <v>118.34743676217248</v>
       </c>
       <c r="F8">
-        <v>107.6</v>
+        <v>107.61363758809195</v>
       </c>
       <c r="G8">
-        <v>109.8</v>
+        <v>109.8191350403347</v>
       </c>
       <c r="H8">
-        <v>105.9</v>
+        <v>105.89161066442058</v>
       </c>
       <c r="I8">
-        <v>106.7</v>
+        <v>106.6847801569353</v>
       </c>
       <c r="J8">
-        <v>111.2</v>
+        <v>111.24052067447779</v>
       </c>
       <c r="K8">
-        <v>109.8</v>
+        <v>109.84389774201263</v>
       </c>
       <c r="L8">
-        <v>112</v>
+        <v>112.00335950303869</v>
       </c>
       <c r="M8">
-        <v>103.9</v>
+        <v>103.92128160485427</v>
       </c>
       <c r="N8">
-        <v>95.8</v>
+        <v>95.791949793032629</v>
       </c>
       <c r="O8">
-        <v>118.1</v>
+        <v>118.05693118730753</v>
       </c>
       <c r="P8">
-        <v>97.3</v>
+        <v>97.286913003214323</v>
       </c>
       <c r="Q8">
-        <v>76.400000000000006</v>
+        <v>76.421037225688877</v>
       </c>
       <c r="R8">
-        <v>68.2</v>
+        <v>68.201338041892726</v>
       </c>
       <c r="S8">
-        <v>63.9</v>
+        <v>63.906590548300763</v>
       </c>
       <c r="T8">
-        <v>53</v>
+        <v>52.980429317372312</v>
       </c>
       <c r="U8">
-        <v>58.2</v>
+        <v>58.214953432589702</v>
       </c>
       <c r="V8">
-        <v>60.3</v>
+        <v>60.308157571218729</v>
       </c>
       <c r="W8">
-        <v>58.6</v>
+        <v>58.592717949031176</v>
       </c>
       <c r="X8">
-        <v>41.6</v>
+        <v>41.612889792206218</v>
       </c>
       <c r="Y8">
-        <v>104.9</v>
+        <v>104.86032724024933</v>
       </c>
       <c r="Z8">
-        <v>71.900000000000006</v>
+        <v>71.90214659484289</v>
       </c>
       <c r="AA8">
-        <v>106.2</v>
+        <v>106.23548906300304</v>
       </c>
       <c r="AB8">
-        <v>72.900000000000006</v>
+        <v>72.862250358781438</v>
       </c>
       <c r="AC8">
-        <v>56</v>
+        <v>56.035341581432704</v>
       </c>
       <c r="AD8">
-        <v>100.8</v>
+        <v>100.75148962395282</v>
       </c>
       <c r="AE8">
-        <v>76.3</v>
+        <v>76.294926564518974</v>
       </c>
       <c r="AF8">
-        <v>75.099999999999994</v>
+        <v>75.104812963569756</v>
       </c>
       <c r="AG8">
-        <v>95.7</v>
+        <v>95.68602203639368</v>
       </c>
       <c r="AH8">
-        <v>70</v>
+        <v>78.766863589313274</v>
       </c>
       <c r="AI8">
-        <v>92.9</v>
+        <v>102.34691431183006</v>
       </c>
       <c r="AJ8">
-        <v>96.8</v>
+        <v>108.03383207844763</v>
       </c>
       <c r="AK8">
-        <v>95.8</v>
+        <v>88.101735524741173</v>
+      </c>
+      <c r="AL8">
+        <v>54.266667273249958</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -19339,64 +19840,64 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>1297.8</v>
+        <v>1297.805144482526</v>
       </c>
       <c r="F9">
-        <v>1180.0999999999999</v>
+        <v>1180.0976539860644</v>
       </c>
       <c r="G9">
-        <v>1204.3</v>
+        <v>1204.2832723481736</v>
       </c>
       <c r="H9">
-        <v>1161.2</v>
+        <v>1161.2138026613482</v>
       </c>
       <c r="I9">
-        <v>1169.9000000000001</v>
+        <v>1169.9117472556263</v>
       </c>
       <c r="J9">
-        <v>1219.9000000000001</v>
+        <v>1219.8702731210883</v>
       </c>
       <c r="K9">
-        <v>1204.5999999999999</v>
+        <v>1204.5548216314373</v>
       </c>
       <c r="L9">
-        <v>1228.2</v>
+        <v>1228.235609821256</v>
       </c>
       <c r="M9">
-        <v>1098.9000000000001</v>
+        <v>1098.8553654483046</v>
       </c>
       <c r="N9">
-        <v>937.6</v>
+        <v>937.62643164904273</v>
       </c>
       <c r="O9">
-        <v>1044.3</v>
+        <v>1044.3013146863907</v>
       </c>
       <c r="P9">
-        <v>995.2</v>
+        <v>995.24901219547473</v>
       </c>
       <c r="Q9">
-        <v>997.1</v>
+        <v>997.07869164725696</v>
       </c>
       <c r="R9">
-        <v>775.1</v>
+        <v>775.13970073159999</v>
       </c>
       <c r="S9">
-        <v>941.6</v>
+        <v>941.58120214402436</v>
       </c>
       <c r="T9">
-        <v>806</v>
+        <v>806.00876642951425</v>
       </c>
       <c r="U9">
-        <v>781.8</v>
+        <v>781.82858882018502</v>
       </c>
       <c r="V9">
-        <v>764.3</v>
+        <v>764.26694925345646</v>
       </c>
       <c r="W9">
-        <v>738.1</v>
+        <v>738.06373689393808</v>
       </c>
       <c r="X9">
-        <v>437.9</v>
+        <v>437.8706094662374</v>
       </c>
       <c r="Y9">
         <v>0</v>
@@ -19437,8 +19938,11 @@
       <c r="AK9">
         <v>0</v>
       </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -19550,8 +20054,11 @@
       <c r="AK10">
         <v>0</v>
       </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -19625,16 +20132,16 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>59.016470613483527</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>66.022044381485088</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>59.491124403017913</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>57.464330530873568</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -19663,8 +20170,11 @@
       <c r="AK11">
         <v>0</v>
       </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -19678,106 +20188,109 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>950.1</v>
+        <v>950.14897298159076</v>
       </c>
       <c r="F12">
-        <v>864</v>
+        <v>863.97297677528252</v>
       </c>
       <c r="G12">
-        <v>881.7</v>
+        <v>881.6797492791361</v>
       </c>
       <c r="H12">
-        <v>850.1</v>
+        <v>850.14773342623539</v>
       </c>
       <c r="I12">
-        <v>856.5</v>
+        <v>856.51567175537446</v>
       </c>
       <c r="J12">
-        <v>893.1</v>
+        <v>893.09130273090909</v>
       </c>
       <c r="K12">
-        <v>881.9</v>
+        <v>881.87855591332459</v>
       </c>
       <c r="L12">
-        <v>899.2</v>
+        <v>899.21573220177447</v>
       </c>
       <c r="M12">
-        <v>897.7</v>
+        <v>897.69532201089282</v>
       </c>
       <c r="N12">
-        <v>895.5</v>
+        <v>895.4501843088434</v>
       </c>
       <c r="O12">
-        <v>1055.5</v>
+        <v>1055.5110393923253</v>
       </c>
       <c r="P12">
-        <v>1246.3</v>
+        <v>1246.3114021332715</v>
       </c>
       <c r="Q12">
-        <v>1362.4</v>
+        <v>1362.4317727094055</v>
       </c>
       <c r="R12">
-        <v>1210.8</v>
+        <v>1210.8366390168421</v>
       </c>
       <c r="S12">
-        <v>945.4</v>
+        <v>945.39731634120176</v>
       </c>
       <c r="T12">
-        <v>739</v>
+        <v>739.02619808234465</v>
       </c>
       <c r="U12">
-        <v>665.6</v>
+        <v>665.55254750183292</v>
       </c>
       <c r="V12">
-        <v>618.70000000000005</v>
+        <v>618.68950290274404</v>
       </c>
       <c r="W12">
-        <v>533.20000000000005</v>
+        <v>533.16239770813468</v>
       </c>
       <c r="X12">
-        <v>356</v>
+        <v>356.01179501293035</v>
       </c>
       <c r="Y12">
-        <v>25.4</v>
+        <v>25.423540506174312</v>
       </c>
       <c r="Z12">
-        <v>33.200000000000003</v>
+        <v>33.181352607502276</v>
       </c>
       <c r="AA12">
-        <v>32.200000000000003</v>
+        <v>32.235022498917395</v>
       </c>
       <c r="AB12">
-        <v>28.1</v>
+        <v>28.128522707186459</v>
       </c>
       <c r="AC12">
-        <v>23.1</v>
+        <v>23.061527681136177</v>
       </c>
       <c r="AD12">
-        <v>26.5</v>
+        <v>26.487930266598035</v>
       </c>
       <c r="AE12">
-        <v>27.8</v>
+        <v>27.827497308603807</v>
       </c>
       <c r="AF12">
-        <v>20.6</v>
+        <v>20.55867029171106</v>
       </c>
       <c r="AG12">
-        <v>24.5</v>
+        <v>24.513647862863966</v>
       </c>
       <c r="AH12">
-        <v>55.7</v>
+        <v>62.650339749408118</v>
       </c>
       <c r="AI12">
-        <v>43.1</v>
+        <v>47.528568331028588</v>
       </c>
       <c r="AJ12">
-        <v>49.2</v>
+        <v>54.904773108574602</v>
       </c>
       <c r="AK12">
-        <v>55.2</v>
+        <v>50.732039881106481</v>
+      </c>
+      <c r="AL12">
+        <v>23.016537184854997</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -19791,106 +20304,109 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>869.8</v>
+        <v>869.76483874098199</v>
       </c>
       <c r="F13">
-        <v>790.9</v>
+        <v>790.87947068283495</v>
       </c>
       <c r="G13">
-        <v>807.1</v>
+        <v>807.08822169911991</v>
       </c>
       <c r="H13">
-        <v>778.2</v>
+        <v>778.22386519993381</v>
       </c>
       <c r="I13">
-        <v>784.1</v>
+        <v>784.05306568475442</v>
       </c>
       <c r="J13">
-        <v>817.5</v>
+        <v>817.53433933961924</v>
       </c>
       <c r="K13">
-        <v>807.3</v>
+        <v>807.27020897168711</v>
       </c>
       <c r="L13">
-        <v>823.1</v>
+        <v>823.14063220798084</v>
       </c>
       <c r="M13">
-        <v>868.8</v>
+        <v>868.8162256656243</v>
       </c>
       <c r="N13">
-        <v>920.1</v>
+        <v>920.06859396434049</v>
       </c>
       <c r="O13">
-        <v>1156.8</v>
+        <v>1156.8342903284495</v>
       </c>
       <c r="P13">
-        <v>1465</v>
+        <v>1464.9843560047721</v>
       </c>
       <c r="Q13">
-        <v>1728.6</v>
+        <v>1728.5670777951236</v>
       </c>
       <c r="R13">
-        <v>1743.9</v>
+        <v>1743.9247466404736</v>
       </c>
       <c r="S13">
-        <v>1548.6</v>
+        <v>1548.6014619205655</v>
       </c>
       <c r="T13">
-        <v>1380.9</v>
+        <v>1380.9432404362656</v>
       </c>
       <c r="U13">
-        <v>1424.8</v>
+        <v>1424.8247022944661</v>
       </c>
       <c r="V13">
-        <v>1526.4</v>
+        <v>1526.3721288719014</v>
       </c>
       <c r="W13">
-        <v>1315.4</v>
+        <v>1315.367757503622</v>
       </c>
       <c r="X13">
-        <v>878.3</v>
+        <v>878.31857322269013</v>
       </c>
       <c r="Y13">
-        <v>40.799999999999997</v>
+        <v>40.820546039357716</v>
       </c>
       <c r="Z13">
-        <v>30.8</v>
+        <v>30.759500936855304</v>
       </c>
       <c r="AA13">
-        <v>29.6</v>
+        <v>29.583213283189451</v>
       </c>
       <c r="AB13">
-        <v>20.5</v>
+        <v>20.46892415297016</v>
       </c>
       <c r="AC13">
-        <v>22.2</v>
+        <v>22.234728332314756</v>
       </c>
       <c r="AD13">
-        <v>29.1</v>
+        <v>29.121709122254448</v>
       </c>
       <c r="AE13">
-        <v>21.9</v>
+        <v>21.889294937542203</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>22.040464815704535</v>
       </c>
       <c r="AG13">
-        <v>24.9</v>
+        <v>24.918741889707555</v>
       </c>
       <c r="AH13">
-        <v>22.6</v>
+        <v>25.379843881184939</v>
       </c>
       <c r="AI13">
-        <v>36.799999999999997</v>
+        <v>40.490676545313065</v>
       </c>
       <c r="AJ13">
-        <v>36.299999999999997</v>
+        <v>40.563945929514482</v>
       </c>
       <c r="AK13">
-        <v>38.799999999999997</v>
+        <v>35.64755623582424</v>
+      </c>
+      <c r="AL13">
+        <v>20.089234415852697</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -20002,8 +20518,11 @@
       <c r="AK14">
         <v>0</v>
       </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -20017,106 +20536,109 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>389</v>
+        <v>388.97272532426217</v>
       </c>
       <c r="F15">
-        <v>353.7</v>
+        <v>353.69392899328886</v>
       </c>
       <c r="G15">
-        <v>360.9</v>
+        <v>360.94274128838356</v>
       </c>
       <c r="H15">
-        <v>348</v>
+        <v>348.03414012157668</v>
       </c>
       <c r="I15">
-        <v>350.6</v>
+        <v>350.64105166599404</v>
       </c>
       <c r="J15">
-        <v>365.6</v>
+        <v>365.61441191324423</v>
       </c>
       <c r="K15">
-        <v>361</v>
+        <v>361.02412890286496</v>
       </c>
       <c r="L15">
-        <v>368.1</v>
+        <v>368.12163561192722</v>
       </c>
       <c r="M15">
-        <v>320</v>
+        <v>320.04762248650411</v>
       </c>
       <c r="N15">
-        <v>261.2</v>
+        <v>261.19091865619788</v>
       </c>
       <c r="O15">
-        <v>198.6</v>
+        <v>198.5935409501989</v>
       </c>
       <c r="P15">
-        <v>103</v>
+        <v>103.00237445899911</v>
       </c>
       <c r="Q15">
-        <v>46.4</v>
+        <v>46.43108498684883</v>
       </c>
       <c r="R15">
-        <v>128.69999999999999</v>
+        <v>128.67779287927081</v>
       </c>
       <c r="S15">
-        <v>194.8</v>
+        <v>194.8220101108123</v>
       </c>
       <c r="T15">
-        <v>229.4</v>
+        <v>229.37919037121057</v>
       </c>
       <c r="U15">
-        <v>307.89999999999998</v>
+        <v>307.94460605397308</v>
       </c>
       <c r="V15">
-        <v>380.2</v>
+        <v>380.22344326088745</v>
       </c>
       <c r="W15">
-        <v>334.5</v>
+        <v>334.52034332173218</v>
       </c>
       <c r="X15">
-        <v>212.7</v>
+        <v>212.70360145273492</v>
       </c>
       <c r="Y15">
-        <v>215.8</v>
+        <v>215.81381415791003</v>
       </c>
       <c r="Z15">
-        <v>194.9</v>
+        <v>194.9181308159236</v>
       </c>
       <c r="AA15">
-        <v>253.2</v>
+        <v>253.15376541951622</v>
       </c>
       <c r="AB15">
-        <v>189.2</v>
+        <v>189.16021887827483</v>
       </c>
       <c r="AC15">
-        <v>165</v>
+        <v>165.01080653270921</v>
       </c>
       <c r="AD15">
-        <v>170.2</v>
+        <v>170.24892740749448</v>
       </c>
       <c r="AE15">
-        <v>216</v>
+        <v>215.97541642994364</v>
       </c>
       <c r="AF15">
-        <v>208</v>
+        <v>207.99532488402249</v>
       </c>
       <c r="AG15">
-        <v>175.9</v>
+        <v>175.91231248050775</v>
       </c>
       <c r="AH15">
-        <v>176.8</v>
+        <v>198.8153512209428</v>
       </c>
       <c r="AI15">
-        <v>191.4</v>
+        <v>210.84099081495953</v>
       </c>
       <c r="AJ15">
-        <v>152.9</v>
+        <v>170.71847330580661</v>
       </c>
       <c r="AK15">
-        <v>123.5</v>
+        <v>113.50807691496141</v>
+      </c>
+      <c r="AL15">
+        <v>74.689200589508786</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -20228,8 +20750,11 @@
       <c r="AK16">
         <v>0</v>
       </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -20243,106 +20768,109 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>7558.2</v>
+        <v>7558.1758168734486</v>
       </c>
       <c r="F17">
-        <v>6899.3</v>
+        <v>6899.335706985079</v>
       </c>
       <c r="G17">
-        <v>6984.8</v>
+        <v>6984.8433968970285</v>
       </c>
       <c r="H17">
-        <v>6662.3</v>
+        <v>6662.3107100082634</v>
       </c>
       <c r="I17">
-        <v>6838.3</v>
+        <v>6838.2996926829146</v>
       </c>
       <c r="J17">
-        <v>7146.3</v>
+        <v>7146.2565393921514</v>
       </c>
       <c r="K17">
-        <v>7031.4</v>
+        <v>7031.4181055643094</v>
       </c>
       <c r="L17">
-        <v>7137.5</v>
+        <v>7137.4948097845072</v>
       </c>
       <c r="M17">
-        <v>6297.2</v>
+        <v>6297.1952516298579</v>
       </c>
       <c r="N17">
-        <v>5840.7</v>
+        <v>5840.650612121718</v>
       </c>
       <c r="O17">
-        <v>5363.8</v>
+        <v>5363.8456797191529</v>
       </c>
       <c r="P17">
-        <v>4167.7</v>
+        <v>4167.6701634313295</v>
       </c>
       <c r="Q17">
-        <v>4837.8</v>
+        <v>4837.8290664556007</v>
       </c>
       <c r="R17">
-        <v>4906.5</v>
+        <v>4906.5114315452147</v>
       </c>
       <c r="S17">
-        <v>2853.3</v>
+        <v>2853.2953647655754</v>
       </c>
       <c r="T17">
-        <v>2995.4</v>
+        <v>2995.4232190133121</v>
       </c>
       <c r="U17">
-        <v>2911.4</v>
+        <v>2911.3628748575602</v>
       </c>
       <c r="V17">
-        <v>2900.5</v>
+        <v>2900.4634651305064</v>
       </c>
       <c r="W17">
-        <v>2707.6</v>
+        <v>2707.6373601342207</v>
       </c>
       <c r="X17">
-        <v>1451.7</v>
+        <v>1451.6513538604765</v>
       </c>
       <c r="Y17">
-        <v>660.6</v>
+        <v>3232.2507612053219</v>
       </c>
       <c r="Z17">
-        <v>729.5</v>
+        <v>3693.354648770041</v>
       </c>
       <c r="AA17">
-        <v>733.9</v>
+        <v>3436.7512790191163</v>
       </c>
       <c r="AB17">
-        <v>759.9</v>
+        <v>3577.2586231890832</v>
       </c>
       <c r="AC17">
-        <v>648.6</v>
+        <v>3703.3042423504239</v>
       </c>
       <c r="AD17">
-        <v>534.1</v>
+        <v>1747.6270188577885</v>
       </c>
       <c r="AE17">
-        <v>313.5</v>
+        <v>313.52227902261495</v>
       </c>
       <c r="AF17">
-        <v>293.5</v>
+        <v>293.45384030816905</v>
       </c>
       <c r="AG17">
-        <v>278.5</v>
+        <v>783.30737932090074</v>
       </c>
       <c r="AH17">
-        <v>432.4</v>
+        <v>2439.5593686936036</v>
       </c>
       <c r="AI17">
-        <v>419.2</v>
+        <v>2238.0011268799226</v>
       </c>
       <c r="AJ17">
-        <v>429</v>
+        <v>2227.8701518909397</v>
       </c>
       <c r="AK17">
-        <v>409.7</v>
+        <v>2479.5853829329594</v>
+      </c>
+      <c r="AL17">
+        <v>2096.5081351919112</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -20356,106 +20884,109 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>24295.9</v>
+        <v>24295.870219978548</v>
       </c>
       <c r="F18">
-        <v>22163.4</v>
+        <v>22163.376767852951</v>
       </c>
       <c r="G18">
-        <v>22243.7</v>
+        <v>22243.72355633472</v>
       </c>
       <c r="H18">
-        <v>21215.9</v>
+        <v>21215.857118412478</v>
       </c>
       <c r="I18">
-        <v>21536.799999999999</v>
+        <v>21536.753400205278</v>
       </c>
       <c r="J18">
-        <v>22565.200000000001</v>
+        <v>22565.236621999422</v>
       </c>
       <c r="K18">
-        <v>22163.200000000001</v>
+        <v>22163.241601624773</v>
       </c>
       <c r="L18">
-        <v>22498.400000000001</v>
+        <v>22498.417112778679</v>
       </c>
       <c r="M18">
-        <v>20115</v>
+        <v>20114.95550242934</v>
       </c>
       <c r="N18">
-        <v>21244.1</v>
+        <v>21244.103680123044</v>
       </c>
       <c r="O18">
-        <v>20951.5</v>
+        <v>20951.535334683631</v>
       </c>
       <c r="P18">
-        <v>18916</v>
+        <v>18915.968119741101</v>
       </c>
       <c r="Q18">
-        <v>15619.3</v>
+        <v>15619.268276365216</v>
       </c>
       <c r="R18">
-        <v>16274.5</v>
+        <v>16274.458716912734</v>
       </c>
       <c r="S18">
-        <v>18286</v>
+        <v>18286.038908668852</v>
       </c>
       <c r="T18">
-        <v>16873.2</v>
+        <v>16873.24915735727</v>
       </c>
       <c r="U18">
-        <v>17853.2</v>
+        <v>17853.214908408529</v>
       </c>
       <c r="V18">
-        <v>17951.599999999999</v>
+        <v>17951.579178292195</v>
       </c>
       <c r="W18">
-        <v>17769.8</v>
+        <v>17769.760858661321</v>
       </c>
       <c r="X18">
-        <v>12682.1</v>
+        <v>12682.146613047153</v>
       </c>
       <c r="Y18">
-        <v>19841.099999999999</v>
+        <v>22614.120272408891</v>
       </c>
       <c r="Z18">
-        <v>20125.099999999999</v>
+        <v>23478.655043707291</v>
       </c>
       <c r="AA18">
-        <v>19603.8</v>
+        <v>22244.080920858782</v>
       </c>
       <c r="AB18">
-        <v>18901.2</v>
+        <v>21670.209297420497</v>
       </c>
       <c r="AC18">
-        <v>19845.7</v>
+        <v>23978.846921490327</v>
       </c>
       <c r="AD18">
-        <v>18000.5</v>
+        <v>20706.191916406075</v>
       </c>
       <c r="AE18">
-        <v>14451.6</v>
+        <v>20865.721267996436</v>
       </c>
       <c r="AF18">
-        <v>10963.4</v>
+        <v>19259.401878597069</v>
       </c>
       <c r="AG18">
-        <v>10721.8</v>
+        <v>19556.280527141516</v>
       </c>
       <c r="AH18">
-        <v>10743.6</v>
+        <v>21431.704840564213</v>
       </c>
       <c r="AI18">
-        <v>6272.8</v>
+        <v>19319.514952867255</v>
       </c>
       <c r="AJ18">
-        <v>5049</v>
+        <v>23206.99429224151</v>
       </c>
       <c r="AK18">
-        <v>5983.2</v>
+        <v>22330.973634788799</v>
+      </c>
+      <c r="AL18">
+        <v>22723.750220957354</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -20567,8 +21098,11 @@
       <c r="AK19">
         <v>0</v>
       </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -20582,106 +21116,109 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>3122.5</v>
+        <v>3122.5083095178566</v>
       </c>
       <c r="F20">
-        <v>2812.8</v>
+        <v>2812.8158794290275</v>
       </c>
       <c r="G20">
-        <v>2879.6</v>
+        <v>2879.588092168889</v>
       </c>
       <c r="H20">
-        <v>2752.5</v>
+        <v>2752.5002213515154</v>
       </c>
       <c r="I20">
-        <v>2864.7</v>
+        <v>2864.6726466796117</v>
       </c>
       <c r="J20">
-        <v>3001.4</v>
+        <v>3001.3750607160509</v>
       </c>
       <c r="K20">
-        <v>2926.2</v>
+        <v>2926.2413748149193</v>
       </c>
       <c r="L20">
-        <v>2962.4</v>
+        <v>2962.4097792707134</v>
       </c>
       <c r="M20">
-        <v>2731.8</v>
+        <v>2731.8338896821306</v>
       </c>
       <c r="N20">
-        <v>2322.1999999999998</v>
+        <v>2322.1693116790316</v>
       </c>
       <c r="O20">
-        <v>1976.9</v>
+        <v>1976.9445654149526</v>
       </c>
       <c r="P20">
-        <v>1336</v>
+        <v>1336.0328537991086</v>
       </c>
       <c r="Q20">
-        <v>1018.3</v>
+        <v>1018.2939054522909</v>
       </c>
       <c r="R20">
-        <v>1114.0999999999999</v>
+        <v>1114.0920085009984</v>
       </c>
       <c r="S20">
-        <v>1142.4000000000001</v>
+        <v>1142.3746675158827</v>
       </c>
       <c r="T20">
-        <v>1303.4000000000001</v>
+        <v>1303.3985524327197</v>
       </c>
       <c r="U20">
-        <v>1480.4</v>
+        <v>1480.355652738464</v>
       </c>
       <c r="V20">
-        <v>1610.7</v>
+        <v>1610.7394257473607</v>
       </c>
       <c r="W20">
-        <v>1523.7</v>
+        <v>1523.7049038446628</v>
       </c>
       <c r="X20">
-        <v>1016.6</v>
+        <v>1016.6136998409546</v>
       </c>
       <c r="Y20">
-        <v>541</v>
+        <v>2333.3949090959832</v>
       </c>
       <c r="Z20">
-        <v>493.2</v>
+        <v>2771.3020334867138</v>
       </c>
       <c r="AA20">
-        <v>473.8</v>
+        <v>2524.2955415697661</v>
       </c>
       <c r="AB20">
-        <v>448</v>
+        <v>2345.450600916131</v>
       </c>
       <c r="AC20">
-        <v>305.10000000000002</v>
+        <v>1912.041066363646</v>
       </c>
       <c r="AD20">
-        <v>312.39999999999998</v>
+        <v>1721.8344205100868</v>
       </c>
       <c r="AE20">
-        <v>247.2</v>
+        <v>247.15302794715814</v>
       </c>
       <c r="AF20">
-        <v>303.3</v>
+        <v>303.27502649476872</v>
       </c>
       <c r="AG20">
-        <v>307.39999999999998</v>
+        <v>307.36569430913903</v>
       </c>
       <c r="AH20">
-        <v>230.7</v>
+        <v>259.4449722993669</v>
       </c>
       <c r="AI20">
-        <v>224.6</v>
+        <v>247.3687427594017</v>
       </c>
       <c r="AJ20">
-        <v>230.3</v>
+        <v>257.1361710597497</v>
       </c>
       <c r="AK20">
-        <v>214</v>
+        <v>196.71154178794833</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -20695,55 +21232,55 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>253.1</v>
+        <v>253.06116335006561</v>
       </c>
       <c r="F21">
-        <v>230.1</v>
+        <v>230.10918584659495</v>
       </c>
       <c r="G21">
-        <v>234.8</v>
+        <v>234.82517941857026</v>
       </c>
       <c r="H21">
-        <v>226.4</v>
+        <v>226.42699256428386</v>
       </c>
       <c r="I21">
-        <v>228.1</v>
+        <v>228.1230191112121</v>
       </c>
       <c r="J21">
-        <v>237.9</v>
+        <v>237.86451437998696</v>
       </c>
       <c r="K21">
-        <v>234.9</v>
+        <v>234.87812926071092</v>
       </c>
       <c r="L21">
-        <v>239.5</v>
+        <v>239.49568516564719</v>
       </c>
       <c r="M21">
-        <v>302.2</v>
+        <v>302.16329610091498</v>
       </c>
       <c r="N21">
-        <v>373</v>
+        <v>373.00003916262688</v>
       </c>
       <c r="O21">
-        <v>536.6</v>
+        <v>536.56472167146194</v>
       </c>
       <c r="P21">
-        <v>766.3</v>
+        <v>766.26753839554544</v>
       </c>
       <c r="Q21">
-        <v>1008</v>
+        <v>1007.9661187817977</v>
       </c>
       <c r="R21">
-        <v>767.6</v>
+        <v>767.59031385468188</v>
       </c>
       <c r="S21">
-        <v>483.9</v>
+        <v>483.88509286118307</v>
       </c>
       <c r="T21">
-        <v>273.10000000000002</v>
+        <v>273.06726120370149</v>
       </c>
       <c r="U21">
-        <v>134.1</v>
+        <v>134.06874590031242</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -20755,31 +21292,31 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>37.4</v>
+        <v>37.366547622391813</v>
       </c>
       <c r="Z21">
-        <v>35.299999999999997</v>
+        <v>35.341636003368649</v>
       </c>
       <c r="AA21">
-        <v>33</v>
+        <v>32.970166616494517</v>
       </c>
       <c r="AB21">
-        <v>38.799999999999997</v>
+        <v>38.768294909135328</v>
       </c>
       <c r="AC21">
-        <v>23.8</v>
+        <v>23.811910726505921</v>
       </c>
       <c r="AD21">
-        <v>32.799999999999997</v>
+        <v>32.847061579539655</v>
       </c>
       <c r="AE21">
-        <v>26.5</v>
+        <v>26.463500283642912</v>
       </c>
       <c r="AF21">
-        <v>29.9</v>
+        <v>29.879753911764595</v>
       </c>
       <c r="AG21">
-        <v>33.799999999999997</v>
+        <v>33.83515936543364</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -20788,13 +21325,16 @@
         <v>0</v>
       </c>
       <c r="AJ21">
-        <v>8.8000000000000007</v>
+        <v>9.8680110240716168</v>
       </c>
       <c r="AK21">
-        <v>408.4</v>
+        <v>375.5030251312383</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -20906,8 +21446,11 @@
       <c r="AK22">
         <v>0</v>
       </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -20921,70 +21464,70 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>1919.6</v>
+        <v>1919.5594036447349</v>
       </c>
       <c r="F23">
-        <v>1729.8</v>
+        <v>1729.8258184914002</v>
       </c>
       <c r="G23">
-        <v>1613.2</v>
+        <v>1613.2394807075332</v>
       </c>
       <c r="H23">
-        <v>1555.6</v>
+        <v>1555.6392724092882</v>
       </c>
       <c r="I23">
-        <v>1567.2</v>
+        <v>1567.1959105902558</v>
       </c>
       <c r="J23">
-        <v>1634.1</v>
+        <v>1634.1195889096964</v>
       </c>
       <c r="K23">
-        <v>1613.6</v>
+        <v>1613.6032439804922</v>
       </c>
       <c r="L23">
-        <v>1645.3</v>
+        <v>1645.3256662039596</v>
       </c>
       <c r="M23">
-        <v>1472</v>
+        <v>1472.009866642069</v>
       </c>
       <c r="N23">
-        <v>1256</v>
+        <v>1256.0300490944976</v>
       </c>
       <c r="O23">
-        <v>1398.9</v>
+        <v>1398.9300933508252</v>
       </c>
       <c r="P23">
-        <v>1333.2</v>
+        <v>1333.2203780247487</v>
       </c>
       <c r="Q23">
-        <v>1335.7</v>
+        <v>1335.6713886768348</v>
       </c>
       <c r="R23">
-        <v>1038.4000000000001</v>
+        <v>1038.3653057355662</v>
       </c>
       <c r="S23">
-        <v>1261.3</v>
+        <v>1261.3277992552235</v>
       </c>
       <c r="T23">
-        <v>1079.7</v>
+        <v>1079.7170347347815</v>
       </c>
       <c r="U23">
-        <v>1047.3</v>
+        <v>1047.325638071246</v>
       </c>
       <c r="V23">
-        <v>1023.8</v>
+        <v>1023.8003338961236</v>
       </c>
       <c r="W23">
-        <v>988.7</v>
+        <v>988.69891077553677</v>
       </c>
       <c r="X23">
-        <v>586.6</v>
+        <v>586.56478160246138</v>
       </c>
       <c r="Y23">
-        <v>169.4</v>
+        <v>1880.3509558733247</v>
       </c>
       <c r="Z23">
-        <v>4669.3999999999996</v>
+        <v>2275.3665706627166</v>
       </c>
       <c r="AA23">
         <v>0</v>
@@ -21019,8 +21562,11 @@
       <c r="AK23">
         <v>0</v>
       </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -21132,8 +21678,11 @@
       <c r="AK24">
         <v>0</v>
       </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -21147,106 +21696,109 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>6812.7</v>
+        <v>6812.6978849183224</v>
       </c>
       <c r="F25">
-        <v>6140.7</v>
+        <v>6140.7445576249684</v>
       </c>
       <c r="G25">
-        <v>6179.5</v>
+        <v>6179.473726480348</v>
       </c>
       <c r="H25">
-        <v>5958.6</v>
+        <v>5958.5686779116004</v>
       </c>
       <c r="I25">
-        <v>6229.1</v>
+        <v>6229.0699485483474</v>
       </c>
       <c r="J25">
-        <v>6480.9</v>
+        <v>6480.92510178476</v>
       </c>
       <c r="K25">
-        <v>6364.3</v>
+        <v>6364.2758733096316</v>
       </c>
       <c r="L25">
-        <v>6472.3</v>
+        <v>6472.283944874338</v>
       </c>
       <c r="M25">
-        <v>5969.8</v>
+        <v>5969.8465427123328</v>
       </c>
       <c r="N25">
-        <v>5610.4</v>
+        <v>5610.3615387678637</v>
       </c>
       <c r="O25">
-        <v>5765.8</v>
+        <v>5765.7873668334214</v>
       </c>
       <c r="P25">
-        <v>5414.4</v>
+        <v>5414.4056003888181</v>
       </c>
       <c r="Q25">
-        <v>5040.5</v>
+        <v>5040.4891391497322</v>
       </c>
       <c r="R25">
-        <v>4617.1000000000004</v>
+        <v>4617.1142576222492</v>
       </c>
       <c r="S25">
-        <v>4181.1000000000004</v>
+        <v>4181.1366920862483</v>
       </c>
       <c r="T25">
-        <v>4422.3</v>
+        <v>4422.3090674545429</v>
       </c>
       <c r="U25">
-        <v>4469.6000000000004</v>
+        <v>4469.6196007993467</v>
       </c>
       <c r="V25">
-        <v>4039</v>
+        <v>4038.9765342003325</v>
       </c>
       <c r="W25">
-        <v>3705.7</v>
+        <v>3705.7183993472827</v>
       </c>
       <c r="X25">
-        <v>2010.8</v>
+        <v>2010.7720377682704</v>
       </c>
       <c r="Y25">
-        <v>12004.4</v>
+        <v>4893.6568606252886</v>
       </c>
       <c r="Z25">
-        <v>11832.5</v>
+        <v>4727.0674680904222</v>
       </c>
       <c r="AA25">
-        <v>9990.2000000000007</v>
+        <v>4889.9059439207167</v>
       </c>
       <c r="AB25">
-        <v>9412.2000000000007</v>
+        <v>5028.3563363021121</v>
       </c>
       <c r="AC25">
-        <v>9820.2999999999993</v>
+        <v>4676.6643943092404</v>
       </c>
       <c r="AD25">
-        <v>9094.2999999999993</v>
+        <v>4439.4815146467936</v>
       </c>
       <c r="AE25">
-        <v>9154.5</v>
+        <v>4364.7127203322161</v>
       </c>
       <c r="AF25">
-        <v>6301.7</v>
+        <v>4126.1492739008836</v>
       </c>
       <c r="AG25">
-        <v>6413.7</v>
+        <v>4159.199680574784</v>
       </c>
       <c r="AH25">
-        <v>6221.3</v>
+        <v>3231.0848308459595</v>
       </c>
       <c r="AI25">
-        <v>5120.7</v>
+        <v>1401.5767588915621</v>
       </c>
       <c r="AJ25">
-        <v>5809.4</v>
+        <v>1542.7056174057939</v>
       </c>
       <c r="AK25">
-        <v>5262.8</v>
+        <v>1507.3210482562963</v>
+      </c>
+      <c r="AL25">
+        <v>1532.7032977783192</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -21260,106 +21812,109 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>209.6</v>
+        <v>209.56138216034407</v>
       </c>
       <c r="F26">
-        <v>190.6</v>
+        <v>190.55471963944652</v>
       </c>
       <c r="G26">
-        <v>194.5</v>
+        <v>194.4600606175693</v>
       </c>
       <c r="H26">
-        <v>187.5</v>
+        <v>187.50547453439964</v>
       </c>
       <c r="I26">
-        <v>188.9</v>
+        <v>188.90996372053073</v>
       </c>
       <c r="J26">
-        <v>197</v>
+        <v>196.97695110732676</v>
       </c>
       <c r="K26">
-        <v>194.5</v>
+        <v>194.50390868163919</v>
       </c>
       <c r="L26">
-        <v>198.3</v>
+        <v>198.32773287034928</v>
       </c>
       <c r="M26">
-        <v>201.9</v>
+        <v>201.86846172746351</v>
       </c>
       <c r="N26">
-        <v>201.4</v>
+        <v>201.37127975456573</v>
       </c>
       <c r="O26">
-        <v>200.8</v>
+        <v>200.75258711219871</v>
       </c>
       <c r="P26">
-        <v>156.1</v>
+        <v>156.078089283613</v>
       </c>
       <c r="Q26">
-        <v>151.30000000000001</v>
+        <v>151.33094366084063</v>
       </c>
       <c r="R26">
-        <v>150</v>
+        <v>150.03768135681236</v>
       </c>
       <c r="S26">
-        <v>142.80000000000001</v>
+        <v>142.84628717468291</v>
       </c>
       <c r="T26">
-        <v>125.3</v>
+        <v>125.29676282784986</v>
       </c>
       <c r="U26">
-        <v>136.1</v>
+        <v>136.10504958731499</v>
       </c>
       <c r="V26">
-        <v>142.80000000000001</v>
+        <v>142.76749940221066</v>
       </c>
       <c r="W26">
-        <v>125.6</v>
+        <v>125.60675508491326</v>
       </c>
       <c r="X26">
-        <v>79.900000000000006</v>
+        <v>79.86662009268899</v>
       </c>
       <c r="Y26">
-        <v>17569</v>
+        <v>26.556236629723681</v>
       </c>
       <c r="Z26">
-        <v>17671.3</v>
+        <v>20.84449332056818</v>
       </c>
       <c r="AA26">
-        <v>19054.599999999999</v>
+        <v>21.685098220884186</v>
       </c>
       <c r="AB26">
-        <v>18468.8</v>
+        <v>13.434733870140763</v>
       </c>
       <c r="AC26">
-        <v>20466.2</v>
+        <v>19.643016607286224</v>
       </c>
       <c r="AD26">
-        <v>12873.5</v>
+        <v>13.618906363789428</v>
       </c>
       <c r="AE26">
-        <v>12381.2</v>
+        <v>21.235755718688885</v>
       </c>
       <c r="AF26">
-        <v>13549.4</v>
+        <v>23.828343501429057</v>
       </c>
       <c r="AG26">
-        <v>15649.4</v>
+        <v>12.932659192296663</v>
       </c>
       <c r="AH26">
-        <v>15068.8</v>
+        <v>14.8707310567885</v>
       </c>
       <c r="AI26">
-        <v>14024.8</v>
+        <v>10.747162063900886</v>
       </c>
       <c r="AJ26">
-        <v>14214.9</v>
+        <v>1.157161928771141</v>
       </c>
       <c r="AK26">
-        <v>13196</v>
+        <v>0.77403459983225387</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -21373,64 +21928,64 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>319</v>
+        <v>318.99485703626084</v>
       </c>
       <c r="F27">
-        <v>290.10000000000002</v>
+        <v>290.06286808349137</v>
       </c>
       <c r="G27">
-        <v>296</v>
+        <v>296.00758783171744</v>
       </c>
       <c r="H27">
-        <v>285.39999999999998</v>
+        <v>285.42129960209678</v>
       </c>
       <c r="I27">
-        <v>287.60000000000002</v>
+        <v>287.55921653373855</v>
       </c>
       <c r="J27">
-        <v>299.8</v>
+        <v>299.83880479392371</v>
       </c>
       <c r="K27">
-        <v>296.10000000000002</v>
+        <v>296.07433346388058</v>
       </c>
       <c r="L27">
-        <v>301.89999999999998</v>
+        <v>301.89496815255649</v>
       </c>
       <c r="M27">
-        <v>333.7</v>
+        <v>333.66411217580412</v>
       </c>
       <c r="N27">
-        <v>360.9</v>
+        <v>360.87387246250904</v>
       </c>
       <c r="O27">
-        <v>389.6</v>
+        <v>389.59553918052632</v>
       </c>
       <c r="P27">
-        <v>327.7</v>
+        <v>327.70793020163336</v>
       </c>
       <c r="Q27">
-        <v>343.5</v>
+        <v>343.53711598531743</v>
       </c>
       <c r="R27">
-        <v>279.2</v>
+        <v>279.24278840183888</v>
       </c>
       <c r="S27">
-        <v>212.2</v>
+        <v>212.1707675817822</v>
       </c>
       <c r="T27">
-        <v>142.69999999999999</v>
+        <v>142.67688474968514</v>
       </c>
       <c r="U27">
-        <v>111.3</v>
+        <v>111.34420043556769</v>
       </c>
       <c r="V27">
-        <v>74.3</v>
+        <v>74.323080571150854</v>
       </c>
       <c r="W27">
-        <v>65.400000000000006</v>
+        <v>65.38939897067543</v>
       </c>
       <c r="X27">
-        <v>41.6</v>
+        <v>41.577622812958673</v>
       </c>
       <c r="Y27">
         <v>0</v>
@@ -21466,13 +22021,16 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.6</v>
+        <v>1.7723813249885461</v>
       </c>
       <c r="AK27">
-        <v>10.199999999999999</v>
+        <v>9.3739696218662321</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -21486,106 +22044,109 @@
         <v>5</v>
       </c>
       <c r="E28">
-        <v>356.4</v>
+        <v>356.39717064614166</v>
       </c>
       <c r="F28">
-        <v>324.10000000000002</v>
+        <v>324.07289087645137</v>
       </c>
       <c r="G28">
-        <v>330.7</v>
+        <v>330.71463212029585</v>
       </c>
       <c r="H28">
-        <v>318.89999999999998</v>
+        <v>318.88709606615669</v>
       </c>
       <c r="I28">
-        <v>321.3</v>
+        <v>321.27568487474366</v>
       </c>
       <c r="J28">
-        <v>335</v>
+        <v>334.99506127250186</v>
       </c>
       <c r="K28">
-        <v>330.8</v>
+        <v>330.78920371269379</v>
       </c>
       <c r="L28">
-        <v>337.3</v>
+        <v>337.29231085894185</v>
       </c>
       <c r="M28">
-        <v>287.3</v>
+        <v>287.29020837094629</v>
       </c>
       <c r="N28">
-        <v>222.9</v>
+        <v>222.89165318604344</v>
       </c>
       <c r="O28">
-        <v>165</v>
+        <v>165.03303539120262</v>
       </c>
       <c r="P28">
-        <v>79.7</v>
+        <v>79.656226455331307</v>
       </c>
       <c r="Q28">
         <v>0</v>
       </c>
       <c r="R28">
-        <v>156.5</v>
+        <v>156.54400504383725</v>
       </c>
       <c r="S28">
-        <v>279.3</v>
+        <v>279.28147019699804</v>
       </c>
       <c r="T28">
-        <v>417.7</v>
+        <v>417.68834820342829</v>
       </c>
       <c r="U28">
-        <v>572.5</v>
+        <v>572.53235210326102</v>
       </c>
       <c r="V28">
-        <v>697</v>
+        <v>696.99318505286703</v>
       </c>
       <c r="W28">
-        <v>660.5</v>
+        <v>660.52712826355025</v>
       </c>
       <c r="X28">
-        <v>453.8</v>
+        <v>453.76074138513144</v>
       </c>
       <c r="Y28">
-        <v>292</v>
+        <v>291.98918152344709</v>
       </c>
       <c r="Z28">
-        <v>372</v>
+        <v>372.02137865737882</v>
       </c>
       <c r="AA28">
-        <v>441.5</v>
+        <v>441.49327968239794</v>
       </c>
       <c r="AB28">
-        <v>476.8</v>
+        <v>476.82371527961476</v>
       </c>
       <c r="AC28">
-        <v>494.1</v>
+        <v>494.06155672640546</v>
       </c>
       <c r="AD28">
-        <v>496.8</v>
+        <v>496.78339666703437</v>
       </c>
       <c r="AE28">
-        <v>0.1</v>
+        <v>0.11554473212613157</v>
       </c>
       <c r="AF28">
-        <v>0.1</v>
+        <v>0.10739611687659149</v>
       </c>
       <c r="AG28">
-        <v>0.1</v>
+        <v>0.11954807735996287</v>
       </c>
       <c r="AH28">
-        <v>0.1</v>
+        <v>0.15133088073748877</v>
       </c>
       <c r="AI28">
-        <v>120.9</v>
+        <v>133.20188114291781</v>
       </c>
       <c r="AJ28">
-        <v>118.7</v>
+        <v>132.52087015057168</v>
       </c>
       <c r="AK28">
-        <v>257.7</v>
+        <v>236.96076315280843</v>
+      </c>
+      <c r="AL28">
+        <v>606.82400586389758</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -21697,8 +22258,11 @@
       <c r="AK29">
         <v>0</v>
       </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -21712,106 +22276,109 @@
         <v>5</v>
       </c>
       <c r="E30">
-        <v>1020.3</v>
+        <v>1020.3255981122813</v>
       </c>
       <c r="F30">
-        <v>927.8</v>
+        <v>927.78476780837207</v>
       </c>
       <c r="G30">
-        <v>946.8</v>
+        <v>946.79933684899174</v>
       </c>
       <c r="H30">
-        <v>912.9</v>
+        <v>912.93841203649924</v>
       </c>
       <c r="I30">
-        <v>919.8</v>
+        <v>919.77667705512249</v>
       </c>
       <c r="J30">
-        <v>959.1</v>
+        <v>959.05373108838455</v>
       </c>
       <c r="K30">
-        <v>947</v>
+        <v>947.01282705284962</v>
       </c>
       <c r="L30">
-        <v>965.6</v>
+        <v>965.63050203762623</v>
       </c>
       <c r="M30">
-        <v>1093.5</v>
+        <v>1093.4996625247018</v>
       </c>
       <c r="N30">
-        <v>1237.8</v>
+        <v>1237.7599165604024</v>
       </c>
       <c r="O30">
-        <v>1657.9</v>
+        <v>1657.9474861862373</v>
       </c>
       <c r="P30">
-        <v>2230.1</v>
+        <v>2230.1311704232025</v>
       </c>
       <c r="Q30">
-        <v>2787.6</v>
+        <v>2787.5879203936543</v>
       </c>
       <c r="R30">
-        <v>2559.5</v>
+        <v>2559.5161514490542</v>
       </c>
       <c r="S30">
-        <v>2072.3000000000002</v>
+        <v>2072.3299895911105</v>
       </c>
       <c r="T30">
-        <v>1687.3</v>
+        <v>1687.3117438984102</v>
       </c>
       <c r="U30">
-        <v>1591.2</v>
+        <v>1591.1755959346349</v>
       </c>
       <c r="V30">
-        <v>1558.9</v>
+        <v>1558.9347342878348</v>
       </c>
       <c r="W30">
-        <v>1343.4</v>
+        <v>1343.4289363303658</v>
       </c>
       <c r="X30">
-        <v>897.1</v>
+        <v>897.0560361181075</v>
       </c>
       <c r="Y30">
-        <v>234.9</v>
+        <v>234.90409239887489</v>
       </c>
       <c r="Z30">
-        <v>296.10000000000002</v>
+        <v>296.05095177214878</v>
       </c>
       <c r="AA30">
-        <v>242.3</v>
+        <v>242.31970298029651</v>
       </c>
       <c r="AB30">
-        <v>242.4</v>
+        <v>242.37138666974587</v>
       </c>
       <c r="AC30">
-        <v>277.89999999999998</v>
+        <v>277.8620276522596</v>
       </c>
       <c r="AD30">
-        <v>225.2</v>
+        <v>225.224749866369</v>
       </c>
       <c r="AE30">
-        <v>268.3</v>
+        <v>268.32628705704184</v>
       </c>
       <c r="AF30">
-        <v>240.2</v>
+        <v>240.22900926403642</v>
       </c>
       <c r="AG30">
-        <v>194.2</v>
+        <v>194.23731169161758</v>
       </c>
       <c r="AH30">
-        <v>177.7</v>
+        <v>199.84693772187916</v>
       </c>
       <c r="AI30">
-        <v>133.4</v>
+        <v>146.97444575389724</v>
       </c>
       <c r="AJ30">
-        <v>118.4</v>
+        <v>132.14430723902163</v>
       </c>
       <c r="AK30">
-        <v>100</v>
+        <v>91.913475827475011</v>
+      </c>
+      <c r="AL30">
+        <v>6.0065396505253075</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -21923,8 +22490,11 @@
       <c r="AK31">
         <v>0</v>
       </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -22031,13 +22601,16 @@
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>34.9</v>
+        <v>39.003198275303802</v>
       </c>
       <c r="AK32">
-        <v>35.700000000000003</v>
+        <v>32.802266729810903</v>
+      </c>
+      <c r="AL32">
+        <v>135.15750817105049</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -22149,8 +22722,11 @@
       <c r="AK33">
         <v>0</v>
       </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -22164,106 +22740,109 @@
         <v>5</v>
       </c>
       <c r="E34">
-        <v>1001.4</v>
+        <v>1001.3874925946883</v>
       </c>
       <c r="F34">
-        <v>910.6</v>
+        <v>910.56429832012452</v>
       </c>
       <c r="G34">
-        <v>929.2</v>
+        <v>929.22594088753885</v>
       </c>
       <c r="H34">
-        <v>896</v>
+        <v>895.99350346006213</v>
       </c>
       <c r="I34">
-        <v>902.7</v>
+        <v>902.7048444999873</v>
       </c>
       <c r="J34">
-        <v>941.3</v>
+        <v>941.25288321198479</v>
       </c>
       <c r="K34">
-        <v>929.4</v>
+        <v>929.43546853276348</v>
       </c>
       <c r="L34">
-        <v>947.7</v>
+        <v>947.70758373348065</v>
       </c>
       <c r="M34">
-        <v>847.9</v>
+        <v>847.87768318583153</v>
       </c>
       <c r="N34">
-        <v>723.5</v>
+        <v>723.47330827843075</v>
       </c>
       <c r="O34">
-        <v>805.8</v>
+        <v>805.78373377007529</v>
       </c>
       <c r="P34">
-        <v>767.9</v>
+        <v>767.93493774225533</v>
       </c>
       <c r="Q34">
-        <v>769.3</v>
+        <v>769.34671987785646</v>
       </c>
       <c r="R34">
-        <v>598.1</v>
+        <v>598.09841610368608</v>
       </c>
       <c r="S34">
-        <v>726.5</v>
+        <v>726.52481237100892</v>
       </c>
       <c r="T34">
-        <v>621.9</v>
+        <v>621.91701200723423</v>
       </c>
       <c r="U34">
-        <v>603.29999999999995</v>
+        <v>603.25956752903767</v>
       </c>
       <c r="V34">
-        <v>589.70000000000005</v>
+        <v>589.7089923241673</v>
       </c>
       <c r="W34">
-        <v>569.5</v>
+        <v>569.49057260670907</v>
       </c>
       <c r="X34">
-        <v>337.9</v>
+        <v>337.86131420301768</v>
       </c>
       <c r="Y34">
-        <v>16.899999999999999</v>
+        <v>16.941779405519458</v>
       </c>
       <c r="Z34">
-        <v>20</v>
+        <v>19.962428617429214</v>
       </c>
       <c r="AA34">
-        <v>24.1</v>
+        <v>24.142926380100032</v>
       </c>
       <c r="AB34">
-        <v>19.2</v>
+        <v>19.161760857497008</v>
       </c>
       <c r="AC34">
         <v>0</v>
       </c>
       <c r="AD34">
-        <v>25.8</v>
+        <v>25.825923043057951</v>
       </c>
       <c r="AE34">
-        <v>24</v>
+        <v>24.02089603021394</v>
       </c>
       <c r="AF34">
-        <v>32</v>
+        <v>32.002787957362024</v>
       </c>
       <c r="AG34">
-        <v>32.1</v>
+        <v>32.136688383994411</v>
       </c>
       <c r="AH34">
-        <v>26.3</v>
+        <v>29.528008186627677</v>
       </c>
       <c r="AI34">
-        <v>24.5</v>
+        <v>26.937687581293719</v>
       </c>
       <c r="AJ34">
-        <v>26.8</v>
+        <v>29.946862504426193</v>
       </c>
       <c r="AK34">
-        <v>23.7</v>
+        <v>21.82378149016148</v>
+      </c>
+      <c r="AL34">
+        <v>62.144480158276345</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -22375,8 +22954,11 @@
       <c r="AK35">
         <v>0</v>
       </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -22488,8 +23070,11 @@
       <c r="AK36">
         <v>0</v>
       </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -22503,91 +23088,91 @@
         <v>5</v>
       </c>
       <c r="E37">
-        <v>1521.9</v>
+        <v>1521.8964202474906</v>
       </c>
       <c r="F37">
-        <v>1389.8</v>
+        <v>1389.8471357581784</v>
       </c>
       <c r="G37">
-        <v>1373</v>
+        <v>1373.0219182436615</v>
       </c>
       <c r="H37">
-        <v>1304.0999999999999</v>
+        <v>1304.0837051282292</v>
       </c>
       <c r="I37">
-        <v>1413</v>
+        <v>1413.0304736377732</v>
       </c>
       <c r="J37">
-        <v>1465.6</v>
+        <v>1465.6122388077781</v>
       </c>
       <c r="K37">
-        <v>1416.8</v>
+        <v>1416.7980270293547</v>
       </c>
       <c r="L37">
-        <v>1420.7</v>
+        <v>1420.6548086030332</v>
       </c>
       <c r="M37">
-        <v>1342.4</v>
+        <v>1342.3829633581527</v>
       </c>
       <c r="N37">
-        <v>1164.2</v>
+        <v>1164.1714034033951</v>
       </c>
       <c r="O37">
-        <v>1243</v>
+        <v>1243.0031211764524</v>
       </c>
       <c r="P37">
-        <v>1108.9000000000001</v>
+        <v>1108.8597193725975</v>
       </c>
       <c r="Q37">
-        <v>1116.5</v>
+        <v>1116.5147291507749</v>
       </c>
       <c r="R37">
-        <v>879.6</v>
+        <v>879.59977982616988</v>
       </c>
       <c r="S37">
-        <v>1011.4</v>
+        <v>1011.4488733031723</v>
       </c>
       <c r="T37">
-        <v>879.4</v>
+        <v>879.39695012273535</v>
       </c>
       <c r="U37">
-        <v>851</v>
+        <v>851.00615823826263</v>
       </c>
       <c r="V37">
-        <v>831.7</v>
+        <v>831.69313911959796</v>
       </c>
       <c r="W37">
-        <v>805.4</v>
+        <v>805.36014955183362</v>
       </c>
       <c r="X37">
-        <v>471.5</v>
+        <v>471.48993703805235</v>
       </c>
       <c r="Y37">
-        <v>33.6</v>
+        <v>89.106984680958462</v>
       </c>
       <c r="Z37">
-        <v>29.3</v>
+        <v>114.16138754888607</v>
       </c>
       <c r="AA37">
-        <v>18.2</v>
+        <v>96.01071631588151</v>
       </c>
       <c r="AB37">
-        <v>26</v>
+        <v>92.058056691236828</v>
       </c>
       <c r="AC37">
-        <v>21.8</v>
+        <v>79.816630206793079</v>
       </c>
       <c r="AD37">
-        <v>34.299999999999997</v>
+        <v>95.144985055491219</v>
       </c>
       <c r="AE37">
-        <v>18.3</v>
+        <v>61.439551220137972</v>
       </c>
       <c r="AF37">
-        <v>12.6</v>
+        <v>60.056339360385948</v>
       </c>
       <c r="AG37">
-        <v>5.9</v>
+        <v>5.9030004244345253</v>
       </c>
       <c r="AH37">
         <v>0</v>
@@ -22596,13 +23181,16 @@
         <v>0</v>
       </c>
       <c r="AJ37">
-        <v>14.5</v>
+        <v>16.189187649101282</v>
       </c>
       <c r="AK37">
-        <v>18.399999999999999</v>
+        <v>16.954871643225236</v>
+      </c>
+      <c r="AL37">
+        <v>44.343958825600204</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -22616,106 +23204,109 @@
         <v>5</v>
       </c>
       <c r="E38">
-        <v>15169.8</v>
+        <v>15169.83046923515</v>
       </c>
       <c r="F38">
-        <v>13699</v>
+        <v>13699.034041725556</v>
       </c>
       <c r="G38">
-        <v>13879</v>
+        <v>13879.003518810603</v>
       </c>
       <c r="H38">
-        <v>13207.1</v>
+        <v>13207.058566486494</v>
       </c>
       <c r="I38">
-        <v>13534.7</v>
+        <v>13534.655007971131</v>
       </c>
       <c r="J38">
-        <v>14027.1</v>
+        <v>14027.057175815555</v>
       </c>
       <c r="K38">
-        <v>13670.3</v>
+        <v>13670.287977099242</v>
       </c>
       <c r="L38">
-        <v>13912.3</v>
+        <v>13912.293622355002</v>
       </c>
       <c r="M38">
-        <v>13620.5</v>
+        <v>13620.506700241467</v>
       </c>
       <c r="N38">
-        <v>14038</v>
+        <v>14037.982347482341</v>
       </c>
       <c r="O38">
-        <v>14236.7</v>
+        <v>14236.739982105644</v>
       </c>
       <c r="P38">
-        <v>12396.8</v>
+        <v>12396.772509952238</v>
       </c>
       <c r="Q38">
-        <v>10603.5</v>
+        <v>10603.455611803971</v>
       </c>
       <c r="R38">
-        <v>8942</v>
+        <v>8941.9642088024775</v>
       </c>
       <c r="S38">
-        <v>10105</v>
+        <v>10105.027611157711</v>
       </c>
       <c r="T38">
-        <v>10722.4</v>
+        <v>10722.399267748282</v>
       </c>
       <c r="U38">
-        <v>10502.7</v>
+        <v>10502.702573549119</v>
       </c>
       <c r="V38">
-        <v>10961.5</v>
+        <v>10961.51470174327</v>
       </c>
       <c r="W38">
-        <v>10058.799999999999</v>
+        <v>10058.840439545407</v>
       </c>
       <c r="X38">
-        <v>4616.3</v>
+        <v>4616.2821142458633</v>
       </c>
       <c r="Y38">
-        <v>2035.7</v>
+        <v>9602.4697516316173</v>
       </c>
       <c r="Z38">
-        <v>1934.1</v>
+        <v>10625.722651632719</v>
       </c>
       <c r="AA38">
-        <v>1841.8</v>
+        <v>8235.4982844903952</v>
       </c>
       <c r="AB38">
-        <v>1786.2</v>
+        <v>7694.108954048851</v>
       </c>
       <c r="AC38">
-        <v>1727.4</v>
+        <v>8932.0372545628707</v>
       </c>
       <c r="AD38">
-        <v>1759.9</v>
+        <v>8143.7075266473221</v>
       </c>
       <c r="AE38">
-        <v>1556.4</v>
+        <v>7993.78466314246</v>
       </c>
       <c r="AF38">
-        <v>1249.4000000000001</v>
+        <v>7387.1609609921188</v>
       </c>
       <c r="AG38">
-        <v>1138.7</v>
+        <v>7807.7187512348655</v>
       </c>
       <c r="AH38">
-        <v>1437.2</v>
+        <v>8152.7993049778415</v>
       </c>
       <c r="AI38">
-        <v>1161.2</v>
+        <v>6681.2519430802222</v>
       </c>
       <c r="AJ38">
-        <v>5389.9</v>
+        <v>7666.115780353668</v>
       </c>
       <c r="AK38">
-        <v>5800.1</v>
+        <v>6850.1212855555477</v>
+      </c>
+      <c r="AL38">
+        <v>8529.1677131880751</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -22729,106 +23320,109 @@
         <v>5</v>
       </c>
       <c r="E39">
-        <v>226.7</v>
+        <v>226.68362652868475</v>
       </c>
       <c r="F39">
-        <v>206.1</v>
+        <v>206.12402177695009</v>
       </c>
       <c r="G39">
-        <v>210.3</v>
+        <v>210.34844922930674</v>
       </c>
       <c r="H39">
-        <v>202.8</v>
+        <v>202.82563764022979</v>
       </c>
       <c r="I39">
-        <v>204.3</v>
+        <v>204.34488082735911</v>
       </c>
       <c r="J39">
-        <v>213.1</v>
+        <v>213.07098263652219</v>
       </c>
       <c r="K39">
-        <v>210.4</v>
+        <v>210.39587990607143</v>
       </c>
       <c r="L39">
-        <v>214.5</v>
+        <v>214.53213022742926</v>
       </c>
       <c r="M39">
-        <v>237.9</v>
+        <v>237.9256417962049</v>
       </c>
       <c r="N39">
-        <v>258.10000000000002</v>
+        <v>258.12837295679219</v>
       </c>
       <c r="O39">
-        <v>279.5</v>
+        <v>279.45809629419756</v>
       </c>
       <c r="P39">
-        <v>235.7</v>
+        <v>235.66921928600351</v>
       </c>
       <c r="Q39">
-        <v>247.6</v>
+        <v>247.63245326319387</v>
       </c>
       <c r="R39">
-        <v>282.2</v>
+        <v>282.2008068719079</v>
       </c>
       <c r="S39">
-        <v>300.8</v>
+        <v>300.77322889935107</v>
       </c>
       <c r="T39">
-        <v>289.8</v>
+        <v>289.78553206390313</v>
       </c>
       <c r="U39">
-        <v>340.9</v>
+        <v>340.87418126370522</v>
       </c>
       <c r="V39">
-        <v>383</v>
+        <v>382.95282192592975</v>
       </c>
       <c r="W39">
-        <v>336.9</v>
+        <v>336.92164893364958</v>
       </c>
       <c r="X39">
-        <v>214.2</v>
+        <v>214.2304633074481</v>
       </c>
       <c r="Y39">
         <v>0</v>
       </c>
       <c r="Z39">
-        <v>11.6</v>
+        <v>11.570125555838827</v>
       </c>
       <c r="AA39">
-        <v>28.7</v>
+        <v>28.662574780322636</v>
       </c>
       <c r="AB39">
-        <v>20.7</v>
+        <v>20.704685475636417</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>9.9550578737855329</v>
       </c>
       <c r="AD39">
-        <v>11.5</v>
+        <v>11.496683238193466</v>
       </c>
       <c r="AE39">
-        <v>12.5</v>
+        <v>12.461527819096917</v>
       </c>
       <c r="AF39">
-        <v>18.600000000000001</v>
+        <v>18.616860657551928</v>
       </c>
       <c r="AG39">
-        <v>39.5</v>
+        <v>39.50379238656631</v>
       </c>
       <c r="AH39">
-        <v>61.8</v>
+        <v>69.44174293977774</v>
       </c>
       <c r="AI39">
-        <v>44.1</v>
+        <v>48.624247941588614</v>
       </c>
       <c r="AJ39">
-        <v>37.200000000000003</v>
+        <v>41.500196354739046</v>
       </c>
       <c r="AK39">
-        <v>14.2</v>
+        <v>13.099974929965569</v>
+      </c>
+      <c r="AL39">
+        <v>319.88574184503312</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>58</v>
       </c>
@@ -22842,106 +23436,109 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>1436.1</v>
+        <v>1436.1425148194919</v>
       </c>
       <c r="F40">
-        <v>1305.9000000000001</v>
+        <v>1305.8881910996679</v>
       </c>
       <c r="G40">
-        <v>1332.7</v>
+        <v>1332.6518350293375</v>
       </c>
       <c r="H40">
-        <v>1285</v>
+        <v>1284.9914472038276</v>
       </c>
       <c r="I40">
-        <v>1294.5999999999999</v>
+        <v>1294.616534665141</v>
       </c>
       <c r="J40">
-        <v>1349.9</v>
+        <v>1349.9003060988778</v>
       </c>
       <c r="K40">
-        <v>1333</v>
+        <v>1332.9523296546072</v>
       </c>
       <c r="L40">
-        <v>1359.2</v>
+        <v>1359.1573318835003</v>
       </c>
       <c r="M40">
-        <v>1055</v>
+        <v>1054.9513770155008</v>
       </c>
       <c r="N40">
-        <v>804.9</v>
+        <v>804.85482086997808</v>
       </c>
       <c r="O40">
-        <v>808.4</v>
+        <v>808.4309017030198</v>
       </c>
       <c r="P40">
-        <v>531</v>
+        <v>530.95611861798113</v>
       </c>
       <c r="Q40">
-        <v>321.5</v>
+        <v>321.49539798393255</v>
       </c>
       <c r="R40">
-        <v>344</v>
+        <v>344.0187379755032</v>
       </c>
       <c r="S40">
-        <v>373.7</v>
+        <v>373.70363589915934</v>
       </c>
       <c r="T40">
-        <v>350.7</v>
+        <v>350.69707776398701</v>
       </c>
       <c r="U40">
-        <v>428.5</v>
+        <v>428.5296288007583</v>
       </c>
       <c r="V40">
-        <v>487</v>
+        <v>486.97227590425371</v>
       </c>
       <c r="W40">
-        <v>473.1</v>
+        <v>473.12055881263967</v>
       </c>
       <c r="X40">
-        <v>336</v>
+        <v>336.01297842888232</v>
       </c>
       <c r="Y40">
-        <v>30.8</v>
+        <v>30.834390544262966</v>
       </c>
       <c r="Z40">
-        <v>31.1</v>
+        <v>31.051679315517365</v>
       </c>
       <c r="AA40">
-        <v>33.1</v>
+        <v>33.084791786251664</v>
       </c>
       <c r="AB40">
-        <v>35.799999999999997</v>
+        <v>35.832059523435461</v>
       </c>
       <c r="AC40">
-        <v>29.8</v>
+        <v>29.826786508732749</v>
       </c>
       <c r="AD40">
-        <v>40.1</v>
+        <v>40.079678948311177</v>
       </c>
       <c r="AE40">
-        <v>30.6</v>
+        <v>30.645991912259859</v>
       </c>
       <c r="AF40">
-        <v>30.8</v>
+        <v>30.820907808443586</v>
       </c>
       <c r="AG40">
-        <v>28.2</v>
+        <v>28.152461864611567</v>
       </c>
       <c r="AH40">
-        <v>27.7</v>
+        <v>31.135253918551257</v>
       </c>
       <c r="AI40">
-        <v>36.6</v>
+        <v>40.336103701980704</v>
       </c>
       <c r="AJ40">
-        <v>27.6</v>
+        <v>30.813574221908457</v>
       </c>
       <c r="AK40">
-        <v>28.5</v>
+        <v>26.201755567484518</v>
+      </c>
+      <c r="AL40">
+        <v>350.77416846678238</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -22955,106 +23552,109 @@
         <v>5</v>
       </c>
       <c r="E41">
-        <v>8956.7999999999993</v>
+        <v>8956.8168166318592</v>
       </c>
       <c r="F41">
-        <v>8093.7</v>
+        <v>8093.6779180750073</v>
       </c>
       <c r="G41">
-        <v>8133.4</v>
+        <v>8133.4180632302887</v>
       </c>
       <c r="H41">
-        <v>7638.8</v>
+        <v>7638.8373344154761</v>
       </c>
       <c r="I41">
-        <v>8480.7999999999993</v>
+        <v>8480.7710693505778</v>
       </c>
       <c r="J41">
-        <v>8718.9</v>
+        <v>8718.892334053151</v>
       </c>
       <c r="K41">
-        <v>8382.2000000000007</v>
+        <v>8382.1888740607446</v>
       </c>
       <c r="L41">
-        <v>8342.7999999999993</v>
+        <v>8342.7911039920818</v>
       </c>
       <c r="M41">
-        <v>7617.7</v>
+        <v>7617.6979177995945</v>
       </c>
       <c r="N41">
-        <v>7638.9</v>
+        <v>7638.8553335515153</v>
       </c>
       <c r="O41">
-        <v>7169</v>
+        <v>7168.9861283095624</v>
       </c>
       <c r="P41">
-        <v>5221.8999999999996</v>
+        <v>5221.8611706913916</v>
       </c>
       <c r="Q41">
-        <v>5754.8</v>
+        <v>5754.8315987489441</v>
       </c>
       <c r="R41">
-        <v>5351.2</v>
+        <v>5351.2375308730034</v>
       </c>
       <c r="S41">
-        <v>5437.9</v>
+        <v>5437.8508115032128</v>
       </c>
       <c r="T41">
-        <v>5277.4</v>
+        <v>5277.3910622817402</v>
       </c>
       <c r="U41">
-        <v>5452.7</v>
+        <v>5452.7118224895175</v>
       </c>
       <c r="V41">
-        <v>5562.8</v>
+        <v>5562.7905953080435</v>
       </c>
       <c r="W41">
-        <v>5351.1</v>
+        <v>5351.0902689240547</v>
       </c>
       <c r="X41">
-        <v>4271.3</v>
+        <v>4271.3257113209665</v>
       </c>
       <c r="Y41">
-        <v>1774.8</v>
+        <v>6367.5620952032332</v>
       </c>
       <c r="Z41">
-        <v>1607.7</v>
+        <v>7278.5763608521083</v>
       </c>
       <c r="AA41">
-        <v>1514.2</v>
+        <v>7297.3453260803153</v>
       </c>
       <c r="AB41">
-        <v>2010.6</v>
+        <v>7790.0814179236631</v>
       </c>
       <c r="AC41">
-        <v>1968.8</v>
+        <v>7142.8018690569716</v>
       </c>
       <c r="AD41">
-        <v>2032.7</v>
+        <v>6382.926301518627</v>
       </c>
       <c r="AE41">
-        <v>1481.7</v>
+        <v>6325.3450790933648</v>
       </c>
       <c r="AF41">
-        <v>1294.2</v>
+        <v>6046.4590054081755</v>
       </c>
       <c r="AG41">
-        <v>1122.5999999999999</v>
+        <v>7070.1067363149778</v>
       </c>
       <c r="AH41">
-        <v>1605.3</v>
+        <v>7554.7683305428345</v>
       </c>
       <c r="AI41">
-        <v>3701.3</v>
+        <v>7117.448209335791</v>
       </c>
       <c r="AJ41">
-        <v>3737</v>
+        <v>8422.0261489399381</v>
       </c>
       <c r="AK41">
-        <v>1584.8</v>
+        <v>8106.6041155327666</v>
+      </c>
+      <c r="AL41">
+        <v>7750.6701912303888</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>58</v>
       </c>
@@ -23166,8 +23766,11 @@
       <c r="AK42">
         <v>0</v>
       </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>58</v>
       </c>
@@ -23181,106 +23784,109 @@
         <v>5</v>
       </c>
       <c r="E43">
-        <v>1641.3</v>
+        <v>1641.2824022989971</v>
       </c>
       <c r="F43">
-        <v>1492.4</v>
+        <v>1492.4224339193447</v>
       </c>
       <c r="G43">
-        <v>1523</v>
+        <v>1523.0090208004415</v>
       </c>
       <c r="H43">
-        <v>1468.5</v>
+        <v>1468.5407803454984</v>
       </c>
       <c r="I43">
-        <v>1479.5</v>
+        <v>1479.5407239498613</v>
       </c>
       <c r="J43">
-        <v>1542.7</v>
+        <v>1542.7212789787729</v>
       </c>
       <c r="K43">
-        <v>1523.4</v>
+        <v>1523.3524383480394</v>
       </c>
       <c r="L43">
-        <v>1553.3</v>
+        <v>1553.3005866457688</v>
       </c>
       <c r="M43">
-        <v>1409</v>
+        <v>1408.9967548175812</v>
       </c>
       <c r="N43">
-        <v>1244.7</v>
+        <v>1244.6574415869366</v>
       </c>
       <c r="O43">
-        <v>1249.5</v>
+        <v>1249.4955416932733</v>
       </c>
       <c r="P43">
-        <v>1177.3</v>
+        <v>1177.2597269381865</v>
       </c>
       <c r="Q43">
-        <v>904.4</v>
+        <v>904.39796475356661</v>
       </c>
       <c r="R43">
-        <v>1333.2</v>
+        <v>1333.2256147295736</v>
       </c>
       <c r="S43">
-        <v>1517.6</v>
+        <v>1517.6132252459072</v>
       </c>
       <c r="T43">
-        <v>1620.7</v>
+        <v>1620.6903894106345</v>
       </c>
       <c r="U43">
-        <v>1921.4</v>
+        <v>1921.4200214975717</v>
       </c>
       <c r="V43">
-        <v>2300.8000000000002</v>
+        <v>2300.7515889195784</v>
       </c>
       <c r="W43">
-        <v>1982.7</v>
+        <v>1982.6976664771262</v>
       </c>
       <c r="X43">
-        <v>1323.9</v>
+        <v>1323.9188627043345</v>
       </c>
       <c r="Y43">
-        <v>75.5</v>
+        <v>75.501444233162047</v>
       </c>
       <c r="Z43">
-        <v>125.9</v>
+        <v>122.65241518078541</v>
       </c>
       <c r="AA43">
-        <v>106.2</v>
+        <v>100.71132739627402</v>
       </c>
       <c r="AB43">
-        <v>113.6</v>
+        <v>108.58456593607501</v>
       </c>
       <c r="AC43">
-        <v>59.5</v>
+        <v>54.921757393544986</v>
       </c>
       <c r="AD43">
-        <v>99.8</v>
+        <v>93.221789930719453</v>
       </c>
       <c r="AE43">
-        <v>56.8</v>
+        <v>50.660957771519541</v>
       </c>
       <c r="AF43">
-        <v>65.2</v>
+        <v>60.850932625711259</v>
       </c>
       <c r="AG43">
-        <v>38</v>
+        <v>32.731745416116645</v>
       </c>
       <c r="AH43">
-        <v>55.5</v>
+        <v>56.688676899445738</v>
       </c>
       <c r="AI43">
-        <v>161.1</v>
+        <v>177.46310266807123</v>
       </c>
       <c r="AJ43">
-        <v>155.1</v>
+        <v>173.10589387491996</v>
       </c>
       <c r="AK43">
-        <v>350.5</v>
+        <v>322.19283211956565</v>
+      </c>
+      <c r="AL43">
+        <v>2.6664611652349643</v>
       </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -23392,8 +23998,11 @@
       <c r="AK44">
         <v>0</v>
       </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -23407,106 +24016,109 @@
         <v>5</v>
       </c>
       <c r="E45">
-        <v>3452.3</v>
+        <v>3452.3080760995163</v>
       </c>
       <c r="F45">
-        <v>3133.1</v>
+        <v>3133.0939680115603</v>
       </c>
       <c r="G45">
-        <v>3194.6</v>
+        <v>3194.5887422016199</v>
       </c>
       <c r="H45">
-        <v>3080.3</v>
+        <v>3080.3388425697435</v>
       </c>
       <c r="I45">
-        <v>3103.4</v>
+        <v>3103.4117827318987</v>
       </c>
       <c r="J45">
-        <v>3235.9</v>
+        <v>3235.936204494898</v>
       </c>
       <c r="K45">
-        <v>3195.3</v>
+        <v>3195.3090779425429</v>
       </c>
       <c r="L45">
-        <v>3258.1</v>
+        <v>3258.126839423318</v>
       </c>
       <c r="M45">
-        <v>3237.3</v>
+        <v>3237.313300505456</v>
       </c>
       <c r="N45">
-        <v>3109.3</v>
+        <v>3109.2847442718503</v>
       </c>
       <c r="O45">
-        <v>3187.2</v>
+        <v>3187.1823260094011</v>
       </c>
       <c r="P45">
-        <v>2819.9</v>
+        <v>2819.853035720238</v>
       </c>
       <c r="Q45">
-        <v>3136.8</v>
+        <v>3136.8318581183521</v>
       </c>
       <c r="R45">
-        <v>3206.8</v>
+        <v>3206.78153972464</v>
       </c>
       <c r="S45">
-        <v>3127.4</v>
+        <v>3127.3993147233127</v>
       </c>
       <c r="T45">
-        <v>3384.3</v>
+        <v>3384.2809432788749</v>
       </c>
       <c r="U45">
-        <v>3752.7</v>
+        <v>3752.720910870954</v>
       </c>
       <c r="V45">
-        <v>3921.2</v>
+        <v>3921.2257183536608</v>
       </c>
       <c r="W45">
-        <v>3716.1</v>
+        <v>3716.0707142651081</v>
       </c>
       <c r="X45">
-        <v>2552.8000000000002</v>
+        <v>2552.8202100909239</v>
       </c>
       <c r="Y45">
-        <v>228.1</v>
+        <v>228.08731177013937</v>
       </c>
       <c r="Z45">
-        <v>138.19999999999999</v>
+        <v>138.23058824195431</v>
       </c>
       <c r="AA45">
-        <v>106.8</v>
+        <v>106.83605882262489</v>
       </c>
       <c r="AB45">
-        <v>114.7</v>
+        <v>114.73643116535402</v>
       </c>
       <c r="AC45">
-        <v>118.6</v>
+        <v>118.60857216953609</v>
       </c>
       <c r="AD45">
-        <v>94</v>
+        <v>93.953808212996123</v>
       </c>
       <c r="AE45">
-        <v>116.2</v>
+        <v>116.19940971672997</v>
       </c>
       <c r="AF45">
-        <v>110.5</v>
+        <v>110.52482614711802</v>
       </c>
       <c r="AG45">
-        <v>129.5</v>
+        <v>129.51192845466323</v>
       </c>
       <c r="AH45">
-        <v>98.4</v>
+        <v>110.65608492858433</v>
       </c>
       <c r="AI45">
-        <v>128</v>
+        <v>140.95461258382161</v>
       </c>
       <c r="AJ45">
-        <v>118.1</v>
+        <v>131.82291590582929</v>
       </c>
       <c r="AK45">
-        <v>158.4</v>
+        <v>145.61319607256303</v>
+      </c>
+      <c r="AL45">
+        <v>208.08746798600444</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -23520,106 +24132,109 @@
         <v>5</v>
       </c>
       <c r="E46">
-        <v>4539.3999999999996</v>
+        <v>4539.433077913206</v>
       </c>
       <c r="F46">
-        <v>4127.7</v>
+        <v>4127.7185164866178</v>
       </c>
       <c r="G46">
-        <v>4212.3</v>
+        <v>4212.3144178586372</v>
       </c>
       <c r="H46">
-        <v>4061.7</v>
+        <v>4061.6670142975186</v>
       </c>
       <c r="I46">
-        <v>4092.1</v>
+        <v>4092.0904854703545</v>
       </c>
       <c r="J46">
-        <v>4266.8</v>
+        <v>4266.8342717788046</v>
       </c>
       <c r="K46">
-        <v>4213.3</v>
+        <v>4213.2642367154758</v>
       </c>
       <c r="L46">
-        <v>4296.1000000000004</v>
+        <v>4296.0943546857525</v>
       </c>
       <c r="M46">
-        <v>3715</v>
+        <v>3715.0057531238613</v>
       </c>
       <c r="N46">
-        <v>3063</v>
+        <v>3063.0191929732937</v>
       </c>
       <c r="O46">
-        <v>3205.3</v>
+        <v>3205.3300318432157</v>
       </c>
       <c r="P46">
-        <v>3068.6</v>
+        <v>3068.6076357390752</v>
       </c>
       <c r="Q46">
-        <v>2941.2</v>
+        <v>2941.1901375972866</v>
       </c>
       <c r="R46">
-        <v>2718.4</v>
+        <v>2718.4002848847103</v>
       </c>
       <c r="S46">
-        <v>2710</v>
+        <v>2710.0123454488025</v>
       </c>
       <c r="T46">
-        <v>2446.4</v>
+        <v>2446.4076231631238</v>
       </c>
       <c r="U46">
-        <v>2654.4</v>
+        <v>2654.3516464556678</v>
       </c>
       <c r="V46">
-        <v>3000.8</v>
+        <v>3000.7930888800088</v>
       </c>
       <c r="W46">
-        <v>2411.6</v>
+        <v>2411.6426837682252</v>
       </c>
       <c r="X46">
-        <v>1470.4</v>
+        <v>1470.4176690353299</v>
       </c>
       <c r="Y46">
-        <v>261.3</v>
+        <v>261.25139111476653</v>
       </c>
       <c r="Z46">
-        <v>286.5</v>
+        <v>286.54878558917903</v>
       </c>
       <c r="AA46">
-        <v>302.10000000000002</v>
+        <v>302.08063739828117</v>
       </c>
       <c r="AB46">
-        <v>234.3</v>
+        <v>234.32600610652483</v>
       </c>
       <c r="AC46">
-        <v>201.8</v>
+        <v>201.84758089707168</v>
       </c>
       <c r="AD46">
-        <v>248.3</v>
+        <v>248.25115991030114</v>
       </c>
       <c r="AE46">
-        <v>1407.6</v>
+        <v>280.30229932685995</v>
       </c>
       <c r="AF46">
-        <v>4354.7</v>
+        <v>275.98030861921569</v>
       </c>
       <c r="AG46">
-        <v>4970.8</v>
+        <v>281.94100126849941</v>
       </c>
       <c r="AH46">
-        <v>4867.5</v>
+        <v>396.77570446158256</v>
       </c>
       <c r="AI46">
-        <v>4069.8</v>
+        <v>340.04204498695003</v>
       </c>
       <c r="AJ46">
-        <v>4204.7</v>
+        <v>338.67044100165339</v>
       </c>
       <c r="AK46">
-        <v>4679.6000000000004</v>
+        <v>347.32405590695276</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -23633,40 +24248,40 @@
         <v>5</v>
       </c>
       <c r="E47">
-        <v>546.1</v>
+        <v>546.05280005253678</v>
       </c>
       <c r="F47">
-        <v>513.70000000000005</v>
+        <v>513.65890872524221</v>
       </c>
       <c r="G47">
-        <v>479.8</v>
+        <v>479.79651388706628</v>
       </c>
       <c r="H47">
-        <v>424.5</v>
+        <v>424.45656249443095</v>
       </c>
       <c r="I47">
-        <v>496</v>
+        <v>496.02044789413952</v>
       </c>
       <c r="J47">
-        <v>503</v>
+        <v>502.95840096752164</v>
       </c>
       <c r="K47">
-        <v>485.9</v>
+        <v>485.85829896610068</v>
       </c>
       <c r="L47">
-        <v>476.4</v>
+        <v>476.44387863605391</v>
       </c>
       <c r="M47">
-        <v>407.2</v>
+        <v>407.18851443220024</v>
       </c>
       <c r="N47">
-        <v>282.8</v>
+        <v>282.76940476682222</v>
       </c>
       <c r="O47">
-        <v>276.89999999999998</v>
+        <v>276.85788119931095</v>
       </c>
       <c r="P47">
-        <v>110.3</v>
+        <v>110.30739734475549</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -23726,13 +24341,16 @@
         <v>0</v>
       </c>
       <c r="AJ47">
-        <v>37.200000000000003</v>
+        <v>41.475965898284805</v>
       </c>
       <c r="AK47">
-        <v>51</v>
+        <v>46.907587397196821</v>
+      </c>
+      <c r="AL47">
+        <v>129.87234655622791</v>
       </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>58</v>
       </c>
@@ -23746,106 +24364,109 @@
         <v>5</v>
       </c>
       <c r="E48">
-        <v>1629</v>
+        <v>1629.019735301825</v>
       </c>
       <c r="F48">
-        <v>1511</v>
+        <v>1510.97715776717</v>
       </c>
       <c r="G48">
-        <v>1513.5</v>
+        <v>1513.4811770905285</v>
       </c>
       <c r="H48">
-        <v>1434.1</v>
+        <v>1434.1416631452887</v>
       </c>
       <c r="I48">
-        <v>1511.1</v>
+        <v>1511.0879772312367</v>
       </c>
       <c r="J48">
-        <v>1564</v>
+        <v>1564.0121166389049</v>
       </c>
       <c r="K48">
-        <v>1528.3</v>
+        <v>1528.2676031076744</v>
       </c>
       <c r="L48">
-        <v>1544.3</v>
+        <v>1544.3494526568704</v>
       </c>
       <c r="M48">
-        <v>1411.7</v>
+        <v>1411.7415200679507</v>
       </c>
       <c r="N48">
-        <v>1205.2</v>
+        <v>1205.1506293632592</v>
       </c>
       <c r="O48">
-        <v>1111.4000000000001</v>
+        <v>1111.4347321218115</v>
       </c>
       <c r="P48">
-        <v>866.6</v>
+        <v>866.58467483609229</v>
       </c>
       <c r="Q48">
-        <v>537.20000000000005</v>
+        <v>537.18817498956685</v>
       </c>
       <c r="R48">
-        <v>825.2</v>
+        <v>825.1829424640689</v>
       </c>
       <c r="S48">
-        <v>945.7</v>
+        <v>945.69813001486159</v>
       </c>
       <c r="T48">
-        <v>1058.5999999999999</v>
+        <v>1058.5797281845873</v>
       </c>
       <c r="U48">
-        <v>1241.2</v>
+        <v>1241.2493566956239</v>
       </c>
       <c r="V48">
-        <v>1517.2</v>
+        <v>1517.174148894572</v>
       </c>
       <c r="W48">
-        <v>1343.4</v>
+        <v>1343.4094751487014</v>
       </c>
       <c r="X48">
-        <v>873.9</v>
+        <v>873.86626864543973</v>
       </c>
       <c r="Y48">
-        <v>238</v>
+        <v>238.04949344859963</v>
       </c>
       <c r="Z48">
-        <v>201.6</v>
+        <v>201.55556429999473</v>
       </c>
       <c r="AA48">
-        <v>132.9</v>
+        <v>132.90246943229806</v>
       </c>
       <c r="AB48">
-        <v>198.7</v>
+        <v>198.69585988706945</v>
       </c>
       <c r="AC48">
-        <v>244.1</v>
+        <v>244.06899976701578</v>
       </c>
       <c r="AD48">
-        <v>286.10000000000002</v>
+        <v>286.06716628961635</v>
       </c>
       <c r="AE48">
-        <v>217.3</v>
+        <v>217.29767720795923</v>
       </c>
       <c r="AF48">
-        <v>153.9</v>
+        <v>153.90097209266645</v>
       </c>
       <c r="AG48">
-        <v>145.1</v>
+        <v>145.08823892350051</v>
       </c>
       <c r="AH48">
-        <v>230.9</v>
+        <v>237.7532935958572</v>
       </c>
       <c r="AI48">
-        <v>261.39999999999998</v>
+        <v>273.13471838992962</v>
       </c>
       <c r="AJ48">
-        <v>295.7</v>
+        <v>310.87452971124219</v>
       </c>
       <c r="AK48">
-        <v>266.60000000000002</v>
+        <v>261.58747765982912</v>
+      </c>
+      <c r="AL48">
+        <v>429.95529990534391</v>
       </c>
     </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -23957,8 +24578,11 @@
       <c r="AK49">
         <v>0</v>
       </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -23972,106 +24596,109 @@
         <v>5</v>
       </c>
       <c r="E50">
-        <v>497.3</v>
+        <v>497.34965755882297</v>
       </c>
       <c r="F50">
-        <v>452.2</v>
+        <v>452.24136041621455</v>
       </c>
       <c r="G50">
-        <v>461.5</v>
+        <v>461.50986197932065</v>
       </c>
       <c r="H50">
-        <v>445</v>
+        <v>445.00462150385329</v>
       </c>
       <c r="I50">
-        <v>448.3</v>
+        <v>448.3378798006176</v>
       </c>
       <c r="J50">
-        <v>467.5</v>
+        <v>467.48316970562752</v>
       </c>
       <c r="K50">
-        <v>461.6</v>
+        <v>461.61392609373405</v>
       </c>
       <c r="L50">
-        <v>470.7</v>
+        <v>470.68896478270864</v>
       </c>
       <c r="M50">
-        <v>327.5</v>
+        <v>327.46044403605646</v>
       </c>
       <c r="N50">
-        <v>213</v>
+        <v>213.0192062220722</v>
       </c>
       <c r="O50">
-        <v>165.3</v>
+        <v>165.2647593928701</v>
       </c>
       <c r="P50">
-        <v>64.5</v>
+        <v>64.499305600052622</v>
       </c>
       <c r="Q50">
         <v>0</v>
       </c>
       <c r="R50">
-        <v>82.4</v>
+        <v>82.381322096518659</v>
       </c>
       <c r="S50">
-        <v>151.30000000000001</v>
+        <v>151.27309197876934</v>
       </c>
       <c r="T50">
-        <v>184.4</v>
+        <v>184.39523187245666</v>
       </c>
       <c r="U50">
-        <v>264.89999999999998</v>
+        <v>264.91359335598844</v>
       </c>
       <c r="V50">
-        <v>336.5</v>
+        <v>336.52381164295724</v>
       </c>
       <c r="W50">
-        <v>327</v>
+        <v>326.95153645580388</v>
       </c>
       <c r="X50">
-        <v>232.2</v>
+        <v>232.20288681202621</v>
       </c>
       <c r="Y50">
-        <v>58.6</v>
+        <v>58.618473913399086</v>
       </c>
       <c r="Z50">
-        <v>94</v>
+        <v>94.041151082785063</v>
       </c>
       <c r="AA50">
-        <v>91.2</v>
+        <v>91.151257588999442</v>
       </c>
       <c r="AB50">
-        <v>95.6</v>
+        <v>95.635899089671113</v>
       </c>
       <c r="AC50">
-        <v>111.4</v>
+        <v>111.37783604620694</v>
       </c>
       <c r="AD50">
-        <v>74.5</v>
+        <v>74.528217681162801</v>
       </c>
       <c r="AE50">
-        <v>62</v>
+        <v>61.969884198717857</v>
       </c>
       <c r="AF50">
-        <v>129.1</v>
+        <v>129.07381915145388</v>
       </c>
       <c r="AG50">
-        <v>90.2</v>
+        <v>90.16663905301769</v>
       </c>
       <c r="AH50">
-        <v>131.19999999999999</v>
+        <v>147.51364525434059</v>
       </c>
       <c r="AI50">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AJ50">
-        <v>39.299999999999997</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>33.200000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>47.530657317329741</v>
       </c>
     </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -24085,106 +24712,109 @@
         <v>5</v>
       </c>
       <c r="E51">
-        <v>1738.4</v>
+        <v>1738.3730817661576</v>
       </c>
       <c r="F51">
-        <v>1580.7</v>
+        <v>1580.7072458190496</v>
       </c>
       <c r="G51">
-        <v>1613.1</v>
+        <v>1613.103193781888</v>
       </c>
       <c r="H51">
-        <v>1555.4</v>
+        <v>1555.4128640218114</v>
       </c>
       <c r="I51">
-        <v>1567.1</v>
+        <v>1567.0635134383811</v>
       </c>
       <c r="J51">
-        <v>1634</v>
+        <v>1633.9815380266302</v>
       </c>
       <c r="K51">
-        <v>1613.5</v>
+        <v>1613.4669263240232</v>
       </c>
       <c r="L51">
-        <v>1645.2</v>
+        <v>1645.1866686283279</v>
       </c>
       <c r="M51">
-        <v>1814.5</v>
+        <v>1814.4770701284247</v>
       </c>
       <c r="N51">
-        <v>1958.7</v>
+        <v>1958.6901267454255</v>
       </c>
       <c r="O51">
-        <v>2110.9</v>
+        <v>2110.8955762175437</v>
       </c>
       <c r="P51">
-        <v>1772.7</v>
+        <v>1772.7474832922107</v>
       </c>
       <c r="Q51">
-        <v>1855.7</v>
+        <v>1855.6560119530359</v>
       </c>
       <c r="R51">
-        <v>1809.5</v>
+        <v>1809.4544441758514</v>
       </c>
       <c r="S51">
-        <v>1696.2</v>
+        <v>1696.1763196114637</v>
       </c>
       <c r="T51">
-        <v>1466.3</v>
+        <v>1466.314941005465</v>
       </c>
       <c r="U51">
-        <v>1571.2</v>
+        <v>1571.2203144463156</v>
       </c>
       <c r="V51">
-        <v>1627.1</v>
+        <v>1627.1295887751951</v>
       </c>
       <c r="W51">
-        <v>1431.5</v>
+        <v>1431.5475763354082</v>
       </c>
       <c r="X51">
-        <v>910.2</v>
+        <v>910.24456723285243</v>
       </c>
       <c r="Y51">
-        <v>55.6</v>
+        <v>55.585975123395663</v>
       </c>
       <c r="Z51">
-        <v>58.7</v>
+        <v>58.745726462050364</v>
       </c>
       <c r="AA51">
-        <v>54.4</v>
+        <v>54.376417068642546</v>
       </c>
       <c r="AB51">
-        <v>50.9</v>
+        <v>50.895153521223691</v>
       </c>
       <c r="AC51">
-        <v>62.7</v>
+        <v>62.651525980984204</v>
       </c>
       <c r="AD51">
-        <v>57.8</v>
+        <v>57.820150796483496</v>
       </c>
       <c r="AE51">
-        <v>62.4</v>
+        <v>62.449480214922183</v>
       </c>
       <c r="AF51">
-        <v>53.5</v>
+        <v>53.499579538751654</v>
       </c>
       <c r="AG51">
-        <v>43.8</v>
+        <v>43.799565636963862</v>
       </c>
       <c r="AH51">
-        <v>37.5</v>
+        <v>42.180043667376424</v>
       </c>
       <c r="AI51">
-        <v>58.6</v>
+        <v>0</v>
       </c>
       <c r="AJ51">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>52.6</v>
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>58.427026721518601</v>
       </c>
     </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -24198,106 +24828,109 @@
         <v>5</v>
       </c>
       <c r="E52">
-        <v>2301.6</v>
+        <v>2301.6193380842774</v>
       </c>
       <c r="F52">
-        <v>2121.9</v>
+        <v>2121.8567004640181</v>
       </c>
       <c r="G52">
-        <v>2077.9</v>
+        <v>2077.8733272585896</v>
       </c>
       <c r="H52">
-        <v>1976.2</v>
+        <v>1976.1547141794254</v>
       </c>
       <c r="I52">
-        <v>2105.1999999999998</v>
+        <v>2105.1943905964777</v>
       </c>
       <c r="J52">
-        <v>2184.3000000000002</v>
+        <v>2184.3322624720872</v>
       </c>
       <c r="K52">
-        <v>2101.6999999999998</v>
+        <v>2101.6548718731869</v>
       </c>
       <c r="L52">
-        <v>2025.1</v>
+        <v>2025.1420445551546</v>
       </c>
       <c r="M52">
-        <v>1923.3</v>
+        <v>1923.3187649552849</v>
       </c>
       <c r="N52">
-        <v>1564.6</v>
+        <v>1564.6059813872844</v>
       </c>
       <c r="O52">
-        <v>1332.4</v>
+        <v>1332.3746253758407</v>
       </c>
       <c r="P52">
-        <v>845.7</v>
+        <v>845.73077711193389</v>
       </c>
       <c r="Q52">
-        <v>243.1</v>
+        <v>243.09282318905738</v>
       </c>
       <c r="R52">
-        <v>271.8</v>
+        <v>271.84926914685013</v>
       </c>
       <c r="S52">
-        <v>257.39999999999998</v>
+        <v>257.42754393915567</v>
       </c>
       <c r="T52">
-        <v>272.8</v>
+        <v>272.80873208223278</v>
       </c>
       <c r="U52">
-        <v>276.3</v>
+        <v>276.28118470008599</v>
       </c>
       <c r="V52">
-        <v>375</v>
+        <v>374.98398386522297</v>
       </c>
       <c r="W52">
-        <v>393.9</v>
+        <v>393.91740380163111</v>
       </c>
       <c r="X52">
-        <v>223.9</v>
+        <v>223.85965993344917</v>
       </c>
       <c r="Y52">
-        <v>279.39999999999998</v>
+        <v>626.71888269717442</v>
       </c>
       <c r="Z52">
-        <v>234.6</v>
+        <v>717.19817442992303</v>
       </c>
       <c r="AA52">
-        <v>103.2</v>
+        <v>420.98546747979492</v>
       </c>
       <c r="AB52">
-        <v>130.5</v>
+        <v>388.66886585656664</v>
       </c>
       <c r="AC52">
-        <v>140</v>
+        <v>441.08858436955705</v>
       </c>
       <c r="AD52">
-        <v>158.80000000000001</v>
+        <v>407.96350750876906</v>
       </c>
       <c r="AE52">
-        <v>100</v>
+        <v>331.17564951399049</v>
       </c>
       <c r="AF52">
-        <v>70.400000000000006</v>
+        <v>285.06994393881234</v>
       </c>
       <c r="AG52">
-        <v>50.7</v>
+        <v>308.17256600589508</v>
       </c>
       <c r="AH52">
-        <v>117</v>
+        <v>390.666903681002</v>
       </c>
       <c r="AI52">
-        <v>124.4</v>
+        <v>406.39852771329987</v>
       </c>
       <c r="AJ52">
-        <v>162.69999999999999</v>
+        <v>474.71312383952244</v>
       </c>
       <c r="AK52">
-        <v>148.6</v>
+        <v>98.099451615241847</v>
+      </c>
+      <c r="AL52">
+        <v>87.81504859555379</v>
       </c>
     </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -24407,6 +25040,9 @@
         <v>0</v>
       </c>
       <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
         <v>0</v>
       </c>
     </row>

--- a/data/ippu_distributions.xlsx
+++ b/data/ippu_distributions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/camobreco_vincent_epa_gov/Documents/GHG Inventory/State Level Data/FFC CO2 Inv State Breakout/2023 Calculations/IPPU Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcorra\OneDrive - Environmental Protection Agency (EPA)\Profile\Documents\Fossil Fuels\Fossil Fuels\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{9D33E2AA-93A9-4101-9189-96289A8CFCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46DB89C9-D887-4D25-8249-36672B369FE1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099CDE5D-BDE4-4B17-9FE2-7341EA0FB58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="3" xr2:uid="{FB5909C3-F38C-4901-A615-5D51A8770A5A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{FB5909C3-F38C-4901-A615-5D51A8770A5A}"/>
   </bookViews>
   <sheets>
     <sheet name="ammonia" sheetId="1" r:id="rId1"/>
@@ -284,9 +284,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -324,7 +324,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -430,7 +430,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -572,7 +572,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -581,9 +581,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84074A0-088C-4684-B63F-D6368A9563AD}">
   <dimension ref="A1:AK53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +696,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -809,7 +809,7 @@
         <v>12210.56328547</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>117.92595962610604</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>317.18525397226534</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>685.23351990460685</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>1948.8607452207436</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>278.27528493332221</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>337.21972659991872</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>3991.9076144291653</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>431.06524449568587</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>236.52586217512305</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>254.41701199270861</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>530.77576603612806</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>1992.2473644612269</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>63.182194645899244</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>32.276810979282665</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>228.7525549861079</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>406.5281013484032</v>
       </c>
     </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -6580,9 +6580,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF8D813B-F6D2-4258-9AD6-288120984E5F}">
   <dimension ref="A1:AL53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>30545.392800000001</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>258.71431663500158</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -8438,7 +8438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>298.93460955724976</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>84.620293554562863</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>180.43985748057531</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>8959.3282780872469</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -9946,7 +9946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -10990,7 +10990,7 @@
         <v>283.95819953333478</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>209.92342054881942</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>815.27620788340846</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -11570,7 +11570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>60</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>47.887692146815851</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>19406.309924572986</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -12266,7 +12266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -12738,9 +12738,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2228759-CE77-4D2C-B113-C568283D079F}">
   <dimension ref="A1:AL53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -13088,7 +13088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -13436,7 +13436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -13552,7 +13552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -13900,7 +13900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -14596,7 +14596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -14828,7 +14828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -14944,7 +14944,7 @@
         <v>84.620293554562863</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -15176,7 +15176,7 @@
         <v>1196.0753031269942</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -15408,7 +15408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -15872,7 +15872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -16220,7 +16220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -16452,7 +16452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -16684,7 +16684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -16916,7 +16916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -17032,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>136.69432035737077</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -17264,7 +17264,7 @@
         <v>209.92342054881942</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -17380,7 +17380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>60</v>
       </c>
@@ -17496,7 +17496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -17612,7 +17612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -17728,7 +17728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>60</v>
       </c>
@@ -17960,7 +17960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -18076,7 +18076,7 @@
         <v>922.68666241225276</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -18192,7 +18192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -18308,7 +18308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -18656,7 +18656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -18896,9 +18896,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC59C81A-71AC-4FBD-8F6E-E86A5690562B}">
   <dimension ref="A1:AL53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -19014,7 +19014,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -19130,7 +19130,7 @@
         <v>46248.117014659168</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -19246,7 +19246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -19362,7 +19362,7 @@
         <v>595.44632988723401</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -19478,7 +19478,7 @@
         <v>342.4666024235778</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -19594,7 +19594,7 @@
         <v>15.852173310472688</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -19710,7 +19710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -19826,7 +19826,7 @@
         <v>54.266667273249958</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -20058,7 +20058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -20174,7 +20174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -20290,7 +20290,7 @@
         <v>23.016537184854997</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -20406,7 +20406,7 @@
         <v>20.089234415852697</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -20522,7 +20522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -20638,7 +20638,7 @@
         <v>74.689200589508786</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -20870,7 +20870,7 @@
         <v>2096.5081351919112</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>22723.750220957354</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -21102,7 +21102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -21218,7 +21218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -21334,7 +21334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -21566,7 +21566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -21682,7 +21682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -21798,7 +21798,7 @@
         <v>1532.7032977783192</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -21914,7 +21914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -22030,7 +22030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -22146,7 +22146,7 @@
         <v>606.82400586389758</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -22262,7 +22262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -22378,7 +22378,7 @@
         <v>6.0065396505253075</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -22494,7 +22494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -22610,7 +22610,7 @@
         <v>135.15750817105049</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -22726,7 +22726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>62.144480158276345</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -22958,7 +22958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -23074,7 +23074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -23190,7 +23190,7 @@
         <v>44.343958825600204</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -23306,7 +23306,7 @@
         <v>8529.1677131880751</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -23422,7 +23422,7 @@
         <v>319.88574184503312</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>58</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>350.77416846678238</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -23654,7 +23654,7 @@
         <v>7750.6701912303888</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>58</v>
       </c>
@@ -23770,7 +23770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>58</v>
       </c>
@@ -23886,7 +23886,7 @@
         <v>2.6664611652349643</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -24118,7 +24118,7 @@
         <v>208.08746798600444</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -24234,7 +24234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -24350,7 +24350,7 @@
         <v>129.87234655622791</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>58</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>429.95529990534391</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -24582,7 +24582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -24698,7 +24698,7 @@
         <v>47.530657317329741</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -24814,7 +24814,7 @@
         <v>58.427026721518601</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -24930,7 +24930,7 @@
         <v>87.81504859555379</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>58</v>
       </c>
